--- a/public/Risk_Template.xlsx
+++ b/public/Risk_Template.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\harms\Desktop\CH_FILES\Development\dms_demo_tau5\frontend\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A623364-82C1-4DAA-9CAA-148C4C954981}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ACF41DC-D1A5-45BB-ACD3-885DE58DACF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="683" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2250" yWindow="2250" windowWidth="21600" windowHeight="11835" tabRatio="683" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0. Revisions" sheetId="15" r:id="rId1"/>
     <sheet name="1. General Information" sheetId="1" r:id="rId2"/>
     <sheet name="2. Standard Information" sheetId="37" r:id="rId3"/>
-    <sheet name="3. General Risk Register" sheetId="41" r:id="rId4"/>
-    <sheet name="4. General JRA Evnts and Ctrls" sheetId="40" r:id="rId5"/>
-    <sheet name="5. 5x5 Matrix" sheetId="38" r:id="rId6"/>
+    <sheet name="3. General Risk Register" sheetId="41" state="hidden" r:id="rId4"/>
+    <sheet name="3. General JRA Evnts and Ctrls" sheetId="40" r:id="rId5"/>
+    <sheet name="4. 5x5 Matrix" sheetId="38" r:id="rId6"/>
     <sheet name="#Ref" sheetId="34" r:id="rId7"/>
   </sheets>
   <definedNames>
@@ -27,24 +27,24 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'0. Revisions'!$B$5:$F$104</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1. General Information'!$B$5:$AU$56</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2. Standard Information'!$B$5:$K$169</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'3. General JRA Evnts and Ctrls'!$B$5:$F$176</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'3. General Risk Register'!$B$5:$G$104</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'4. General JRA Evnts and Ctrls'!$B$5:$F$176</definedName>
     <definedName name="_HOC">#REF!</definedName>
     <definedName name="_SAFEGRP">#REF!</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="6">'#Ref'!$A$1:$H$24</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'0. Revisions'!$A$1:$G$101</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'1. General Information'!$A:$AV</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'2. Standard Information'!$A$1:$L$28</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'3. General JRA Evnts and Ctrls'!$A$1:$G$177</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'3. General Risk Register'!$A$1:$H$104</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'4. General JRA Evnts and Ctrls'!$A$1:$G$177</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">'5. 5x5 Matrix'!$A$1:$G$14</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'4. 5x5 Matrix'!$A$1:$G$14</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'#Ref'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'0. Revisions'!$5:$5</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'1. General Information'!$5:$5</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'2. Standard Information'!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'3. General JRA Evnts and Ctrls'!$5:$5</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'3. General Risk Register'!$5:$5</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="4">'4. General JRA Evnts and Ctrls'!$5:$5</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="5">'5. 5x5 Matrix'!#REF!</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'4. 5x5 Matrix'!#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -103,7 +103,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
   <metadataTypes count="1">
     <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
@@ -205,7 +205,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="378">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="378">
   <si>
     <t>Abbreviation</t>
   </si>
@@ -244,9 +244,6 @@
   </si>
   <si>
     <t>Name</t>
-  </si>
-  <si>
-    <t>Stakeholders</t>
   </si>
   <si>
     <t>Term</t>
@@ -1329,12 +1326,6 @@
     <t>Mobile Machinery</t>
   </si>
   <si>
-    <t>Standard Designations</t>
-  </si>
-  <si>
-    <t>Designation</t>
-  </si>
-  <si>
     <t>Main Task Step</t>
   </si>
   <si>
@@ -1342,6 +1333,15 @@
   </si>
   <si>
     <t>Category</t>
+  </si>
+  <si>
+    <t>Standard Positions</t>
+  </si>
+  <si>
+    <t>External Stakeholders</t>
+  </si>
+  <si>
+    <t>Company</t>
   </si>
 </sst>
 </file>
@@ -2104,10 +2104,10 @@
     <xf numFmtId="164" fontId="5" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="10" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2135,7 +2135,17 @@
     <cellStyle name="Normal 5" xfId="3" xr:uid="{151F580F-10B6-4A4F-A70C-A45C677C25FB}"/>
     <cellStyle name="Normal 9" xfId="1" xr:uid="{35A4EF1C-1C92-4220-B3BB-B271881CFCDD}"/>
   </cellStyles>
-  <dxfs count="70">
+  <dxfs count="71">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -4644,154 +4654,154 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E4DB93B9-9BB5-4807-B423-CDE49E544CAE}" name="Table15" displayName="Table15" ref="P1:P29" totalsRowShown="0" headerRowDxfId="69" dataDxfId="68" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E4DB93B9-9BB5-4807-B423-CDE49E544CAE}" name="Table15" displayName="Table15" ref="P1:P29" totalsRowShown="0" headerRowDxfId="70" dataDxfId="69" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
   <autoFilter ref="P1:P29" xr:uid="{E4DB93B9-9BB5-4807-B423-CDE49E544CAE}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{A4E83315-1532-4AAA-B923-2F307BFCA1CF}" name="Hazards" dataDxfId="67" dataCellStyle="Normal 2"/>
+    <tableColumn id="1" xr3:uid="{A4E83315-1532-4AAA-B923-2F307BFCA1CF}" name="Hazards" dataDxfId="68" dataCellStyle="Normal 2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{0FCA2908-9398-4E06-8D4A-AA405986137B}" name="Table6" displayName="Table6" ref="A20:A22" totalsRowShown="0" headerRowDxfId="38" dataDxfId="37" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{0FCA2908-9398-4E06-8D4A-AA405986137B}" name="Table6" displayName="Table6" ref="A20:A22" totalsRowShown="0" headerRowDxfId="39" dataDxfId="38" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
   <autoFilter ref="A20:A22" xr:uid="{0FCA2908-9398-4E06-8D4A-AA405986137B}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{356754D1-7D62-4C3B-B57A-69359BABF779}" name="Area Availability" dataDxfId="36" dataCellStyle="Normal 2"/>
+    <tableColumn id="1" xr3:uid="{356754D1-7D62-4C3B-B57A-69359BABF779}" name="Area Availability" dataDxfId="37" dataCellStyle="Normal 2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{C59949D0-7D9B-4005-8500-D07430169BBA}" name="Table7" displayName="Table7" ref="A31:A34" totalsRowShown="0" headerRowDxfId="35" dataDxfId="34" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{C59949D0-7D9B-4005-8500-D07430169BBA}" name="Table7" displayName="Table7" ref="A31:A34" totalsRowShown="0" headerRowDxfId="36" dataDxfId="35" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
   <autoFilter ref="A31:A34" xr:uid="{C59949D0-7D9B-4005-8500-D07430169BBA}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{67E618F0-E9E8-44B3-ACC9-CF52EEEE4259}" name="Control Information" dataDxfId="33" dataCellStyle="Normal 2"/>
+    <tableColumn id="1" xr3:uid="{67E618F0-E9E8-44B3-ACC9-CF52EEEE4259}" name="Control Information" dataDxfId="34" dataCellStyle="Normal 2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{13304DDB-7F05-451A-A3F7-1F8D3717FB26}" name="Table8" displayName="Table8" ref="C31:C35" totalsRowShown="0" headerRowDxfId="32" dataDxfId="31" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{13304DDB-7F05-451A-A3F7-1F8D3717FB26}" name="Table8" displayName="Table8" ref="C31:C35" totalsRowShown="0" headerRowDxfId="33" dataDxfId="32" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
   <autoFilter ref="C31:C35" xr:uid="{13304DDB-7F05-451A-A3F7-1F8D3717FB26}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{9FA7C898-B51E-48CD-92EF-C24E75422995}" name="Impact" dataDxfId="30" dataCellStyle="Normal 2"/>
+    <tableColumn id="1" xr3:uid="{9FA7C898-B51E-48CD-92EF-C24E75422995}" name="Impact" dataDxfId="31" dataCellStyle="Normal 2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{20BA4A9C-64E9-4AEF-B3E5-06080D2DFE85}" name="Table9" displayName="Table9" ref="E20:E27" totalsRowShown="0" headerRowDxfId="29" dataDxfId="28" headerRowCellStyle="Normal 9" dataCellStyle="Normal 5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{20BA4A9C-64E9-4AEF-B3E5-06080D2DFE85}" name="Table9" displayName="Table9" ref="E20:E27" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29" headerRowCellStyle="Normal 9" dataCellStyle="Normal 5">
   <autoFilter ref="E20:E27" xr:uid="{20BA4A9C-64E9-4AEF-B3E5-06080D2DFE85}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{52735A1B-A75E-4276-A8A4-3CB92E7D172D}" name="I_C" dataDxfId="27" dataCellStyle="Normal 5"/>
+    <tableColumn id="1" xr3:uid="{52735A1B-A75E-4276-A8A4-3CB92E7D172D}" name="I_C" dataDxfId="28" dataCellStyle="Normal 5"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{A2D68AEA-52A0-44F0-A125-B17009EE685F}" name="Table10" displayName="Table10" ref="C1:C3" totalsRowShown="0" headerRowDxfId="26" dataDxfId="25" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{A2D68AEA-52A0-44F0-A125-B17009EE685F}" name="Table10" displayName="Table10" ref="C1:C3" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
   <autoFilter ref="C1:C3" xr:uid="{A2D68AEA-52A0-44F0-A125-B17009EE685F}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{CA259FA7-AC99-4199-A618-8F3ABBFD9E1F}" name="YesNo" dataDxfId="24" dataCellStyle="Normal 2"/>
+    <tableColumn id="1" xr3:uid="{CA259FA7-AC99-4199-A618-8F3ABBFD9E1F}" name="YesNo" dataDxfId="25" dataCellStyle="Normal 2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{D326FF98-4466-4C63-AFAB-8AE31CC81CFF}" name="Table1" displayName="Table1" ref="T1:T10" totalsRowShown="0" headerRowDxfId="23" dataDxfId="22" headerRowCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{D326FF98-4466-4C63-AFAB-8AE31CC81CFF}" name="Table1" displayName="Table1" ref="T1:T10" totalsRowShown="0" headerRowDxfId="24" dataDxfId="23" headerRowCellStyle="Normal 2">
   <autoFilter ref="T1:T10" xr:uid="{D326FF98-4466-4C63-AFAB-8AE31CC81CFF}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{130EABA6-8BB2-4BC0-8AA8-0F2E876233A3}" name="Control Level" dataDxfId="21"/>
+    <tableColumn id="1" xr3:uid="{130EABA6-8BB2-4BC0-8AA8-0F2E876233A3}" name="Control Level" dataDxfId="22"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{89FED767-CB12-44E0-AD37-C4C058411E3B}" name="Table16" displayName="Table16" ref="R1:R12" totalsRowShown="0" headerRowDxfId="66" dataDxfId="65" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{89FED767-CB12-44E0-AD37-C4C058411E3B}" name="Table16" displayName="Table16" ref="R1:R12" totalsRowShown="0" headerRowDxfId="67" dataDxfId="66" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
   <autoFilter ref="R1:R12" xr:uid="{89FED767-CB12-44E0-AD37-C4C058411E3B}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{3E7C20E1-0083-4FA6-B8CD-F18BCFC29C0C}" name="Functions" dataDxfId="64" dataCellStyle="Normal 2"/>
+    <tableColumn id="1" xr3:uid="{3E7C20E1-0083-4FA6-B8CD-F18BCFC29C0C}" name="Functions" dataDxfId="65" dataCellStyle="Normal 2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{33461173-53BB-4469-B43B-C30157FF6B61}" name="Table17" displayName="Table17" ref="E1:E6" totalsRowShown="0" headerRowDxfId="63" dataDxfId="62" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{33461173-53BB-4469-B43B-C30157FF6B61}" name="Table17" displayName="Table17" ref="E1:E6" totalsRowShown="0" headerRowDxfId="64" dataDxfId="63" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
   <autoFilter ref="E1:E6" xr:uid="{33461173-53BB-4469-B43B-C30157FF6B61}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{FABE7ED9-6B7C-44E0-AD4D-8D1323A4E4F6}" name="Likelihood" dataDxfId="61" dataCellStyle="Normal 2"/>
+    <tableColumn id="1" xr3:uid="{FABE7ED9-6B7C-44E0-AD4D-8D1323A4E4F6}" name="Likelihood" dataDxfId="62" dataCellStyle="Normal 2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{8550E780-9FBF-45EB-9022-1895A1AF2ED0}" name="Table18" displayName="Table18" ref="G1:G6" totalsRowShown="0" headerRowDxfId="60" dataDxfId="59" headerRowCellStyle="Normal 2" dataCellStyle="Normal 9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{8550E780-9FBF-45EB-9022-1895A1AF2ED0}" name="Table18" displayName="Table18" ref="G1:G6" totalsRowShown="0" headerRowDxfId="61" dataDxfId="60" headerRowCellStyle="Normal 2" dataCellStyle="Normal 9">
   <autoFilter ref="G1:G6" xr:uid="{8550E780-9FBF-45EB-9022-1895A1AF2ED0}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{2299BFF3-AB2F-4B7A-95F8-98325172D078}" name="Consequence" dataDxfId="58" dataCellStyle="Normal 9"/>
+    <tableColumn id="1" xr3:uid="{2299BFF3-AB2F-4B7A-95F8-98325172D078}" name="Consequence" dataDxfId="59" dataCellStyle="Normal 9"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{D764ED73-5559-4234-BD02-EB4696632F02}" name="Table23" displayName="Table23" ref="B12:F16" totalsRowShown="0" headerRowDxfId="57" dataDxfId="56">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{D764ED73-5559-4234-BD02-EB4696632F02}" name="Table23" displayName="Table23" ref="B12:F16" totalsRowShown="0" headerRowDxfId="58" dataDxfId="57">
   <autoFilter ref="B12:F16" xr:uid="{D764ED73-5559-4234-BD02-EB4696632F02}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{C7665F04-656B-4655-BD2E-06B67D38E17F}" name="1 (L)" dataDxfId="55"/>
-    <tableColumn id="2" xr3:uid="{76ABF063-4E24-4CFA-86B9-0DC19CF24BBC}" name="3 (L)" dataDxfId="54"/>
-    <tableColumn id="3" xr3:uid="{D10437F8-ACDB-4874-8C10-6908FD164343}" name="6 (M)" dataDxfId="53" dataCellStyle="Normal 2"/>
-    <tableColumn id="4" xr3:uid="{2F00B1EC-703D-47C1-8612-94C91C8E9BC2}" name="10 (M)" dataDxfId="52"/>
-    <tableColumn id="5" xr3:uid="{C475F2A3-C677-435D-9202-AD792BCFE835}" name="15 (S)" dataDxfId="51" dataCellStyle="Normal 2"/>
+    <tableColumn id="1" xr3:uid="{C7665F04-656B-4655-BD2E-06B67D38E17F}" name="1 (L)" dataDxfId="56"/>
+    <tableColumn id="2" xr3:uid="{76ABF063-4E24-4CFA-86B9-0DC19CF24BBC}" name="3 (L)" dataDxfId="55"/>
+    <tableColumn id="3" xr3:uid="{D10437F8-ACDB-4874-8C10-6908FD164343}" name="6 (M)" dataDxfId="54" dataCellStyle="Normal 2"/>
+    <tableColumn id="4" xr3:uid="{2F00B1EC-703D-47C1-8612-94C91C8E9BC2}" name="10 (M)" dataDxfId="53"/>
+    <tableColumn id="5" xr3:uid="{C475F2A3-C677-435D-9202-AD792BCFE835}" name="15 (S)" dataDxfId="52" dataCellStyle="Normal 2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{35CE8A27-FB09-4D6F-BFEF-53A495779208}" name="Table24" displayName="Table24" ref="I1:I7" totalsRowShown="0" headerRowDxfId="50" dataDxfId="49" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{35CE8A27-FB09-4D6F-BFEF-53A495779208}" name="Table24" displayName="Table24" ref="I1:I7" totalsRowShown="0" headerRowDxfId="51" dataDxfId="50" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
   <autoFilter ref="I1:I7" xr:uid="{35CE8A27-FB09-4D6F-BFEF-53A495779208}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{67A595D5-4B09-40D8-AF0A-30E7CB998DB1}" name="Control Type" dataDxfId="48" dataCellStyle="Normal 2"/>
+    <tableColumn id="1" xr3:uid="{67A595D5-4B09-40D8-AF0A-30E7CB998DB1}" name="Control Type" dataDxfId="49" dataCellStyle="Normal 2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{3C4E97BF-F9BA-47B6-8E06-E99D4DB8A8A1}" name="Table25" displayName="Table25" ref="K1:K5" totalsRowShown="0" headerRowDxfId="47" dataDxfId="46" headerRowCellStyle="Normal 2" dataCellStyle="Normal 9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{3C4E97BF-F9BA-47B6-8E06-E99D4DB8A8A1}" name="Table25" displayName="Table25" ref="K1:K5" totalsRowShown="0" headerRowDxfId="48" dataDxfId="47" headerRowCellStyle="Normal 2" dataCellStyle="Normal 9">
   <autoFilter ref="K1:K5" xr:uid="{3C4E97BF-F9BA-47B6-8E06-E99D4DB8A8A1}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{28CA88D8-332A-4CFD-8883-2D8BDB97106E}" name="Control Quality" dataDxfId="45" dataCellStyle="Normal 9"/>
+    <tableColumn id="1" xr3:uid="{28CA88D8-332A-4CFD-8883-2D8BDB97106E}" name="Control Quality" dataDxfId="46" dataCellStyle="Normal 9"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{3025DD08-08F4-4688-ACCB-86792B0FD2C5}" name="Table2" displayName="Table2" ref="A1:A8" totalsRowShown="0" headerRowDxfId="44" dataDxfId="43" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{3025DD08-08F4-4688-ACCB-86792B0FD2C5}" name="Table2" displayName="Table2" ref="A1:A8" totalsRowShown="0" headerRowDxfId="45" dataDxfId="44" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
   <autoFilter ref="A1:A8" xr:uid="{3025DD08-08F4-4688-ACCB-86792B0FD2C5}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{74B604CB-6600-40E4-BC6B-168E69749558}" name="Consequence_x000a_Type" dataDxfId="42" dataCellStyle="Normal 2"/>
+    <tableColumn id="1" xr3:uid="{74B604CB-6600-40E4-BC6B-168E69749558}" name="Consequence_x000a_Type" dataDxfId="43" dataCellStyle="Normal 2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{72A36D82-7F17-4619-896F-7F0787B6574E}" name="Table4" displayName="Table4" ref="C20:C23" totalsRowShown="0" headerRowDxfId="41" dataDxfId="40">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{72A36D82-7F17-4619-896F-7F0787B6574E}" name="Table4" displayName="Table4" ref="C20:C23" totalsRowShown="0" headerRowDxfId="42" dataDxfId="41">
   <autoFilter ref="C20:C23" xr:uid="{72A36D82-7F17-4619-896F-7F0787B6574E}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{A6FFA3B8-0CD1-4148-8182-FF1AF41B244D}" name="Control_Detail" dataDxfId="39"/>
+    <tableColumn id="1" xr3:uid="{A6FFA3B8-0CD1-4148-8182-FF1AF41B244D}" name="Control_Detail" dataDxfId="40"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5100,7 +5110,7 @@
     </row>
     <row r="4" spans="2:6" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="112" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C4" s="113"/>
       <c r="D4" s="113"/>
@@ -5109,19 +5119,19 @@
     </row>
     <row r="5" spans="2:6" ht="19.350000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="77" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="78" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="78" t="s">
+      <c r="D5" s="78" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="79" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="78" t="s">
+      <c r="F5" s="78" t="s">
         <v>20</v>
-      </c>
-      <c r="E5" s="79" t="s">
-        <v>17</v>
-      </c>
-      <c r="F5" s="78" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.25">
@@ -5839,7 +5849,7 @@
   <sheetPr codeName="Sheet4">
     <tabColor rgb="FF7EAC89"/>
   </sheetPr>
-  <dimension ref="B1:AV176"/>
+  <dimension ref="B1:AU176"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="1.140625" style="66" customWidth="1"/>
@@ -5874,9 +5884,8 @@
     <col min="30" max="30" width="32.42578125" style="66" customWidth="1"/>
     <col min="31" max="31" width="2.42578125" style="66" customWidth="1"/>
     <col min="32" max="32" width="3.85546875" style="66" customWidth="1"/>
-    <col min="33" max="33" width="22.85546875" style="66" customWidth="1"/>
-    <col min="34" max="34" width="30.85546875" style="66" customWidth="1"/>
-    <col min="35" max="35" width="2.42578125" style="66" customWidth="1"/>
+    <col min="33" max="34" width="22.85546875" style="66" customWidth="1"/>
+    <col min="35" max="35" width="30.85546875" style="66" customWidth="1"/>
     <col min="36" max="36" width="3.85546875" style="66" customWidth="1"/>
     <col min="37" max="37" width="22.85546875" style="66" customWidth="1"/>
     <col min="38" max="38" width="2.42578125" style="66" customWidth="1"/>
@@ -5911,18 +5920,18 @@
       <c r="AU3" s="6"/>
     </row>
     <row r="4" spans="2:47" s="1" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="116" t="s">
+      <c r="B4" s="115" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="116"/>
-      <c r="D4" s="116"/>
-      <c r="E4" s="116"/>
-      <c r="G4" s="116" t="s">
-        <v>371</v>
-      </c>
-      <c r="H4" s="116"/>
-      <c r="I4" s="116"/>
-      <c r="J4" s="116"/>
+      <c r="C4" s="115"/>
+      <c r="D4" s="115"/>
+      <c r="E4" s="115"/>
+      <c r="G4" s="115" t="s">
+        <v>370</v>
+      </c>
+      <c r="H4" s="115"/>
+      <c r="I4" s="115"/>
+      <c r="J4" s="115"/>
       <c r="L4" s="67" t="s">
         <v>2</v>
       </c>
@@ -5944,31 +5953,32 @@
       <c r="Y4" s="67"/>
       <c r="Z4" s="67"/>
       <c r="AB4" s="67" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="AC4" s="67"/>
       <c r="AD4" s="67"/>
       <c r="AF4" s="67" t="s">
-        <v>13</v>
+        <v>376</v>
       </c>
       <c r="AG4" s="67"/>
       <c r="AH4" s="67"/>
-      <c r="AJ4" s="116" t="s">
-        <v>265</v>
-      </c>
-      <c r="AK4" s="116"/>
+      <c r="AI4" s="67"/>
+      <c r="AJ4" s="115" t="s">
+        <v>264</v>
+      </c>
+      <c r="AK4" s="115"/>
       <c r="AL4" s="9"/>
-      <c r="AM4" s="116" t="s">
-        <v>344</v>
-      </c>
-      <c r="AN4" s="116"/>
-      <c r="AP4" s="115" t="s">
-        <v>221</v>
-      </c>
-      <c r="AQ4" s="116"/>
-      <c r="AR4" s="116"/>
+      <c r="AM4" s="115" t="s">
+        <v>343</v>
+      </c>
+      <c r="AN4" s="115"/>
+      <c r="AP4" s="116" t="s">
+        <v>220</v>
+      </c>
+      <c r="AQ4" s="115"/>
+      <c r="AR4" s="115"/>
       <c r="AT4" s="112" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="AU4" s="112"/>
     </row>
@@ -5983,19 +5993,19 @@
         <v>1</v>
       </c>
       <c r="E5" s="68" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G5" s="68" t="s">
         <v>9</v>
       </c>
       <c r="H5" s="68" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I5" s="68" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="J5" s="68" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L5" s="68" t="s">
         <v>9</v>
@@ -6004,7 +6014,7 @@
         <v>2</v>
       </c>
       <c r="N5" s="68" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="P5" s="68" t="s">
         <v>9</v>
@@ -6013,7 +6023,7 @@
         <v>3</v>
       </c>
       <c r="R5" s="68" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="T5" s="68" t="s">
         <v>9</v>
@@ -6022,7 +6032,7 @@
         <v>10</v>
       </c>
       <c r="V5" s="68" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="X5" s="68" t="s">
         <v>9</v>
@@ -6031,7 +6041,7 @@
         <v>4</v>
       </c>
       <c r="Z5" s="68" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AB5" s="68" t="s">
         <v>9</v>
@@ -6040,7 +6050,7 @@
         <v>11</v>
       </c>
       <c r="AD5" s="68" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AF5" s="68" t="s">
         <v>9</v>
@@ -6049,35 +6059,38 @@
         <v>12</v>
       </c>
       <c r="AH5" s="68" t="s">
+        <v>377</v>
+      </c>
+      <c r="AI5" s="68" t="s">
         <v>5</v>
       </c>
       <c r="AJ5" s="68" t="s">
         <v>9</v>
       </c>
       <c r="AK5" s="68" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL5" s="85"/>
       <c r="AM5" s="68" t="s">
         <v>9</v>
       </c>
       <c r="AN5" s="68" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="AP5" s="70" t="s">
         <v>9</v>
       </c>
       <c r="AQ5" s="68" t="s">
+        <v>221</v>
+      </c>
+      <c r="AR5" s="68" t="s">
         <v>222</v>
-      </c>
-      <c r="AR5" s="68" t="s">
-        <v>223</v>
       </c>
       <c r="AT5" s="77" t="s">
         <v>9</v>
       </c>
       <c r="AU5" s="77" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
     </row>
     <row r="6" spans="2:47" x14ac:dyDescent="0.25">
@@ -6107,6 +6120,7 @@
       <c r="AF6" s="71"/>
       <c r="AG6" s="72"/>
       <c r="AH6" s="72"/>
+      <c r="AI6" s="72"/>
       <c r="AJ6" s="71"/>
       <c r="AK6" s="72"/>
       <c r="AL6" s="69"/>
@@ -6145,6 +6159,7 @@
       <c r="AF7" s="71"/>
       <c r="AG7" s="72"/>
       <c r="AH7" s="72"/>
+      <c r="AI7" s="72"/>
       <c r="AJ7" s="71"/>
       <c r="AK7" s="72"/>
       <c r="AL7" s="69"/>
@@ -6183,6 +6198,7 @@
       <c r="AF8" s="71"/>
       <c r="AG8" s="72"/>
       <c r="AH8" s="72"/>
+      <c r="AI8" s="72"/>
       <c r="AJ8" s="71"/>
       <c r="AK8" s="72"/>
       <c r="AL8" s="69"/>
@@ -6221,6 +6237,7 @@
       <c r="AF9" s="71"/>
       <c r="AG9" s="72"/>
       <c r="AH9" s="72"/>
+      <c r="AI9" s="72"/>
       <c r="AJ9" s="71"/>
       <c r="AK9" s="72"/>
       <c r="AL9" s="69"/>
@@ -6259,6 +6276,7 @@
       <c r="AF10" s="71"/>
       <c r="AG10" s="72"/>
       <c r="AH10" s="72"/>
+      <c r="AI10" s="72"/>
       <c r="AJ10" s="71"/>
       <c r="AK10" s="72"/>
       <c r="AL10" s="69"/>
@@ -6297,6 +6315,7 @@
       <c r="AF11" s="71"/>
       <c r="AG11" s="72"/>
       <c r="AH11" s="72"/>
+      <c r="AI11" s="72"/>
       <c r="AJ11" s="71"/>
       <c r="AK11" s="72"/>
       <c r="AL11" s="69"/>
@@ -6335,6 +6354,7 @@
       <c r="AF12" s="71"/>
       <c r="AG12" s="72"/>
       <c r="AH12" s="72"/>
+      <c r="AI12" s="72"/>
       <c r="AJ12" s="71"/>
       <c r="AK12" s="72"/>
       <c r="AL12" s="69"/>
@@ -6373,6 +6393,7 @@
       <c r="AF13" s="71"/>
       <c r="AG13" s="72"/>
       <c r="AH13" s="72"/>
+      <c r="AI13" s="72"/>
       <c r="AJ13" s="71"/>
       <c r="AK13" s="72"/>
       <c r="AL13" s="69"/>
@@ -6411,6 +6432,7 @@
       <c r="AF14" s="71"/>
       <c r="AG14" s="72"/>
       <c r="AH14" s="72"/>
+      <c r="AI14" s="72"/>
       <c r="AJ14" s="71"/>
       <c r="AK14" s="72"/>
       <c r="AL14" s="69"/>
@@ -6449,6 +6471,7 @@
       <c r="AF15" s="71"/>
       <c r="AG15" s="72"/>
       <c r="AH15" s="72"/>
+      <c r="AI15" s="72"/>
       <c r="AJ15" s="71"/>
       <c r="AK15" s="72"/>
       <c r="AL15" s="69"/>
@@ -6486,6 +6509,7 @@
       <c r="AF16" s="71"/>
       <c r="AG16" s="72"/>
       <c r="AH16" s="72"/>
+      <c r="AI16" s="72"/>
       <c r="AJ16" s="71"/>
       <c r="AK16" s="72"/>
       <c r="AL16" s="69"/>
@@ -6524,6 +6548,7 @@
       <c r="AF17" s="71"/>
       <c r="AG17" s="72"/>
       <c r="AH17" s="72"/>
+      <c r="AI17" s="72"/>
       <c r="AJ17" s="71"/>
       <c r="AK17" s="72"/>
       <c r="AL17" s="69"/>
@@ -6562,6 +6587,7 @@
       <c r="AF18" s="71"/>
       <c r="AG18" s="72"/>
       <c r="AH18" s="72"/>
+      <c r="AI18" s="72"/>
       <c r="AJ18" s="71"/>
       <c r="AK18" s="72"/>
       <c r="AL18" s="69"/>
@@ -6600,6 +6626,7 @@
       <c r="AF19" s="71"/>
       <c r="AG19" s="72"/>
       <c r="AH19" s="72"/>
+      <c r="AI19" s="72"/>
       <c r="AJ19" s="71"/>
       <c r="AK19" s="72"/>
       <c r="AL19" s="69"/>
@@ -6638,6 +6665,7 @@
       <c r="AF20" s="71"/>
       <c r="AG20" s="72"/>
       <c r="AH20" s="72"/>
+      <c r="AI20" s="72"/>
       <c r="AJ20" s="71"/>
       <c r="AK20" s="72"/>
       <c r="AL20" s="69"/>
@@ -6676,6 +6704,7 @@
       <c r="AF21" s="71"/>
       <c r="AG21" s="72"/>
       <c r="AH21" s="72"/>
+      <c r="AI21" s="72"/>
       <c r="AJ21" s="71"/>
       <c r="AK21" s="72"/>
       <c r="AL21" s="69"/>
@@ -6714,6 +6743,7 @@
       <c r="AF22" s="71"/>
       <c r="AG22" s="72"/>
       <c r="AH22" s="72"/>
+      <c r="AI22" s="72"/>
       <c r="AJ22" s="71"/>
       <c r="AK22" s="72"/>
       <c r="AL22" s="69"/>
@@ -6752,6 +6782,7 @@
       <c r="AF23" s="71"/>
       <c r="AG23" s="72"/>
       <c r="AH23" s="72"/>
+      <c r="AI23" s="72"/>
       <c r="AJ23" s="71"/>
       <c r="AK23" s="72"/>
       <c r="AL23" s="69"/>
@@ -6790,6 +6821,7 @@
       <c r="AF24" s="71"/>
       <c r="AG24" s="72"/>
       <c r="AH24" s="72"/>
+      <c r="AI24" s="72"/>
       <c r="AJ24" s="71"/>
       <c r="AK24" s="72"/>
       <c r="AL24" s="69"/>
@@ -6828,6 +6860,7 @@
       <c r="AF25" s="71"/>
       <c r="AG25" s="72"/>
       <c r="AH25" s="72"/>
+      <c r="AI25" s="72"/>
       <c r="AJ25" s="71"/>
       <c r="AK25" s="72"/>
       <c r="AL25" s="69"/>
@@ -6866,6 +6899,7 @@
       <c r="AF26" s="71"/>
       <c r="AG26" s="72"/>
       <c r="AH26" s="72"/>
+      <c r="AI26" s="72"/>
       <c r="AJ26" s="71"/>
       <c r="AK26" s="72"/>
       <c r="AL26" s="69"/>
@@ -6904,6 +6938,7 @@
       <c r="AF27" s="71"/>
       <c r="AG27" s="72"/>
       <c r="AH27" s="72"/>
+      <c r="AI27" s="72"/>
       <c r="AJ27" s="71"/>
       <c r="AK27" s="72"/>
       <c r="AL27" s="69"/>
@@ -6942,6 +6977,7 @@
       <c r="AF28" s="71"/>
       <c r="AG28" s="72"/>
       <c r="AH28" s="72"/>
+      <c r="AI28" s="72"/>
       <c r="AJ28" s="71"/>
       <c r="AK28" s="72"/>
       <c r="AL28" s="69"/>
@@ -6980,6 +7016,7 @@
       <c r="AF29" s="71"/>
       <c r="AG29" s="72"/>
       <c r="AH29" s="72"/>
+      <c r="AI29" s="72"/>
       <c r="AJ29" s="71"/>
       <c r="AK29" s="72"/>
       <c r="AL29" s="69"/>
@@ -7018,6 +7055,7 @@
       <c r="AF30" s="71"/>
       <c r="AG30" s="72"/>
       <c r="AH30" s="72"/>
+      <c r="AI30" s="72"/>
       <c r="AJ30" s="71"/>
       <c r="AK30" s="72"/>
       <c r="AL30" s="69"/>
@@ -7056,6 +7094,7 @@
       <c r="AF31" s="71"/>
       <c r="AG31" s="72"/>
       <c r="AH31" s="72"/>
+      <c r="AI31" s="72"/>
       <c r="AJ31" s="71"/>
       <c r="AK31" s="72"/>
       <c r="AL31" s="69"/>
@@ -7094,6 +7133,7 @@
       <c r="AF32" s="71"/>
       <c r="AG32" s="72"/>
       <c r="AH32" s="72"/>
+      <c r="AI32" s="72"/>
       <c r="AJ32" s="71"/>
       <c r="AK32" s="72"/>
       <c r="AL32" s="69"/>
@@ -7132,6 +7172,7 @@
       <c r="AF33" s="71"/>
       <c r="AG33" s="72"/>
       <c r="AH33" s="72"/>
+      <c r="AI33" s="72"/>
       <c r="AJ33" s="71"/>
       <c r="AK33" s="72"/>
       <c r="AL33" s="69"/>
@@ -7170,6 +7211,7 @@
       <c r="AF34" s="71"/>
       <c r="AG34" s="72"/>
       <c r="AH34" s="72"/>
+      <c r="AI34" s="72"/>
       <c r="AJ34" s="71"/>
       <c r="AK34" s="72"/>
       <c r="AL34" s="69"/>
@@ -7208,6 +7250,7 @@
       <c r="AF35" s="71"/>
       <c r="AG35" s="72"/>
       <c r="AH35" s="72"/>
+      <c r="AI35" s="72"/>
       <c r="AJ35" s="71"/>
       <c r="AK35" s="72"/>
       <c r="AL35" s="69"/>
@@ -7246,6 +7289,7 @@
       <c r="AF36" s="71"/>
       <c r="AG36" s="72"/>
       <c r="AH36" s="72"/>
+      <c r="AI36" s="72"/>
       <c r="AJ36" s="71"/>
       <c r="AK36" s="72"/>
       <c r="AL36" s="69"/>
@@ -7284,6 +7328,7 @@
       <c r="AF37" s="71"/>
       <c r="AG37" s="72"/>
       <c r="AH37" s="72"/>
+      <c r="AI37" s="72"/>
       <c r="AJ37" s="71"/>
       <c r="AK37" s="72"/>
       <c r="AL37" s="69"/>
@@ -7322,6 +7367,7 @@
       <c r="AF38" s="71"/>
       <c r="AG38" s="72"/>
       <c r="AH38" s="72"/>
+      <c r="AI38" s="72"/>
       <c r="AJ38" s="71"/>
       <c r="AK38" s="72"/>
       <c r="AL38" s="69"/>
@@ -7360,6 +7406,7 @@
       <c r="AF39" s="71"/>
       <c r="AG39" s="72"/>
       <c r="AH39" s="72"/>
+      <c r="AI39" s="72"/>
       <c r="AJ39" s="71"/>
       <c r="AK39" s="72"/>
       <c r="AL39" s="69"/>
@@ -7398,6 +7445,7 @@
       <c r="AF40" s="71"/>
       <c r="AG40" s="72"/>
       <c r="AH40" s="72"/>
+      <c r="AI40" s="72"/>
       <c r="AJ40" s="71"/>
       <c r="AK40" s="72"/>
       <c r="AL40" s="69"/>
@@ -7436,6 +7484,7 @@
       <c r="AF41" s="71"/>
       <c r="AG41" s="72"/>
       <c r="AH41" s="72"/>
+      <c r="AI41" s="72"/>
       <c r="AJ41" s="71"/>
       <c r="AK41" s="72"/>
       <c r="AL41" s="69"/>
@@ -7474,6 +7523,7 @@
       <c r="AF42" s="71"/>
       <c r="AG42" s="72"/>
       <c r="AH42" s="72"/>
+      <c r="AI42" s="72"/>
       <c r="AJ42" s="71"/>
       <c r="AK42" s="72"/>
       <c r="AL42" s="69"/>
@@ -7512,6 +7562,7 @@
       <c r="AF43" s="71"/>
       <c r="AG43" s="72"/>
       <c r="AH43" s="72"/>
+      <c r="AI43" s="72"/>
       <c r="AJ43" s="71"/>
       <c r="AK43" s="72"/>
       <c r="AL43" s="69"/>
@@ -7550,6 +7601,7 @@
       <c r="AF44" s="71"/>
       <c r="AG44" s="72"/>
       <c r="AH44" s="72"/>
+      <c r="AI44" s="72"/>
       <c r="AJ44" s="71"/>
       <c r="AK44" s="72"/>
       <c r="AL44" s="69"/>
@@ -7588,6 +7640,7 @@
       <c r="AF45" s="71"/>
       <c r="AG45" s="72"/>
       <c r="AH45" s="72"/>
+      <c r="AI45" s="72"/>
       <c r="AJ45" s="71"/>
       <c r="AK45" s="72"/>
       <c r="AL45" s="69"/>
@@ -7626,6 +7679,7 @@
       <c r="AF46" s="71"/>
       <c r="AG46" s="72"/>
       <c r="AH46" s="72"/>
+      <c r="AI46" s="72"/>
       <c r="AJ46" s="71"/>
       <c r="AK46" s="72"/>
       <c r="AL46" s="69"/>
@@ -7664,6 +7718,7 @@
       <c r="AF47" s="71"/>
       <c r="AG47" s="72"/>
       <c r="AH47" s="72"/>
+      <c r="AI47" s="72"/>
       <c r="AJ47" s="71"/>
       <c r="AK47" s="72"/>
       <c r="AL47" s="69"/>
@@ -7702,6 +7757,7 @@
       <c r="AF48" s="71"/>
       <c r="AG48" s="72"/>
       <c r="AH48" s="72"/>
+      <c r="AI48" s="72"/>
       <c r="AJ48" s="71"/>
       <c r="AK48" s="72"/>
       <c r="AL48" s="69"/>
@@ -7740,6 +7796,7 @@
       <c r="AF49" s="71"/>
       <c r="AG49" s="72"/>
       <c r="AH49" s="72"/>
+      <c r="AI49" s="72"/>
       <c r="AJ49" s="71"/>
       <c r="AK49" s="72"/>
       <c r="AL49" s="69"/>
@@ -7778,6 +7835,7 @@
       <c r="AF50" s="71"/>
       <c r="AG50" s="72"/>
       <c r="AH50" s="72"/>
+      <c r="AI50" s="72"/>
       <c r="AJ50" s="71"/>
       <c r="AK50" s="72"/>
       <c r="AL50" s="69"/>
@@ -7816,6 +7874,7 @@
       <c r="AF51" s="71"/>
       <c r="AG51" s="72"/>
       <c r="AH51" s="72"/>
+      <c r="AI51" s="72"/>
       <c r="AJ51" s="71"/>
       <c r="AK51" s="72"/>
       <c r="AL51" s="69"/>
@@ -7854,6 +7913,7 @@
       <c r="AF52" s="71"/>
       <c r="AG52" s="72"/>
       <c r="AH52" s="72"/>
+      <c r="AI52" s="72"/>
       <c r="AJ52" s="71"/>
       <c r="AK52" s="72"/>
       <c r="AL52" s="69"/>
@@ -7892,6 +7952,7 @@
       <c r="AF53" s="71"/>
       <c r="AG53" s="72"/>
       <c r="AH53" s="72"/>
+      <c r="AI53" s="72"/>
       <c r="AJ53" s="71"/>
       <c r="AK53" s="72"/>
       <c r="AL53" s="69"/>
@@ -7930,6 +7991,7 @@
       <c r="AF54" s="71"/>
       <c r="AG54" s="72"/>
       <c r="AH54" s="72"/>
+      <c r="AI54" s="72"/>
       <c r="AJ54" s="71"/>
       <c r="AK54" s="72"/>
       <c r="AL54" s="69"/>
@@ -7968,6 +8030,7 @@
       <c r="AF55" s="71"/>
       <c r="AG55" s="72"/>
       <c r="AH55" s="72"/>
+      <c r="AI55" s="72"/>
       <c r="AJ55" s="71"/>
       <c r="AK55" s="72"/>
       <c r="AL55" s="69"/>
@@ -8005,6 +8068,7 @@
       <c r="AF56" s="71"/>
       <c r="AG56" s="72"/>
       <c r="AH56" s="72"/>
+      <c r="AI56" s="72"/>
       <c r="AJ56" s="71"/>
       <c r="AK56" s="72"/>
       <c r="AL56" s="69"/>
@@ -8043,6 +8107,7 @@
       <c r="AF57" s="71"/>
       <c r="AG57" s="72"/>
       <c r="AH57" s="72"/>
+      <c r="AI57" s="72"/>
       <c r="AJ57" s="71"/>
       <c r="AK57" s="72"/>
       <c r="AL57" s="69"/>
@@ -8081,6 +8146,7 @@
       <c r="AF58" s="71"/>
       <c r="AG58" s="72"/>
       <c r="AH58" s="72"/>
+      <c r="AI58" s="72"/>
       <c r="AJ58" s="71"/>
       <c r="AK58" s="72"/>
       <c r="AL58" s="69"/>
@@ -8119,6 +8185,7 @@
       <c r="AF59" s="71"/>
       <c r="AG59" s="72"/>
       <c r="AH59" s="72"/>
+      <c r="AI59" s="72"/>
       <c r="AJ59" s="71"/>
       <c r="AK59" s="72"/>
       <c r="AL59" s="69"/>
@@ -8157,6 +8224,7 @@
       <c r="AF60" s="71"/>
       <c r="AG60" s="72"/>
       <c r="AH60" s="72"/>
+      <c r="AI60" s="72"/>
       <c r="AJ60" s="71"/>
       <c r="AK60" s="72"/>
       <c r="AL60" s="69"/>
@@ -8195,6 +8263,7 @@
       <c r="AF61" s="71"/>
       <c r="AG61" s="72"/>
       <c r="AH61" s="72"/>
+      <c r="AI61" s="72"/>
       <c r="AJ61" s="71"/>
       <c r="AK61" s="72"/>
       <c r="AL61" s="69"/>
@@ -8233,6 +8302,7 @@
       <c r="AF62" s="71"/>
       <c r="AG62" s="72"/>
       <c r="AH62" s="72"/>
+      <c r="AI62" s="72"/>
       <c r="AJ62" s="71"/>
       <c r="AK62" s="72"/>
       <c r="AL62" s="69"/>
@@ -8271,6 +8341,7 @@
       <c r="AF63" s="71"/>
       <c r="AG63" s="72"/>
       <c r="AH63" s="72"/>
+      <c r="AI63" s="72"/>
       <c r="AJ63" s="71"/>
       <c r="AK63" s="72"/>
       <c r="AL63" s="69"/>
@@ -8309,6 +8380,7 @@
       <c r="AF64" s="71"/>
       <c r="AG64" s="72"/>
       <c r="AH64" s="72"/>
+      <c r="AI64" s="72"/>
       <c r="AJ64" s="71"/>
       <c r="AK64" s="72"/>
       <c r="AL64" s="69"/>
@@ -8347,6 +8419,7 @@
       <c r="AF65" s="71"/>
       <c r="AG65" s="72"/>
       <c r="AH65" s="72"/>
+      <c r="AI65" s="72"/>
       <c r="AJ65" s="71"/>
       <c r="AK65" s="72"/>
       <c r="AL65" s="69"/>
@@ -8385,6 +8458,7 @@
       <c r="AF66" s="71"/>
       <c r="AG66" s="72"/>
       <c r="AH66" s="72"/>
+      <c r="AI66" s="72"/>
       <c r="AJ66" s="71"/>
       <c r="AK66" s="72"/>
       <c r="AL66" s="69"/>
@@ -8423,6 +8497,7 @@
       <c r="AF67" s="71"/>
       <c r="AG67" s="72"/>
       <c r="AH67" s="72"/>
+      <c r="AI67" s="72"/>
       <c r="AJ67" s="71"/>
       <c r="AK67" s="72"/>
       <c r="AL67" s="69"/>
@@ -8461,6 +8536,7 @@
       <c r="AF68" s="71"/>
       <c r="AG68" s="72"/>
       <c r="AH68" s="72"/>
+      <c r="AI68" s="72"/>
       <c r="AJ68" s="71"/>
       <c r="AK68" s="72"/>
       <c r="AL68" s="69"/>
@@ -8499,6 +8575,7 @@
       <c r="AF69" s="71"/>
       <c r="AG69" s="72"/>
       <c r="AH69" s="72"/>
+      <c r="AI69" s="72"/>
       <c r="AJ69" s="71"/>
       <c r="AK69" s="72"/>
       <c r="AL69" s="69"/>
@@ -8537,6 +8614,7 @@
       <c r="AF70" s="71"/>
       <c r="AG70" s="72"/>
       <c r="AH70" s="72"/>
+      <c r="AI70" s="72"/>
       <c r="AJ70" s="71"/>
       <c r="AK70" s="72"/>
       <c r="AL70" s="69"/>
@@ -8575,6 +8653,7 @@
       <c r="AF71" s="71"/>
       <c r="AG71" s="72"/>
       <c r="AH71" s="72"/>
+      <c r="AI71" s="72"/>
       <c r="AJ71" s="71"/>
       <c r="AK71" s="72"/>
       <c r="AL71" s="69"/>
@@ -8613,6 +8692,7 @@
       <c r="AF72" s="71"/>
       <c r="AG72" s="72"/>
       <c r="AH72" s="72"/>
+      <c r="AI72" s="72"/>
       <c r="AJ72" s="71"/>
       <c r="AK72" s="72"/>
       <c r="AL72" s="69"/>
@@ -8651,6 +8731,7 @@
       <c r="AF73" s="71"/>
       <c r="AG73" s="72"/>
       <c r="AH73" s="72"/>
+      <c r="AI73" s="72"/>
       <c r="AJ73" s="71"/>
       <c r="AK73" s="72"/>
       <c r="AL73" s="69"/>
@@ -8689,6 +8770,7 @@
       <c r="AF74" s="71"/>
       <c r="AG74" s="72"/>
       <c r="AH74" s="72"/>
+      <c r="AI74" s="72"/>
       <c r="AJ74" s="71"/>
       <c r="AK74" s="72"/>
       <c r="AL74" s="69"/>
@@ -8727,6 +8809,7 @@
       <c r="AF75" s="71"/>
       <c r="AG75" s="72"/>
       <c r="AH75" s="72"/>
+      <c r="AI75" s="72"/>
       <c r="AJ75" s="71"/>
       <c r="AK75" s="72"/>
       <c r="AL75" s="69"/>
@@ -8765,6 +8848,7 @@
       <c r="AF76" s="71"/>
       <c r="AG76" s="72"/>
       <c r="AH76" s="72"/>
+      <c r="AI76" s="72"/>
       <c r="AJ76" s="71"/>
       <c r="AK76" s="72"/>
       <c r="AL76" s="69"/>
@@ -8803,6 +8887,7 @@
       <c r="AF77" s="71"/>
       <c r="AG77" s="72"/>
       <c r="AH77" s="72"/>
+      <c r="AI77" s="72"/>
       <c r="AJ77" s="71"/>
       <c r="AK77" s="72"/>
       <c r="AL77" s="69"/>
@@ -8841,6 +8926,7 @@
       <c r="AF78" s="71"/>
       <c r="AG78" s="72"/>
       <c r="AH78" s="72"/>
+      <c r="AI78" s="72"/>
       <c r="AJ78" s="71"/>
       <c r="AK78" s="72"/>
       <c r="AL78" s="69"/>
@@ -8879,6 +8965,7 @@
       <c r="AF79" s="71"/>
       <c r="AG79" s="72"/>
       <c r="AH79" s="72"/>
+      <c r="AI79" s="72"/>
       <c r="AJ79" s="71"/>
       <c r="AK79" s="72"/>
       <c r="AL79" s="69"/>
@@ -8917,6 +9004,7 @@
       <c r="AF80" s="71"/>
       <c r="AG80" s="72"/>
       <c r="AH80" s="72"/>
+      <c r="AI80" s="72"/>
       <c r="AJ80" s="71"/>
       <c r="AK80" s="72"/>
       <c r="AL80" s="69"/>
@@ -8955,6 +9043,7 @@
       <c r="AF81" s="71"/>
       <c r="AG81" s="72"/>
       <c r="AH81" s="72"/>
+      <c r="AI81" s="72"/>
       <c r="AJ81" s="71"/>
       <c r="AK81" s="72"/>
       <c r="AL81" s="69"/>
@@ -8993,6 +9082,7 @@
       <c r="AF82" s="71"/>
       <c r="AG82" s="72"/>
       <c r="AH82" s="72"/>
+      <c r="AI82" s="72"/>
       <c r="AJ82" s="71"/>
       <c r="AK82" s="72"/>
       <c r="AL82" s="69"/>
@@ -9031,6 +9121,7 @@
       <c r="AF83" s="71"/>
       <c r="AG83" s="72"/>
       <c r="AH83" s="72"/>
+      <c r="AI83" s="72"/>
       <c r="AJ83" s="71"/>
       <c r="AK83" s="72"/>
       <c r="AL83" s="69"/>
@@ -9069,6 +9160,7 @@
       <c r="AF84" s="71"/>
       <c r="AG84" s="72"/>
       <c r="AH84" s="72"/>
+      <c r="AI84" s="72"/>
       <c r="AJ84" s="71"/>
       <c r="AK84" s="72"/>
       <c r="AL84" s="69"/>
@@ -9107,6 +9199,7 @@
       <c r="AF85" s="71"/>
       <c r="AG85" s="72"/>
       <c r="AH85" s="72"/>
+      <c r="AI85" s="72"/>
       <c r="AJ85" s="71"/>
       <c r="AK85" s="72"/>
       <c r="AL85" s="69"/>
@@ -9145,6 +9238,7 @@
       <c r="AF86" s="71"/>
       <c r="AG86" s="72"/>
       <c r="AH86" s="72"/>
+      <c r="AI86" s="72"/>
       <c r="AJ86" s="71"/>
       <c r="AK86" s="72"/>
       <c r="AL86" s="69"/>
@@ -9183,6 +9277,7 @@
       <c r="AF87" s="71"/>
       <c r="AG87" s="72"/>
       <c r="AH87" s="72"/>
+      <c r="AI87" s="72"/>
       <c r="AJ87" s="71"/>
       <c r="AK87" s="72"/>
       <c r="AL87" s="69"/>
@@ -9221,6 +9316,7 @@
       <c r="AF88" s="71"/>
       <c r="AG88" s="72"/>
       <c r="AH88" s="72"/>
+      <c r="AI88" s="72"/>
       <c r="AJ88" s="71"/>
       <c r="AK88" s="72"/>
       <c r="AL88" s="69"/>
@@ -9259,6 +9355,7 @@
       <c r="AF89" s="71"/>
       <c r="AG89" s="72"/>
       <c r="AH89" s="72"/>
+      <c r="AI89" s="72"/>
       <c r="AJ89" s="71"/>
       <c r="AK89" s="72"/>
       <c r="AL89" s="69"/>
@@ -9297,6 +9394,7 @@
       <c r="AF90" s="71"/>
       <c r="AG90" s="72"/>
       <c r="AH90" s="72"/>
+      <c r="AI90" s="72"/>
       <c r="AJ90" s="71"/>
       <c r="AK90" s="72"/>
       <c r="AL90" s="69"/>
@@ -9335,6 +9433,7 @@
       <c r="AF91" s="71"/>
       <c r="AG91" s="72"/>
       <c r="AH91" s="72"/>
+      <c r="AI91" s="72"/>
       <c r="AJ91" s="71"/>
       <c r="AK91" s="72"/>
       <c r="AL91" s="69"/>
@@ -9373,6 +9472,7 @@
       <c r="AF92" s="71"/>
       <c r="AG92" s="72"/>
       <c r="AH92" s="72"/>
+      <c r="AI92" s="72"/>
       <c r="AJ92" s="71"/>
       <c r="AK92" s="72"/>
       <c r="AL92" s="69"/>
@@ -9411,6 +9511,7 @@
       <c r="AF93" s="71"/>
       <c r="AG93" s="72"/>
       <c r="AH93" s="72"/>
+      <c r="AI93" s="72"/>
       <c r="AJ93" s="71"/>
       <c r="AK93" s="72"/>
       <c r="AL93" s="69"/>
@@ -9449,6 +9550,7 @@
       <c r="AF94" s="71"/>
       <c r="AG94" s="72"/>
       <c r="AH94" s="72"/>
+      <c r="AI94" s="72"/>
       <c r="AJ94" s="71"/>
       <c r="AK94" s="72"/>
       <c r="AL94" s="69"/>
@@ -9487,6 +9589,7 @@
       <c r="AF95" s="71"/>
       <c r="AG95" s="72"/>
       <c r="AH95" s="72"/>
+      <c r="AI95" s="72"/>
       <c r="AJ95" s="71"/>
       <c r="AK95" s="72"/>
       <c r="AL95" s="69"/>
@@ -9525,6 +9628,7 @@
       <c r="AF96" s="71"/>
       <c r="AG96" s="72"/>
       <c r="AH96" s="72"/>
+      <c r="AI96" s="72"/>
       <c r="AJ96" s="71"/>
       <c r="AK96" s="72"/>
       <c r="AL96" s="69"/>
@@ -9563,6 +9667,7 @@
       <c r="AF97" s="71"/>
       <c r="AG97" s="72"/>
       <c r="AH97" s="72"/>
+      <c r="AI97" s="72"/>
       <c r="AJ97" s="71"/>
       <c r="AK97" s="72"/>
       <c r="AL97" s="69"/>
@@ -9601,6 +9706,7 @@
       <c r="AF98" s="71"/>
       <c r="AG98" s="72"/>
       <c r="AH98" s="72"/>
+      <c r="AI98" s="72"/>
       <c r="AJ98" s="71"/>
       <c r="AK98" s="72"/>
       <c r="AL98" s="69"/>
@@ -9639,6 +9745,7 @@
       <c r="AF99" s="71"/>
       <c r="AG99" s="72"/>
       <c r="AH99" s="72"/>
+      <c r="AI99" s="72"/>
       <c r="AJ99" s="71"/>
       <c r="AK99" s="72"/>
       <c r="AL99" s="69"/>
@@ -9677,6 +9784,7 @@
       <c r="AF100" s="71"/>
       <c r="AG100" s="72"/>
       <c r="AH100" s="72"/>
+      <c r="AI100" s="72"/>
       <c r="AJ100" s="71"/>
       <c r="AK100" s="72"/>
       <c r="AL100" s="69"/>
@@ -9715,6 +9823,7 @@
       <c r="AF101" s="71"/>
       <c r="AG101" s="72"/>
       <c r="AH101" s="72"/>
+      <c r="AI101" s="72"/>
       <c r="AJ101" s="71"/>
       <c r="AK101" s="72"/>
       <c r="AL101" s="69"/>
@@ -9753,6 +9862,7 @@
       <c r="AF102" s="71"/>
       <c r="AG102" s="72"/>
       <c r="AH102" s="72"/>
+      <c r="AI102" s="72"/>
       <c r="AJ102" s="71"/>
       <c r="AK102" s="72"/>
       <c r="AL102" s="69"/>
@@ -10066,63 +10176,63 @@
     <sortCondition ref="H6:H34"/>
   </sortState>
   <mergeCells count="6">
+    <mergeCell ref="AT4:AU4"/>
     <mergeCell ref="G4:J4"/>
     <mergeCell ref="AP4:AR4"/>
     <mergeCell ref="B4:E4"/>
     <mergeCell ref="AM4:AN4"/>
     <mergeCell ref="AJ4:AK4"/>
-    <mergeCell ref="AT4:AU4"/>
   </mergeCells>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="20" priority="250"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="251"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H6:H102">
-    <cfRule type="duplicateValues" dxfId="19" priority="386"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="387"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H27 H21:H24 H16:H17 H1:H11 H35:H1048576">
-    <cfRule type="duplicateValues" dxfId="18" priority="292"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="293"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M1:M1048576">
+    <cfRule type="duplicateValues" dxfId="18" priority="19"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q1:Q24 Q26:Q34 Q36:Q1048576">
     <cfRule type="duplicateValues" dxfId="17" priority="18"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q1:Q24 Q26:Q34 Q36:Q1048576">
-    <cfRule type="duplicateValues" dxfId="16" priority="17"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="Q25">
-    <cfRule type="duplicateValues" dxfId="15" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q35">
-    <cfRule type="duplicateValues" dxfId="14" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="U34:U36">
-    <cfRule type="duplicateValues" dxfId="13" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="U41">
-    <cfRule type="duplicateValues" dxfId="12" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="U57:U1048576 U37:U40 U1:U33 U42:U55">
+    <cfRule type="duplicateValues" dxfId="12" priority="17"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Y1:Y15 Y17:Y1048576 AC16">
     <cfRule type="duplicateValues" dxfId="11" priority="16"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Y1:Y15 Y17:Y1048576 AC16">
+  <conditionalFormatting sqref="AC17:AC1048576 AC1:AC15">
     <cfRule type="duplicateValues" dxfId="10" priority="15"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AC17:AC1048576 AC1:AC15">
-    <cfRule type="duplicateValues" dxfId="9" priority="14"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AG1:AG1048576">
+  <conditionalFormatting sqref="AK1:AK1048576">
     <cfRule type="duplicateValues" dxfId="8" priority="13"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AK1:AK1048576">
+  <conditionalFormatting sqref="AN1:AN1048576">
     <cfRule type="duplicateValues" dxfId="7" priority="12"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AN1:AN1048576">
-    <cfRule type="duplicateValues" dxfId="6" priority="11"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="AQ6:AQ102">
-    <cfRule type="duplicateValues" dxfId="5" priority="425"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="426"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AR1:AR1048576">
-    <cfRule type="duplicateValues" dxfId="4" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AG1:AH1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -10226,7 +10336,7 @@
     </row>
     <row r="4" spans="2:37" ht="13.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="112" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C4" s="112"/>
       <c r="D4" s="112"/>
@@ -10238,24 +10348,24 @@
       <c r="J4" s="112"/>
       <c r="K4" s="112"/>
       <c r="M4" s="113" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="N4" s="113"/>
       <c r="O4" s="113"/>
       <c r="P4" s="113"/>
       <c r="R4" s="113" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="S4" s="113"/>
       <c r="T4" s="113"/>
       <c r="U4" s="113"/>
       <c r="W4" s="113" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="X4" s="113"/>
       <c r="Y4" s="113"/>
       <c r="AA4" s="113" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AB4" s="113"/>
       <c r="AC4" s="113"/>
@@ -10263,7 +10373,7 @@
       <c r="AE4" s="113"/>
       <c r="AF4" s="113"/>
       <c r="AH4" s="113" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="AI4" s="113"/>
       <c r="AJ4" s="113"/>
@@ -10274,94 +10384,94 @@
         <v>9</v>
       </c>
       <c r="C5" s="78" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D5" s="103" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E5" s="103" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F5" s="78" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G5" s="79" t="s">
+        <v>30</v>
+      </c>
+      <c r="H5" s="79" t="s">
         <v>31</v>
       </c>
-      <c r="H5" s="79" t="s">
+      <c r="I5" s="78" t="s">
         <v>32</v>
       </c>
-      <c r="I5" s="78" t="s">
-        <v>33</v>
-      </c>
       <c r="J5" s="78" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K5" s="97" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="M5" s="78" t="s">
         <v>9</v>
       </c>
       <c r="N5" s="78" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O5" s="78" t="s">
         <v>1</v>
       </c>
       <c r="P5" s="78" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="R5" s="78" t="s">
         <v>9</v>
       </c>
       <c r="S5" s="78" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="T5" s="78" t="s">
         <v>1</v>
       </c>
       <c r="U5" s="78" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="W5" s="78" t="s">
         <v>9</v>
       </c>
       <c r="X5" s="78" t="s">
-        <v>374</v>
+        <v>5</v>
       </c>
       <c r="Y5" s="78" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AA5" s="78" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="AB5" s="78" t="s">
+        <v>341</v>
+      </c>
+      <c r="AC5" s="78" t="s">
+        <v>340</v>
+      </c>
+      <c r="AD5" s="78" t="s">
+        <v>339</v>
+      </c>
+      <c r="AE5" s="78" t="s">
+        <v>79</v>
+      </c>
+      <c r="AF5" s="78" t="s">
         <v>342</v>
       </c>
-      <c r="AC5" s="78" t="s">
-        <v>341</v>
-      </c>
-      <c r="AD5" s="78" t="s">
-        <v>340</v>
-      </c>
-      <c r="AE5" s="78" t="s">
-        <v>80</v>
-      </c>
-      <c r="AF5" s="78" t="s">
-        <v>343</v>
-      </c>
       <c r="AH5" s="78" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="AI5" s="78" t="s">
         <v>1</v>
       </c>
       <c r="AJ5" s="78" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="AK5" s="78" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="6" spans="2:37" ht="24" x14ac:dyDescent="0.25">
@@ -10387,34 +10497,34 @@
       <c r="X6" s="81"/>
       <c r="Y6" s="81"/>
       <c r="AA6" s="87" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="AB6" s="81" t="s">
+        <v>272</v>
+      </c>
+      <c r="AC6" s="81" t="s">
         <v>273</v>
       </c>
-      <c r="AC6" s="81" t="s">
+      <c r="AD6" s="81" t="s">
         <v>274</v>
       </c>
-      <c r="AD6" s="81" t="s">
+      <c r="AE6" s="81" t="s">
         <v>275</v>
       </c>
-      <c r="AE6" s="81" t="s">
+      <c r="AF6" s="81" t="s">
         <v>276</v>
       </c>
-      <c r="AF6" s="81" t="s">
-        <v>277</v>
-      </c>
       <c r="AH6" s="81" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="AI6" s="81" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="AJ6" s="81" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="AK6" s="81" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="7" spans="2:37" ht="60" x14ac:dyDescent="0.25">
@@ -10440,34 +10550,34 @@
       <c r="X7" s="81"/>
       <c r="Y7" s="81"/>
       <c r="AA7" s="87" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="AB7" s="81" t="s">
+        <v>277</v>
+      </c>
+      <c r="AC7" s="81" t="s">
         <v>278</v>
       </c>
-      <c r="AC7" s="81" t="s">
+      <c r="AD7" s="81" t="s">
         <v>279</v>
       </c>
-      <c r="AD7" s="81" t="s">
+      <c r="AE7" s="81" t="s">
         <v>280</v>
       </c>
-      <c r="AE7" s="81" t="s">
+      <c r="AF7" s="81" t="s">
         <v>281</v>
       </c>
-      <c r="AF7" s="81" t="s">
-        <v>282</v>
-      </c>
       <c r="AH7" s="81" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="AI7" s="81" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AJ7" s="81" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="AK7" s="81" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="8" spans="2:37" ht="48" x14ac:dyDescent="0.25">
@@ -10493,34 +10603,34 @@
       <c r="X8" s="81"/>
       <c r="Y8" s="81"/>
       <c r="AA8" s="87" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AB8" s="81" t="s">
+        <v>282</v>
+      </c>
+      <c r="AC8" s="81" t="s">
         <v>283</v>
       </c>
-      <c r="AC8" s="81" t="s">
+      <c r="AD8" s="81" t="s">
         <v>284</v>
       </c>
-      <c r="AD8" s="81" t="s">
+      <c r="AE8" s="81" t="s">
         <v>285</v>
       </c>
-      <c r="AE8" s="81" t="s">
+      <c r="AF8" s="81" t="s">
         <v>286</v>
       </c>
-      <c r="AF8" s="81" t="s">
-        <v>287</v>
-      </c>
       <c r="AH8" s="81" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="AI8" s="81" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="AJ8" s="81" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="AK8" s="81" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="9" spans="2:37" ht="48" x14ac:dyDescent="0.25">
@@ -10546,34 +10656,34 @@
       <c r="X9" s="81"/>
       <c r="Y9" s="81"/>
       <c r="AA9" s="87" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AB9" s="81" t="s">
+        <v>287</v>
+      </c>
+      <c r="AC9" s="81" t="s">
         <v>288</v>
       </c>
-      <c r="AC9" s="81" t="s">
+      <c r="AD9" s="81" t="s">
         <v>289</v>
       </c>
-      <c r="AD9" s="81" t="s">
+      <c r="AE9" s="81" t="s">
         <v>290</v>
       </c>
-      <c r="AE9" s="81" t="s">
+      <c r="AF9" s="81" t="s">
         <v>291</v>
       </c>
-      <c r="AF9" s="81" t="s">
-        <v>292</v>
-      </c>
       <c r="AH9" s="81" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AI9" s="81" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="AJ9" s="81" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="AK9" s="81" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="2:37" ht="48" x14ac:dyDescent="0.25">
@@ -10599,34 +10709,34 @@
       <c r="X10" s="81"/>
       <c r="Y10" s="81"/>
       <c r="AA10" s="87" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="AB10" s="81" t="s">
+        <v>292</v>
+      </c>
+      <c r="AC10" s="81" t="s">
         <v>293</v>
       </c>
-      <c r="AC10" s="81" t="s">
+      <c r="AD10" s="81" t="s">
         <v>294</v>
       </c>
-      <c r="AD10" s="81" t="s">
+      <c r="AE10" s="81" t="s">
         <v>295</v>
       </c>
-      <c r="AE10" s="81" t="s">
+      <c r="AF10" s="81" t="s">
         <v>296</v>
       </c>
-      <c r="AF10" s="81" t="s">
-        <v>297</v>
-      </c>
       <c r="AH10" s="81" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AI10" s="81" t="s">
+        <v>326</v>
+      </c>
+      <c r="AJ10" s="81" t="s">
         <v>327</v>
       </c>
-      <c r="AJ10" s="81" t="s">
-        <v>328</v>
-      </c>
       <c r="AK10" s="81" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="11" spans="2:37" ht="24" x14ac:dyDescent="0.25">
@@ -10648,34 +10758,34 @@
       <c r="X11" s="81"/>
       <c r="Y11" s="81"/>
       <c r="AA11" s="87" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="AB11" s="81" t="s">
+        <v>297</v>
+      </c>
+      <c r="AC11" s="81" t="s">
         <v>298</v>
       </c>
-      <c r="AC11" s="81" t="s">
+      <c r="AD11" s="81" t="s">
         <v>299</v>
       </c>
-      <c r="AD11" s="81" t="s">
+      <c r="AE11" s="81" t="s">
         <v>300</v>
       </c>
-      <c r="AE11" s="81" t="s">
+      <c r="AF11" s="81" t="s">
         <v>301</v>
       </c>
-      <c r="AF11" s="81" t="s">
-        <v>302</v>
-      </c>
       <c r="AH11" s="81" t="s">
+        <v>328</v>
+      </c>
+      <c r="AI11" s="81" t="s">
         <v>329</v>
       </c>
-      <c r="AI11" s="81" t="s">
-        <v>330</v>
-      </c>
       <c r="AJ11" s="81" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="AK11" s="81" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="12" spans="2:37" ht="36" x14ac:dyDescent="0.25">
@@ -10697,34 +10807,34 @@
       <c r="X12" s="81"/>
       <c r="Y12" s="81"/>
       <c r="AA12" s="87" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="AB12" s="81" t="s">
+        <v>302</v>
+      </c>
+      <c r="AC12" s="81" t="s">
         <v>303</v>
       </c>
-      <c r="AC12" s="81" t="s">
+      <c r="AD12" s="81" t="s">
         <v>304</v>
       </c>
-      <c r="AD12" s="81" t="s">
+      <c r="AE12" s="81" t="s">
         <v>305</v>
       </c>
-      <c r="AE12" s="81" t="s">
+      <c r="AF12" s="81" t="s">
         <v>306</v>
       </c>
-      <c r="AF12" s="81" t="s">
-        <v>307</v>
-      </c>
       <c r="AH12" s="81" t="s">
+        <v>330</v>
+      </c>
+      <c r="AI12" s="81" t="s">
         <v>331</v>
       </c>
-      <c r="AI12" s="81" t="s">
-        <v>332</v>
-      </c>
       <c r="AJ12" s="81" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="AK12" s="81" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="13" spans="2:37" x14ac:dyDescent="0.25">
@@ -10746,16 +10856,16 @@
       <c r="X13" s="81"/>
       <c r="Y13" s="81"/>
       <c r="AH13" s="81" t="s">
+        <v>332</v>
+      </c>
+      <c r="AI13" s="81" t="s">
         <v>333</v>
       </c>
-      <c r="AI13" s="81" t="s">
-        <v>334</v>
-      </c>
       <c r="AJ13" s="81" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="AK13" s="81" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="14" spans="2:37" ht="41.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -10777,16 +10887,16 @@
       <c r="X14" s="81"/>
       <c r="Y14" s="81"/>
       <c r="AH14" s="81" t="s">
+        <v>334</v>
+      </c>
+      <c r="AI14" s="81" t="s">
         <v>335</v>
       </c>
-      <c r="AI14" s="81" t="s">
-        <v>336</v>
-      </c>
       <c r="AJ14" s="81" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="AK14" s="81" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" spans="2:37" x14ac:dyDescent="0.25">
@@ -10808,16 +10918,16 @@
       <c r="X15" s="81"/>
       <c r="Y15" s="81"/>
       <c r="AH15" s="81" t="s">
+        <v>336</v>
+      </c>
+      <c r="AI15" s="81" t="s">
         <v>337</v>
       </c>
-      <c r="AI15" s="81" t="s">
+      <c r="AJ15" s="81" t="s">
         <v>338</v>
       </c>
-      <c r="AJ15" s="81" t="s">
-        <v>339</v>
-      </c>
       <c r="AK15" s="81" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="16" spans="2:37" x14ac:dyDescent="0.25">
@@ -13306,7 +13416,7 @@
     <mergeCell ref="W4:Y4"/>
   </mergeCells>
   <conditionalFormatting sqref="C6:C169">
-    <cfRule type="duplicateValues" dxfId="3" priority="105"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="105"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -13365,7 +13475,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E776848A-2589-4915-8D6F-4F9A89B0D7AA}">
   <sheetPr codeName="Sheet1">
-    <tabColor rgb="FF7EAC89"/>
+    <tabColor rgb="FFFF0000"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:G104"/>
@@ -13408,7 +13518,7 @@
     </row>
     <row r="4" spans="2:7" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="112" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C4" s="113"/>
       <c r="D4" s="113"/>
@@ -13421,19 +13531,19 @@
         <v>9</v>
       </c>
       <c r="C5" s="78" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D5" s="78" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E5" s="79" t="s">
+        <v>224</v>
+      </c>
+      <c r="F5" s="79" t="s">
         <v>225</v>
       </c>
-      <c r="F5" s="79" t="s">
+      <c r="G5" s="78" t="s">
         <v>226</v>
-      </c>
-      <c r="G5" s="78" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
@@ -14306,7 +14416,7 @@
     </row>
     <row r="4" spans="2:6" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="112" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C4" s="112"/>
       <c r="D4" s="113"/>
@@ -14318,16 +14428,16 @@
         <v>9</v>
       </c>
       <c r="C5" s="77" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="D5" s="78" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E5" s="78" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F5" s="79" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.25">
@@ -15598,7 +15708,7 @@
     </row>
     <row r="4" spans="2:8" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="88" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C4" s="89"/>
       <c r="D4" s="89"/>
@@ -15609,13 +15719,13 @@
     </row>
     <row r="5" spans="2:8" ht="28.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="117" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C5" s="118" t="s">
+        <v>35</v>
+      </c>
+      <c r="D5" s="118" t="s">
         <v>36</v>
-      </c>
-      <c r="D5" s="118" t="s">
-        <v>37</v>
       </c>
       <c r="E5" s="118"/>
       <c r="F5" s="118"/>
@@ -15626,134 +15736,134 @@
       <c r="B6" s="117"/>
       <c r="C6" s="118"/>
       <c r="D6" s="91" t="s">
+        <v>227</v>
+      </c>
+      <c r="E6" s="91" t="s">
         <v>228</v>
       </c>
-      <c r="E6" s="91" t="s">
+      <c r="F6" s="91" t="s">
         <v>229</v>
       </c>
-      <c r="F6" s="91" t="s">
+      <c r="G6" s="91" t="s">
         <v>230</v>
       </c>
-      <c r="G6" s="91" t="s">
+      <c r="H6" s="91" t="s">
         <v>231</v>
-      </c>
-      <c r="H6" s="91" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="7" spans="2:8" ht="28.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="102" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C7" s="92" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D7" s="93" t="s">
+        <v>238</v>
+      </c>
+      <c r="E7" s="94" t="s">
         <v>239</v>
       </c>
-      <c r="E7" s="94" t="s">
+      <c r="F7" s="94" t="s">
         <v>240</v>
       </c>
-      <c r="F7" s="94" t="s">
+      <c r="G7" s="95" t="s">
         <v>241</v>
       </c>
-      <c r="G7" s="95" t="s">
+      <c r="H7" s="95" t="s">
         <v>242</v>
-      </c>
-      <c r="H7" s="95" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="8" spans="2:8" ht="28.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="102" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C8" s="92" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D8" s="93" t="s">
+        <v>243</v>
+      </c>
+      <c r="E8" s="93" t="s">
         <v>244</v>
       </c>
-      <c r="E8" s="93" t="s">
+      <c r="F8" s="94" t="s">
         <v>245</v>
       </c>
-      <c r="F8" s="94" t="s">
+      <c r="G8" s="95" t="s">
         <v>246</v>
       </c>
-      <c r="G8" s="95" t="s">
+      <c r="H8" s="95" t="s">
         <v>247</v>
-      </c>
-      <c r="H8" s="95" t="s">
-        <v>248</v>
       </c>
     </row>
     <row r="9" spans="2:8" ht="28.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="102" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C9" s="92" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D9" s="96" t="s">
+        <v>248</v>
+      </c>
+      <c r="E9" s="93" t="s">
         <v>249</v>
       </c>
-      <c r="E9" s="93" t="s">
+      <c r="F9" s="94" t="s">
         <v>250</v>
       </c>
-      <c r="F9" s="94" t="s">
+      <c r="G9" s="94" t="s">
         <v>251</v>
       </c>
-      <c r="G9" s="94" t="s">
+      <c r="H9" s="95" t="s">
         <v>252</v>
-      </c>
-      <c r="H9" s="95" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="10" spans="2:8" ht="28.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="102" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C10" s="92" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D10" s="96" t="s">
+        <v>253</v>
+      </c>
+      <c r="E10" s="96" t="s">
         <v>254</v>
       </c>
-      <c r="E10" s="96" t="s">
+      <c r="F10" s="93" t="s">
         <v>255</v>
       </c>
-      <c r="F10" s="93" t="s">
+      <c r="G10" s="94" t="s">
         <v>256</v>
       </c>
-      <c r="G10" s="94" t="s">
+      <c r="H10" s="94" t="s">
         <v>257</v>
-      </c>
-      <c r="H10" s="94" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="11" spans="2:8" ht="28.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="102" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C11" s="92" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D11" s="96" t="s">
+        <v>258</v>
+      </c>
+      <c r="E11" s="96" t="s">
         <v>259</v>
       </c>
-      <c r="E11" s="96" t="s">
+      <c r="F11" s="93" t="s">
         <v>260</v>
       </c>
-      <c r="F11" s="93" t="s">
+      <c r="G11" s="93" t="s">
         <v>261</v>
       </c>
-      <c r="G11" s="93" t="s">
+      <c r="H11" s="94" t="s">
         <v>262</v>
-      </c>
-      <c r="H11" s="94" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="12" spans="2:8" x14ac:dyDescent="0.25">
@@ -16158,95 +16268,95 @@
   <sheetData>
     <row r="1" spans="1:27" s="13" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="E1" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="G1" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="I1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="K1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="K1" s="12" t="s">
+      <c r="M1" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="M1" s="14" t="s">
+      <c r="P1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="P1" s="12" t="s">
+      <c r="R1" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="R1" s="12" t="s">
+      <c r="T1" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="T1" s="15" t="s">
+      <c r="V1" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="X1" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="V1" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="X1" s="16" t="s">
+      <c r="Z1" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="Z1" s="16" t="s">
+      <c r="AA1" s="16" t="s">
         <v>45</v>
-      </c>
-      <c r="AA1" s="16" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:27" s="13" customFormat="1" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="17" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B2" s="18"/>
       <c r="C2" s="17" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D2" s="18"/>
       <c r="E2" s="19" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F2" s="18"/>
       <c r="G2" s="20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H2" s="18"/>
       <c r="I2" s="19" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J2" s="18"/>
       <c r="K2" s="98" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="L2" s="18"/>
       <c r="M2" s="20" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="N2" s="18"/>
       <c r="P2" s="19" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="Q2" s="18"/>
       <c r="R2" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="T2" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="T2" s="22" t="s">
+      <c r="V2" s="23" t="s">
         <v>54</v>
       </c>
-      <c r="V2" s="23" t="s">
+      <c r="X2" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="X2" s="24" t="s">
+      <c r="Z2" s="24" t="s">
         <v>56</v>
-      </c>
-      <c r="Z2" s="24" t="s">
-        <v>57</v>
       </c>
       <c r="AA2" s="24" t="e" vm="1">
         <v>#VALUE!</v>
@@ -16254,51 +16364,51 @@
     </row>
     <row r="3" spans="1:27" s="13" customFormat="1" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="17" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B3" s="18"/>
       <c r="C3" s="17" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D3" s="18"/>
       <c r="E3" s="19" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F3" s="18"/>
       <c r="G3" s="20" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H3" s="18"/>
       <c r="I3" s="19" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J3" s="18"/>
       <c r="K3" s="99" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="L3" s="18"/>
       <c r="M3" s="20" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N3" s="18"/>
       <c r="P3" s="19" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q3" s="18"/>
       <c r="R3" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="T3" s="22" t="s">
         <v>64</v>
       </c>
-      <c r="T3" s="22" t="s">
+      <c r="V3" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="V3" s="23" t="s">
+      <c r="X3" s="24" t="s">
         <v>66</v>
       </c>
-      <c r="X3" s="24" t="s">
+      <c r="Z3" s="24" t="s">
         <v>67</v>
-      </c>
-      <c r="Z3" s="24" t="s">
-        <v>68</v>
       </c>
       <c r="AA3" s="24" t="e" vm="2">
         <v>#VALUE!</v>
@@ -16306,49 +16416,49 @@
     </row>
     <row r="4" spans="1:27" s="13" customFormat="1" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B4" s="18"/>
       <c r="C4" s="18"/>
       <c r="D4" s="18"/>
       <c r="E4" s="19" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F4" s="18"/>
       <c r="G4" s="20" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H4" s="18"/>
       <c r="I4" s="19" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="J4" s="18"/>
       <c r="K4" s="100" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="L4" s="18"/>
       <c r="M4" s="20" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="N4" s="18"/>
       <c r="P4" s="19" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q4" s="18"/>
       <c r="R4" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="T4" s="22" t="s">
         <v>74</v>
       </c>
-      <c r="T4" s="22" t="s">
+      <c r="V4" s="23" t="s">
         <v>75</v>
       </c>
-      <c r="V4" s="23" t="s">
+      <c r="X4" s="24" t="s">
         <v>76</v>
       </c>
-      <c r="X4" s="24" t="s">
+      <c r="Z4" s="24" t="s">
         <v>77</v>
-      </c>
-      <c r="Z4" s="24" t="s">
-        <v>78</v>
       </c>
       <c r="AA4" s="24" t="e" vm="3">
         <v>#VALUE!</v>
@@ -16356,49 +16466,49 @@
     </row>
     <row r="5" spans="1:27" s="13" customFormat="1" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="17" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B5" s="18"/>
       <c r="C5" s="18"/>
       <c r="D5" s="18"/>
       <c r="E5" s="19" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F5" s="18"/>
       <c r="G5" s="20" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H5" s="18"/>
       <c r="I5" s="19" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="J5" s="18"/>
       <c r="K5" s="101" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="L5" s="18"/>
       <c r="M5" s="20" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="N5" s="18"/>
       <c r="P5" s="19" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q5" s="18"/>
       <c r="R5" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="T5" s="22" t="s">
         <v>84</v>
       </c>
-      <c r="T5" s="22" t="s">
+      <c r="V5" s="23" t="s">
         <v>85</v>
       </c>
-      <c r="V5" s="23" t="s">
+      <c r="X5" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="X5" s="24" t="s">
+      <c r="Z5" s="24" t="s">
         <v>87</v>
-      </c>
-      <c r="Z5" s="24" t="s">
-        <v>88</v>
       </c>
       <c r="AA5" s="24" t="e" vm="4">
         <v>#VALUE!</v>
@@ -16406,46 +16516,46 @@
     </row>
     <row r="6" spans="1:27" s="13" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A6" s="54" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B6" s="18"/>
       <c r="C6" s="12" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D6" s="18"/>
       <c r="E6" s="25" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F6" s="18"/>
       <c r="G6" s="20" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H6" s="18"/>
       <c r="I6" s="19" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J6" s="18"/>
       <c r="K6" s="21"/>
       <c r="L6" s="18"/>
       <c r="M6" s="20" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="N6" s="18"/>
       <c r="P6" s="19" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Q6" s="18"/>
       <c r="R6" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="T6" s="22" t="s">
         <v>95</v>
       </c>
-      <c r="T6" s="22" t="s">
+      <c r="X6" s="24" t="s">
         <v>96</v>
       </c>
-      <c r="X6" s="24" t="s">
+      <c r="Z6" s="24" t="s">
         <v>97</v>
-      </c>
-      <c r="Z6" s="24" t="s">
-        <v>98</v>
       </c>
       <c r="AA6" s="24" t="e" vm="5">
         <v>#VALUE!</v>
@@ -16453,11 +16563,11 @@
     </row>
     <row r="7" spans="1:27" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="17" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B7" s="18"/>
       <c r="C7" s="30" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D7" s="18"/>
       <c r="E7" s="18"/>
@@ -16465,30 +16575,30 @@
       <c r="G7" s="18"/>
       <c r="H7" s="18"/>
       <c r="I7" s="19" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="J7" s="18"/>
       <c r="K7" s="18"/>
       <c r="L7" s="18"/>
       <c r="M7" s="20" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="N7" s="18"/>
       <c r="P7" s="19" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="Q7" s="18"/>
       <c r="R7" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="T7" s="22" t="s">
         <v>103</v>
       </c>
-      <c r="T7" s="22" t="s">
+      <c r="X7" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="X7" s="24" t="s">
+      <c r="Z7" s="24" t="s">
         <v>105</v>
-      </c>
-      <c r="Z7" s="24" t="s">
-        <v>106</v>
       </c>
       <c r="AA7" s="24" t="e" vm="6">
         <v>#VALUE!</v>
@@ -16496,7 +16606,7 @@
     </row>
     <row r="8" spans="1:27" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="17" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B8" s="18"/>
       <c r="C8" s="30" t="s">
@@ -16518,16 +16628,16 @@
       </c>
       <c r="Q8" s="18"/>
       <c r="R8" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="T8" s="22" t="s">
         <v>107</v>
       </c>
-      <c r="T8" s="22" t="s">
+      <c r="X8" s="24" t="s">
         <v>108</v>
       </c>
-      <c r="X8" s="24" t="s">
+      <c r="Z8" s="24" t="s">
         <v>109</v>
-      </c>
-      <c r="Z8" s="24" t="s">
-        <v>110</v>
       </c>
       <c r="AA8" s="24" t="e" vm="7">
         <v>#VALUE!</v>
@@ -16537,7 +16647,7 @@
       <c r="B9" s="119"/>
       <c r="C9" s="119"/>
       <c r="H9" s="120" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I9" s="120"/>
       <c r="J9" s="120"/>
@@ -16545,20 +16655,20 @@
       <c r="L9" s="120"/>
       <c r="M9" s="120"/>
       <c r="P9" s="19" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Q9" s="18"/>
       <c r="R9" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="T9" s="22" t="s">
         <v>113</v>
       </c>
-      <c r="T9" s="22" t="s">
+      <c r="X9" s="24" t="s">
         <v>114</v>
       </c>
-      <c r="X9" s="24" t="s">
+      <c r="Z9" s="24" t="s">
         <v>115</v>
-      </c>
-      <c r="Z9" s="24" t="s">
-        <v>116</v>
       </c>
       <c r="AA9" s="24" t="e" vm="8">
         <v>#VALUE!</v>
@@ -16566,7 +16676,7 @@
     </row>
     <row r="10" spans="1:27" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="121" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B10" s="121"/>
       <c r="C10" s="121"/>
@@ -16575,35 +16685,35 @@
       <c r="F10" s="121"/>
       <c r="I10" s="27"/>
       <c r="J10" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="K10" s="29" t="s">
         <v>118</v>
       </c>
-      <c r="K10" s="29" t="s">
+      <c r="L10" s="29" t="s">
         <v>119</v>
       </c>
-      <c r="L10" s="29" t="s">
+      <c r="M10" s="29" t="s">
         <v>120</v>
       </c>
-      <c r="M10" s="29" t="s">
+      <c r="N10" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="P10" s="19" t="s">
         <v>121</v>
-      </c>
-      <c r="N10" s="29" t="s">
-        <v>121</v>
-      </c>
-      <c r="P10" s="19" t="s">
-        <v>122</v>
       </c>
       <c r="Q10" s="18"/>
       <c r="R10" s="19" t="s">
+        <v>122</v>
+      </c>
+      <c r="T10" s="22" t="s">
         <v>123</v>
       </c>
-      <c r="T10" s="22" t="s">
+      <c r="X10" s="24" t="s">
         <v>124</v>
       </c>
-      <c r="X10" s="24" t="s">
+      <c r="Z10" s="24" t="s">
         <v>125</v>
-      </c>
-      <c r="Z10" s="24" t="s">
-        <v>126</v>
       </c>
       <c r="AA10" s="24" t="e" vm="9">
         <v>#VALUE!</v>
@@ -16645,14 +16755,14 @@
         <v>3</v>
       </c>
       <c r="P11" s="19" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="Q11" s="18"/>
       <c r="R11" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="X11" s="24" t="s">
         <v>128</v>
-      </c>
-      <c r="X11" s="24" t="s">
-        <v>129</v>
       </c>
       <c r="Z11" s="24"/>
       <c r="AA11" s="24"/>
@@ -16662,22 +16772,22 @@
         <v>1</v>
       </c>
       <c r="B12" s="33" t="s">
+        <v>129</v>
+      </c>
+      <c r="C12" s="33" t="s">
         <v>130</v>
       </c>
-      <c r="C12" s="33" t="s">
+      <c r="D12" s="34" t="s">
         <v>131</v>
       </c>
-      <c r="D12" s="34" t="s">
+      <c r="E12" s="34" t="s">
         <v>132</v>
       </c>
-      <c r="E12" s="34" t="s">
+      <c r="F12" s="35" t="s">
         <v>133</v>
       </c>
-      <c r="F12" s="35" t="s">
+      <c r="I12" s="31" t="s">
         <v>134</v>
-      </c>
-      <c r="I12" s="31" t="s">
-        <v>135</v>
       </c>
       <c r="J12" s="36">
         <v>2</v>
@@ -16695,14 +16805,14 @@
         <v>3</v>
       </c>
       <c r="P12" s="19" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="Q12" s="18"/>
       <c r="R12" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="X12" s="24" t="s">
         <v>137</v>
-      </c>
-      <c r="X12" s="24" t="s">
-        <v>138</v>
       </c>
       <c r="Z12" s="24"/>
       <c r="AA12" s="24"/>
@@ -16712,22 +16822,22 @@
         <v>2</v>
       </c>
       <c r="B13" s="33" t="s">
+        <v>138</v>
+      </c>
+      <c r="C13" s="33" t="s">
         <v>139</v>
       </c>
-      <c r="C13" s="33" t="s">
+      <c r="D13" s="34" t="s">
         <v>140</v>
       </c>
-      <c r="D13" s="34" t="s">
+      <c r="E13" s="35" t="s">
         <v>141</v>
       </c>
-      <c r="E13" s="35" t="s">
+      <c r="F13" s="35" t="s">
         <v>142</v>
       </c>
-      <c r="F13" s="35" t="s">
+      <c r="I13" s="31" t="s">
         <v>143</v>
-      </c>
-      <c r="I13" s="31" t="s">
-        <v>144</v>
       </c>
       <c r="J13" s="37">
         <v>1</v>
@@ -16745,12 +16855,12 @@
         <v>3</v>
       </c>
       <c r="P13" s="19" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="Q13" s="18"/>
       <c r="R13" s="18"/>
       <c r="X13" s="24" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="Z13" s="24"/>
       <c r="AA13" s="24"/>
@@ -16760,22 +16870,22 @@
         <v>3</v>
       </c>
       <c r="B14" s="33" t="s">
+        <v>146</v>
+      </c>
+      <c r="C14" s="34" t="s">
         <v>147</v>
       </c>
-      <c r="C14" s="34" t="s">
+      <c r="D14" s="35" t="s">
         <v>148</v>
       </c>
-      <c r="D14" s="35" t="s">
+      <c r="E14" s="35" t="s">
         <v>149</v>
       </c>
-      <c r="E14" s="35" t="s">
+      <c r="F14" s="38" t="s">
         <v>150</v>
       </c>
-      <c r="F14" s="38" t="s">
+      <c r="I14" s="31" t="s">
         <v>151</v>
-      </c>
-      <c r="I14" s="31" t="s">
-        <v>152</v>
       </c>
       <c r="J14" s="37">
         <v>1</v>
@@ -16793,12 +16903,12 @@
         <v>3</v>
       </c>
       <c r="P14" s="19" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="Q14" s="18"/>
       <c r="R14" s="18"/>
       <c r="X14" s="24" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="Z14" s="24"/>
       <c r="AA14" s="24"/>
@@ -16808,22 +16918,22 @@
         <v>4</v>
       </c>
       <c r="B15" s="34" t="s">
+        <v>154</v>
+      </c>
+      <c r="C15" s="34" t="s">
         <v>155</v>
       </c>
-      <c r="C15" s="34" t="s">
+      <c r="D15" s="35" t="s">
         <v>156</v>
       </c>
-      <c r="D15" s="35" t="s">
+      <c r="E15" s="38" t="s">
         <v>157</v>
       </c>
-      <c r="E15" s="38" t="s">
+      <c r="F15" s="38" t="s">
         <v>158</v>
       </c>
-      <c r="F15" s="38" t="s">
+      <c r="I15" s="31" t="s">
         <v>159</v>
-      </c>
-      <c r="I15" s="31" t="s">
-        <v>160</v>
       </c>
       <c r="J15" s="37">
         <v>1</v>
@@ -16841,12 +16951,12 @@
         <v>3</v>
       </c>
       <c r="P15" s="19" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="Q15" s="18"/>
       <c r="R15" s="18"/>
       <c r="X15" s="24" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="Z15" s="24"/>
       <c r="AA15" s="24"/>
@@ -16856,22 +16966,22 @@
         <v>5</v>
       </c>
       <c r="B16" s="34" t="s">
+        <v>162</v>
+      </c>
+      <c r="C16" s="35" t="s">
         <v>163</v>
       </c>
-      <c r="C16" s="35" t="s">
+      <c r="D16" s="35" t="s">
         <v>164</v>
       </c>
-      <c r="D16" s="35" t="s">
+      <c r="E16" s="38" t="s">
         <v>165</v>
       </c>
-      <c r="E16" s="38" t="s">
+      <c r="F16" s="38" t="s">
         <v>166</v>
       </c>
-      <c r="F16" s="38" t="s">
+      <c r="I16" s="31" t="s">
         <v>167</v>
-      </c>
-      <c r="I16" s="31" t="s">
-        <v>168</v>
       </c>
       <c r="J16" s="37">
         <v>1</v>
@@ -16889,12 +16999,12 @@
         <v>3</v>
       </c>
       <c r="P16" s="19" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="Q16" s="18"/>
       <c r="R16" s="18"/>
       <c r="X16" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="Z16" s="24"/>
       <c r="AA16" s="24"/>
@@ -16906,12 +17016,12 @@
       <c r="E17" s="119"/>
       <c r="F17" s="119"/>
       <c r="P17" s="19" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Q17" s="18"/>
       <c r="R17" s="18"/>
       <c r="X17" s="24" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Z17" s="24"/>
       <c r="AA17" s="24"/>
@@ -16919,12 +17029,12 @@
     <row r="18" spans="1:27" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C18" s="39"/>
       <c r="P18" s="19" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q18" s="18"/>
       <c r="R18" s="18"/>
       <c r="X18" s="24" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Z18" s="24"/>
       <c r="AA18" s="24"/>
@@ -16932,74 +17042,74 @@
     <row r="19" spans="1:27" s="13" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C19" s="40"/>
       <c r="P19" s="19" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q19" s="18"/>
       <c r="R19" s="18"/>
       <c r="X19" s="24" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Z19" s="24"/>
       <c r="AA19" s="24"/>
     </row>
     <row r="20" spans="1:27" s="13" customFormat="1" ht="13.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="15" t="s">
+        <v>176</v>
+      </c>
+      <c r="C20" s="41" t="s">
         <v>177</v>
       </c>
-      <c r="C20" s="41" t="s">
+      <c r="E20" s="42" t="s">
         <v>178</v>
       </c>
-      <c r="E20" s="42" t="s">
+      <c r="P20" s="19" t="s">
         <v>179</v>
-      </c>
-      <c r="P20" s="19" t="s">
-        <v>180</v>
       </c>
       <c r="Q20" s="18"/>
       <c r="R20" s="18"/>
       <c r="X20" s="24" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Z20" s="24"/>
       <c r="AA20" s="24"/>
     </row>
     <row r="21" spans="1:27" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="17" t="s">
+        <v>181</v>
+      </c>
+      <c r="C21" s="43" t="s">
+        <v>24</v>
+      </c>
+      <c r="E21" s="44" t="s">
         <v>182</v>
       </c>
-      <c r="C21" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="E21" s="44" t="s">
+      <c r="H21" s="122" t="s">
+        <v>32</v>
+      </c>
+      <c r="I21" s="122" t="s">
         <v>183</v>
-      </c>
-      <c r="H21" s="122" t="s">
-        <v>33</v>
-      </c>
-      <c r="I21" s="122" t="s">
-        <v>184</v>
       </c>
       <c r="J21" s="122"/>
       <c r="K21" s="122"/>
       <c r="L21" s="122"/>
       <c r="P21" s="19" t="s">
+        <v>184</v>
+      </c>
+      <c r="X21" s="24" t="s">
         <v>185</v>
-      </c>
-      <c r="X21" s="24" t="s">
-        <v>186</v>
       </c>
       <c r="Z21" s="24"/>
       <c r="AA21" s="24"/>
     </row>
     <row r="22" spans="1:27" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="17" t="s">
+        <v>186</v>
+      </c>
+      <c r="C22" s="43" t="s">
         <v>187</v>
       </c>
-      <c r="C22" s="43" t="s">
+      <c r="E22" s="45" t="s">
         <v>188</v>
-      </c>
-      <c r="E22" s="45" t="s">
-        <v>189</v>
       </c>
       <c r="H22" s="122"/>
       <c r="I22" s="122"/>
@@ -17007,20 +17117,20 @@
       <c r="K22" s="122"/>
       <c r="L22" s="122"/>
       <c r="P22" s="19" t="s">
+        <v>189</v>
+      </c>
+      <c r="X22" s="24" t="s">
         <v>190</v>
-      </c>
-      <c r="X22" s="24" t="s">
-        <v>191</v>
       </c>
       <c r="Z22" s="24"/>
       <c r="AA22" s="24"/>
     </row>
     <row r="23" spans="1:27" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C23" s="43" t="s">
+        <v>191</v>
+      </c>
+      <c r="E23" s="44" t="s">
         <v>192</v>
-      </c>
-      <c r="E23" s="44" t="s">
-        <v>193</v>
       </c>
       <c r="H23" s="122"/>
       <c r="I23" s="46">
@@ -17036,17 +17146,17 @@
         <v>0.3</v>
       </c>
       <c r="P23" s="19" t="s">
+        <v>193</v>
+      </c>
+      <c r="X23" s="24" t="s">
         <v>194</v>
-      </c>
-      <c r="X23" s="24" t="s">
-        <v>195</v>
       </c>
       <c r="Z23" s="24"/>
       <c r="AA23" s="24"/>
     </row>
     <row r="24" spans="1:27" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="E24" s="45" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H24" s="122"/>
       <c r="I24" s="46">
@@ -17062,94 +17172,94 @@
         <v>0</v>
       </c>
       <c r="P24" s="19" t="s">
+        <v>196</v>
+      </c>
+      <c r="X24" s="24" t="s">
         <v>197</v>
-      </c>
-      <c r="X24" s="24" t="s">
-        <v>198</v>
       </c>
       <c r="Z24" s="24"/>
       <c r="AA24" s="24"/>
     </row>
     <row r="25" spans="1:27" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="E25" s="44" t="s">
+        <v>198</v>
+      </c>
+      <c r="H25" s="47" t="s">
+        <v>49</v>
+      </c>
+      <c r="I25" s="48" t="s">
         <v>199</v>
       </c>
-      <c r="H25" s="47" t="s">
-        <v>50</v>
-      </c>
-      <c r="I25" s="48" t="s">
+      <c r="J25" s="49" t="s">
         <v>200</v>
       </c>
-      <c r="J25" s="49" t="s">
+      <c r="K25" s="50" t="s">
         <v>201</v>
       </c>
-      <c r="K25" s="50" t="s">
+      <c r="L25" s="50" t="s">
+        <v>201</v>
+      </c>
+      <c r="P25" s="19" t="s">
         <v>202</v>
       </c>
-      <c r="L25" s="50" t="s">
-        <v>202</v>
-      </c>
-      <c r="P25" s="19" t="s">
+      <c r="X25" s="24" t="s">
         <v>203</v>
-      </c>
-      <c r="X25" s="24" t="s">
-        <v>204</v>
       </c>
       <c r="Z25" s="24"/>
       <c r="AA25" s="24"/>
     </row>
     <row r="26" spans="1:27" s="13" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="E26" s="45" t="s">
+        <v>204</v>
+      </c>
+      <c r="H26" s="47" t="s">
+        <v>60</v>
+      </c>
+      <c r="I26" s="48" t="s">
+        <v>199</v>
+      </c>
+      <c r="J26" s="49" t="s">
+        <v>200</v>
+      </c>
+      <c r="K26" s="50" t="s">
+        <v>201</v>
+      </c>
+      <c r="L26" s="50" t="s">
+        <v>201</v>
+      </c>
+      <c r="P26" s="19" t="s">
         <v>205</v>
       </c>
-      <c r="H26" s="47" t="s">
-        <v>61</v>
-      </c>
-      <c r="I26" s="48" t="s">
-        <v>200</v>
-      </c>
-      <c r="J26" s="49" t="s">
-        <v>201</v>
-      </c>
-      <c r="K26" s="50" t="s">
-        <v>202</v>
-      </c>
-      <c r="L26" s="50" t="s">
-        <v>202</v>
-      </c>
-      <c r="P26" s="19" t="s">
+      <c r="X26" s="24" t="s">
         <v>206</v>
-      </c>
-      <c r="X26" s="24" t="s">
-        <v>207</v>
       </c>
       <c r="Z26" s="24"/>
       <c r="AA26" s="24"/>
     </row>
     <row r="27" spans="1:27" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="E27" s="45" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H27" s="47" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I27" s="48" t="s">
+        <v>199</v>
+      </c>
+      <c r="J27" s="49" t="s">
         <v>200</v>
       </c>
-      <c r="J27" s="49" t="s">
+      <c r="K27" s="50" t="s">
         <v>201</v>
       </c>
-      <c r="K27" s="50" t="s">
-        <v>202</v>
-      </c>
       <c r="L27" s="50" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="P27" s="19" t="s">
+        <v>207</v>
+      </c>
+      <c r="X27" s="24" t="s">
         <v>208</v>
-      </c>
-      <c r="X27" s="24" t="s">
-        <v>209</v>
       </c>
       <c r="Z27" s="24"/>
       <c r="AA27" s="24"/>
@@ -17157,25 +17267,25 @@
     <row r="28" spans="1:27" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="E28" s="51"/>
       <c r="H28" s="52" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I28" s="48" t="s">
+        <v>199</v>
+      </c>
+      <c r="J28" s="49" t="s">
         <v>200</v>
       </c>
-      <c r="J28" s="49" t="s">
+      <c r="K28" s="50" t="s">
         <v>201</v>
       </c>
-      <c r="K28" s="50" t="s">
-        <v>202</v>
-      </c>
       <c r="L28" s="50" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="P28" s="19" t="s">
+        <v>209</v>
+      </c>
+      <c r="X28" s="24" t="s">
         <v>210</v>
-      </c>
-      <c r="X28" s="24" t="s">
-        <v>211</v>
       </c>
       <c r="Z28" s="24"/>
       <c r="AA28" s="24"/>
@@ -17183,86 +17293,86 @@
     <row r="29" spans="1:27" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="E29" s="51"/>
       <c r="H29" s="47" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I29" s="49" t="s">
+        <v>200</v>
+      </c>
+      <c r="J29" s="49" t="s">
+        <v>200</v>
+      </c>
+      <c r="K29" s="50" t="s">
         <v>201</v>
       </c>
-      <c r="J29" s="49" t="s">
+      <c r="L29" s="50" t="s">
         <v>201</v>
       </c>
-      <c r="K29" s="50" t="s">
-        <v>202</v>
-      </c>
-      <c r="L29" s="50" t="s">
-        <v>202</v>
-      </c>
       <c r="P29" s="19" t="s">
+        <v>211</v>
+      </c>
+      <c r="X29" s="24" t="s">
         <v>212</v>
-      </c>
-      <c r="X29" s="24" t="s">
-        <v>213</v>
       </c>
       <c r="Z29" s="24"/>
       <c r="AA29" s="24"/>
     </row>
     <row r="30" spans="1:27" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="H30" s="47" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I30" s="53" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="J30" s="53" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="K30" s="50" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="L30" s="50" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="P30" s="19"/>
     </row>
     <row r="31" spans="1:27" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="15" t="s">
+        <v>213</v>
+      </c>
+      <c r="C31" s="15" t="s">
         <v>214</v>
-      </c>
-      <c r="C31" s="15" t="s">
-        <v>215</v>
       </c>
       <c r="P31" s="19"/>
     </row>
     <row r="32" spans="1:27" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="54" t="s">
+        <v>215</v>
+      </c>
+      <c r="C32" s="55" t="s">
         <v>216</v>
-      </c>
-      <c r="C32" s="55" t="s">
-        <v>217</v>
       </c>
       <c r="P32" s="19"/>
     </row>
     <row r="33" spans="1:24" s="13" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A33" s="54" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C33" s="56" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P33" s="19"/>
     </row>
     <row r="34" spans="1:24" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="54" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C34" s="57" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P34" s="19"/>
     </row>
     <row r="35" spans="1:24" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C35" s="58" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P35" s="19"/>
     </row>
@@ -17317,37 +17427,37 @@
     </row>
     <row r="58" spans="22:24" s="13" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="V58" s="60" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="X58" s="59"/>
     </row>
     <row r="59" spans="22:24" s="13" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="V59" s="61" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="X59" s="59"/>
     </row>
     <row r="60" spans="22:24" s="13" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="V60" s="62" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="X60" s="59"/>
     </row>
     <row r="61" spans="22:24" s="13" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="V61" s="62" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="X61" s="59"/>
     </row>
     <row r="62" spans="22:24" s="13" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="V62" s="62" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="X62" s="59"/>
     </row>
     <row r="63" spans="22:24" s="13" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="V63" s="62" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="X63" s="59"/>
     </row>
@@ -17696,13 +17806,13 @@
     <mergeCell ref="I21:L22"/>
   </mergeCells>
   <conditionalFormatting sqref="I25:L30">
-    <cfRule type="cellIs" dxfId="2" priority="1" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="1" stopIfTrue="1" operator="equal">
       <formula>"NE"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="2" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="2" stopIfTrue="1" operator="equal">
       <formula>"VE"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="3" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="3" stopIfTrue="1" operator="equal">
       <formula>"CI"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/public/Risk_Template.xlsx
+++ b/public/Risk_Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\harms\Desktop\CH_FILES\Development\dms_demo_tau5\frontend\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ACF41DC-D1A5-45BB-ACD3-885DE58DACF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E156DA80-CF18-4AA1-AA20-ACD67BB2E9A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2250" yWindow="2250" windowWidth="21600" windowHeight="11835" tabRatio="683" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="683" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0. Revisions" sheetId="15" r:id="rId1"/>
@@ -26,7 +26,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'#Ref'!$A$1:$H$4657</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'0. Revisions'!$B$5:$F$104</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1. General Information'!$B$5:$AU$56</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2. Standard Information'!$B$5:$K$169</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2. Standard Information'!$B$5:$L$169</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'3. General JRA Evnts and Ctrls'!$B$5:$F$176</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'3. General Risk Register'!$B$5:$G$104</definedName>
     <definedName name="_HOC">#REF!</definedName>
@@ -34,7 +34,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="6">'#Ref'!$A$1:$H$24</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'0. Revisions'!$A$1:$G$101</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'1. General Information'!$A:$AV</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'2. Standard Information'!$A$1:$L$28</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'2. Standard Information'!$A$1:$M$28</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'3. General JRA Evnts and Ctrls'!$A$1:$G$177</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'3. General Risk Register'!$A$1:$H$104</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'4. 5x5 Matrix'!$A$1:$G$14</definedName>
@@ -72,7 +72,7 @@
     <author>Abel Moetji</author>
   </authors>
   <commentList>
-    <comment ref="AA4" authorId="0" shapeId="0" xr:uid="{F5CED637-52B0-48A0-B492-BECC1E17F4A8}">
+    <comment ref="AB4" authorId="0" shapeId="0" xr:uid="{F5CED637-52B0-48A0-B492-BECC1E17F4A8}">
       <text>
         <r>
           <rPr>
@@ -85,7 +85,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AH4" authorId="0" shapeId="0" xr:uid="{7BB9FFDC-ED76-4F27-985F-44CA5A3EA670}">
+    <comment ref="AI4" authorId="0" shapeId="0" xr:uid="{7BB9FFDC-ED76-4F27-985F-44CA5A3EA670}">
       <text>
         <r>
           <rPr>
@@ -205,7 +205,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="378">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="378">
   <si>
     <t>Abbreviation</t>
   </si>
@@ -1746,7 +1746,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="123">
+  <cellXfs count="125">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -2089,6 +2089,12 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2135,17 +2141,7 @@
     <cellStyle name="Normal 5" xfId="3" xr:uid="{151F580F-10B6-4A4F-A70C-A45C677C25FB}"/>
     <cellStyle name="Normal 9" xfId="1" xr:uid="{35A4EF1C-1C92-4220-B3BB-B271881CFCDD}"/>
   </cellStyles>
-  <dxfs count="71">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="70">
     <dxf>
       <fill>
         <patternFill>
@@ -3959,7 +3955,7 @@
       <xdr:rowOff>55245</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>36</xdr:col>
+      <xdr:col>37</xdr:col>
       <xdr:colOff>1360713</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>15240</xdr:rowOff>
@@ -4654,154 +4650,154 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E4DB93B9-9BB5-4807-B423-CDE49E544CAE}" name="Table15" displayName="Table15" ref="P1:P29" totalsRowShown="0" headerRowDxfId="70" dataDxfId="69" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E4DB93B9-9BB5-4807-B423-CDE49E544CAE}" name="Table15" displayName="Table15" ref="P1:P29" totalsRowShown="0" headerRowDxfId="69" dataDxfId="68" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
   <autoFilter ref="P1:P29" xr:uid="{E4DB93B9-9BB5-4807-B423-CDE49E544CAE}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{A4E83315-1532-4AAA-B923-2F307BFCA1CF}" name="Hazards" dataDxfId="68" dataCellStyle="Normal 2"/>
+    <tableColumn id="1" xr3:uid="{A4E83315-1532-4AAA-B923-2F307BFCA1CF}" name="Hazards" dataDxfId="67" dataCellStyle="Normal 2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{0FCA2908-9398-4E06-8D4A-AA405986137B}" name="Table6" displayName="Table6" ref="A20:A22" totalsRowShown="0" headerRowDxfId="39" dataDxfId="38" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{0FCA2908-9398-4E06-8D4A-AA405986137B}" name="Table6" displayName="Table6" ref="A20:A22" totalsRowShown="0" headerRowDxfId="38" dataDxfId="37" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
   <autoFilter ref="A20:A22" xr:uid="{0FCA2908-9398-4E06-8D4A-AA405986137B}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{356754D1-7D62-4C3B-B57A-69359BABF779}" name="Area Availability" dataDxfId="37" dataCellStyle="Normal 2"/>
+    <tableColumn id="1" xr3:uid="{356754D1-7D62-4C3B-B57A-69359BABF779}" name="Area Availability" dataDxfId="36" dataCellStyle="Normal 2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{C59949D0-7D9B-4005-8500-D07430169BBA}" name="Table7" displayName="Table7" ref="A31:A34" totalsRowShown="0" headerRowDxfId="36" dataDxfId="35" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{C59949D0-7D9B-4005-8500-D07430169BBA}" name="Table7" displayName="Table7" ref="A31:A34" totalsRowShown="0" headerRowDxfId="35" dataDxfId="34" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
   <autoFilter ref="A31:A34" xr:uid="{C59949D0-7D9B-4005-8500-D07430169BBA}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{67E618F0-E9E8-44B3-ACC9-CF52EEEE4259}" name="Control Information" dataDxfId="34" dataCellStyle="Normal 2"/>
+    <tableColumn id="1" xr3:uid="{67E618F0-E9E8-44B3-ACC9-CF52EEEE4259}" name="Control Information" dataDxfId="33" dataCellStyle="Normal 2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{13304DDB-7F05-451A-A3F7-1F8D3717FB26}" name="Table8" displayName="Table8" ref="C31:C35" totalsRowShown="0" headerRowDxfId="33" dataDxfId="32" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{13304DDB-7F05-451A-A3F7-1F8D3717FB26}" name="Table8" displayName="Table8" ref="C31:C35" totalsRowShown="0" headerRowDxfId="32" dataDxfId="31" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
   <autoFilter ref="C31:C35" xr:uid="{13304DDB-7F05-451A-A3F7-1F8D3717FB26}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{9FA7C898-B51E-48CD-92EF-C24E75422995}" name="Impact" dataDxfId="31" dataCellStyle="Normal 2"/>
+    <tableColumn id="1" xr3:uid="{9FA7C898-B51E-48CD-92EF-C24E75422995}" name="Impact" dataDxfId="30" dataCellStyle="Normal 2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{20BA4A9C-64E9-4AEF-B3E5-06080D2DFE85}" name="Table9" displayName="Table9" ref="E20:E27" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29" headerRowCellStyle="Normal 9" dataCellStyle="Normal 5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{20BA4A9C-64E9-4AEF-B3E5-06080D2DFE85}" name="Table9" displayName="Table9" ref="E20:E27" totalsRowShown="0" headerRowDxfId="29" dataDxfId="28" headerRowCellStyle="Normal 9" dataCellStyle="Normal 5">
   <autoFilter ref="E20:E27" xr:uid="{20BA4A9C-64E9-4AEF-B3E5-06080D2DFE85}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{52735A1B-A75E-4276-A8A4-3CB92E7D172D}" name="I_C" dataDxfId="28" dataCellStyle="Normal 5"/>
+    <tableColumn id="1" xr3:uid="{52735A1B-A75E-4276-A8A4-3CB92E7D172D}" name="I_C" dataDxfId="27" dataCellStyle="Normal 5"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{A2D68AEA-52A0-44F0-A125-B17009EE685F}" name="Table10" displayName="Table10" ref="C1:C3" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{A2D68AEA-52A0-44F0-A125-B17009EE685F}" name="Table10" displayName="Table10" ref="C1:C3" totalsRowShown="0" headerRowDxfId="26" dataDxfId="25" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
   <autoFilter ref="C1:C3" xr:uid="{A2D68AEA-52A0-44F0-A125-B17009EE685F}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{CA259FA7-AC99-4199-A618-8F3ABBFD9E1F}" name="YesNo" dataDxfId="25" dataCellStyle="Normal 2"/>
+    <tableColumn id="1" xr3:uid="{CA259FA7-AC99-4199-A618-8F3ABBFD9E1F}" name="YesNo" dataDxfId="24" dataCellStyle="Normal 2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{D326FF98-4466-4C63-AFAB-8AE31CC81CFF}" name="Table1" displayName="Table1" ref="T1:T10" totalsRowShown="0" headerRowDxfId="24" dataDxfId="23" headerRowCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{D326FF98-4466-4C63-AFAB-8AE31CC81CFF}" name="Table1" displayName="Table1" ref="T1:T10" totalsRowShown="0" headerRowDxfId="23" dataDxfId="22" headerRowCellStyle="Normal 2">
   <autoFilter ref="T1:T10" xr:uid="{D326FF98-4466-4C63-AFAB-8AE31CC81CFF}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{130EABA6-8BB2-4BC0-8AA8-0F2E876233A3}" name="Control Level" dataDxfId="22"/>
+    <tableColumn id="1" xr3:uid="{130EABA6-8BB2-4BC0-8AA8-0F2E876233A3}" name="Control Level" dataDxfId="21"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{89FED767-CB12-44E0-AD37-C4C058411E3B}" name="Table16" displayName="Table16" ref="R1:R12" totalsRowShown="0" headerRowDxfId="67" dataDxfId="66" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{89FED767-CB12-44E0-AD37-C4C058411E3B}" name="Table16" displayName="Table16" ref="R1:R12" totalsRowShown="0" headerRowDxfId="66" dataDxfId="65" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
   <autoFilter ref="R1:R12" xr:uid="{89FED767-CB12-44E0-AD37-C4C058411E3B}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{3E7C20E1-0083-4FA6-B8CD-F18BCFC29C0C}" name="Functions" dataDxfId="65" dataCellStyle="Normal 2"/>
+    <tableColumn id="1" xr3:uid="{3E7C20E1-0083-4FA6-B8CD-F18BCFC29C0C}" name="Functions" dataDxfId="64" dataCellStyle="Normal 2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{33461173-53BB-4469-B43B-C30157FF6B61}" name="Table17" displayName="Table17" ref="E1:E6" totalsRowShown="0" headerRowDxfId="64" dataDxfId="63" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{33461173-53BB-4469-B43B-C30157FF6B61}" name="Table17" displayName="Table17" ref="E1:E6" totalsRowShown="0" headerRowDxfId="63" dataDxfId="62" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
   <autoFilter ref="E1:E6" xr:uid="{33461173-53BB-4469-B43B-C30157FF6B61}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{FABE7ED9-6B7C-44E0-AD4D-8D1323A4E4F6}" name="Likelihood" dataDxfId="62" dataCellStyle="Normal 2"/>
+    <tableColumn id="1" xr3:uid="{FABE7ED9-6B7C-44E0-AD4D-8D1323A4E4F6}" name="Likelihood" dataDxfId="61" dataCellStyle="Normal 2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{8550E780-9FBF-45EB-9022-1895A1AF2ED0}" name="Table18" displayName="Table18" ref="G1:G6" totalsRowShown="0" headerRowDxfId="61" dataDxfId="60" headerRowCellStyle="Normal 2" dataCellStyle="Normal 9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{8550E780-9FBF-45EB-9022-1895A1AF2ED0}" name="Table18" displayName="Table18" ref="G1:G6" totalsRowShown="0" headerRowDxfId="60" dataDxfId="59" headerRowCellStyle="Normal 2" dataCellStyle="Normal 9">
   <autoFilter ref="G1:G6" xr:uid="{8550E780-9FBF-45EB-9022-1895A1AF2ED0}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{2299BFF3-AB2F-4B7A-95F8-98325172D078}" name="Consequence" dataDxfId="59" dataCellStyle="Normal 9"/>
+    <tableColumn id="1" xr3:uid="{2299BFF3-AB2F-4B7A-95F8-98325172D078}" name="Consequence" dataDxfId="58" dataCellStyle="Normal 9"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{D764ED73-5559-4234-BD02-EB4696632F02}" name="Table23" displayName="Table23" ref="B12:F16" totalsRowShown="0" headerRowDxfId="58" dataDxfId="57">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{D764ED73-5559-4234-BD02-EB4696632F02}" name="Table23" displayName="Table23" ref="B12:F16" totalsRowShown="0" headerRowDxfId="57" dataDxfId="56">
   <autoFilter ref="B12:F16" xr:uid="{D764ED73-5559-4234-BD02-EB4696632F02}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{C7665F04-656B-4655-BD2E-06B67D38E17F}" name="1 (L)" dataDxfId="56"/>
-    <tableColumn id="2" xr3:uid="{76ABF063-4E24-4CFA-86B9-0DC19CF24BBC}" name="3 (L)" dataDxfId="55"/>
-    <tableColumn id="3" xr3:uid="{D10437F8-ACDB-4874-8C10-6908FD164343}" name="6 (M)" dataDxfId="54" dataCellStyle="Normal 2"/>
-    <tableColumn id="4" xr3:uid="{2F00B1EC-703D-47C1-8612-94C91C8E9BC2}" name="10 (M)" dataDxfId="53"/>
-    <tableColumn id="5" xr3:uid="{C475F2A3-C677-435D-9202-AD792BCFE835}" name="15 (S)" dataDxfId="52" dataCellStyle="Normal 2"/>
+    <tableColumn id="1" xr3:uid="{C7665F04-656B-4655-BD2E-06B67D38E17F}" name="1 (L)" dataDxfId="55"/>
+    <tableColumn id="2" xr3:uid="{76ABF063-4E24-4CFA-86B9-0DC19CF24BBC}" name="3 (L)" dataDxfId="54"/>
+    <tableColumn id="3" xr3:uid="{D10437F8-ACDB-4874-8C10-6908FD164343}" name="6 (M)" dataDxfId="53" dataCellStyle="Normal 2"/>
+    <tableColumn id="4" xr3:uid="{2F00B1EC-703D-47C1-8612-94C91C8E9BC2}" name="10 (M)" dataDxfId="52"/>
+    <tableColumn id="5" xr3:uid="{C475F2A3-C677-435D-9202-AD792BCFE835}" name="15 (S)" dataDxfId="51" dataCellStyle="Normal 2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{35CE8A27-FB09-4D6F-BFEF-53A495779208}" name="Table24" displayName="Table24" ref="I1:I7" totalsRowShown="0" headerRowDxfId="51" dataDxfId="50" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{35CE8A27-FB09-4D6F-BFEF-53A495779208}" name="Table24" displayName="Table24" ref="I1:I7" totalsRowShown="0" headerRowDxfId="50" dataDxfId="49" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
   <autoFilter ref="I1:I7" xr:uid="{35CE8A27-FB09-4D6F-BFEF-53A495779208}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{67A595D5-4B09-40D8-AF0A-30E7CB998DB1}" name="Control Type" dataDxfId="49" dataCellStyle="Normal 2"/>
+    <tableColumn id="1" xr3:uid="{67A595D5-4B09-40D8-AF0A-30E7CB998DB1}" name="Control Type" dataDxfId="48" dataCellStyle="Normal 2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{3C4E97BF-F9BA-47B6-8E06-E99D4DB8A8A1}" name="Table25" displayName="Table25" ref="K1:K5" totalsRowShown="0" headerRowDxfId="48" dataDxfId="47" headerRowCellStyle="Normal 2" dataCellStyle="Normal 9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{3C4E97BF-F9BA-47B6-8E06-E99D4DB8A8A1}" name="Table25" displayName="Table25" ref="K1:K5" totalsRowShown="0" headerRowDxfId="47" dataDxfId="46" headerRowCellStyle="Normal 2" dataCellStyle="Normal 9">
   <autoFilter ref="K1:K5" xr:uid="{3C4E97BF-F9BA-47B6-8E06-E99D4DB8A8A1}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{28CA88D8-332A-4CFD-8883-2D8BDB97106E}" name="Control Quality" dataDxfId="46" dataCellStyle="Normal 9"/>
+    <tableColumn id="1" xr3:uid="{28CA88D8-332A-4CFD-8883-2D8BDB97106E}" name="Control Quality" dataDxfId="45" dataCellStyle="Normal 9"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{3025DD08-08F4-4688-ACCB-86792B0FD2C5}" name="Table2" displayName="Table2" ref="A1:A8" totalsRowShown="0" headerRowDxfId="45" dataDxfId="44" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{3025DD08-08F4-4688-ACCB-86792B0FD2C5}" name="Table2" displayName="Table2" ref="A1:A8" totalsRowShown="0" headerRowDxfId="44" dataDxfId="43" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
   <autoFilter ref="A1:A8" xr:uid="{3025DD08-08F4-4688-ACCB-86792B0FD2C5}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{74B604CB-6600-40E4-BC6B-168E69749558}" name="Consequence_x000a_Type" dataDxfId="43" dataCellStyle="Normal 2"/>
+    <tableColumn id="1" xr3:uid="{74B604CB-6600-40E4-BC6B-168E69749558}" name="Consequence_x000a_Type" dataDxfId="42" dataCellStyle="Normal 2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{72A36D82-7F17-4619-896F-7F0787B6574E}" name="Table4" displayName="Table4" ref="C20:C23" totalsRowShown="0" headerRowDxfId="42" dataDxfId="41">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{72A36D82-7F17-4619-896F-7F0787B6574E}" name="Table4" displayName="Table4" ref="C20:C23" totalsRowShown="0" headerRowDxfId="41" dataDxfId="40">
   <autoFilter ref="C20:C23" xr:uid="{72A36D82-7F17-4619-896F-7F0787B6574E}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{A6FFA3B8-0CD1-4148-8182-FF1AF41B244D}" name="Control_Detail" dataDxfId="40"/>
+    <tableColumn id="1" xr3:uid="{A6FFA3B8-0CD1-4148-8182-FF1AF41B244D}" name="Control_Detail" dataDxfId="39"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5096,10 +5092,10 @@
     </row>
     <row r="2" spans="2:6" ht="53.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="6"/>
-      <c r="C2" s="110"/>
-      <c r="D2" s="110"/>
-      <c r="E2" s="111"/>
-      <c r="F2" s="110"/>
+      <c r="C2" s="112"/>
+      <c r="D2" s="112"/>
+      <c r="E2" s="113"/>
+      <c r="F2" s="112"/>
     </row>
     <row r="3" spans="2:6" ht="9.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="6"/>
@@ -5109,13 +5105,13 @@
       <c r="F3" s="1"/>
     </row>
     <row r="4" spans="2:6" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="112" t="s">
+      <c r="B4" s="114" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="113"/>
-      <c r="D4" s="113"/>
-      <c r="E4" s="114"/>
-      <c r="F4" s="113"/>
+      <c r="C4" s="115"/>
+      <c r="D4" s="115"/>
+      <c r="E4" s="116"/>
+      <c r="F4" s="115"/>
     </row>
     <row r="5" spans="2:6" ht="19.350000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="77" t="s">
@@ -5920,18 +5916,18 @@
       <c r="AU3" s="6"/>
     </row>
     <row r="4" spans="2:47" s="1" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="115" t="s">
+      <c r="B4" s="117" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="115"/>
-      <c r="D4" s="115"/>
-      <c r="E4" s="115"/>
-      <c r="G4" s="115" t="s">
+      <c r="C4" s="117"/>
+      <c r="D4" s="117"/>
+      <c r="E4" s="117"/>
+      <c r="G4" s="117" t="s">
         <v>370</v>
       </c>
-      <c r="H4" s="115"/>
-      <c r="I4" s="115"/>
-      <c r="J4" s="115"/>
+      <c r="H4" s="117"/>
+      <c r="I4" s="117"/>
+      <c r="J4" s="117"/>
       <c r="L4" s="67" t="s">
         <v>2</v>
       </c>
@@ -5963,24 +5959,24 @@
       <c r="AG4" s="67"/>
       <c r="AH4" s="67"/>
       <c r="AI4" s="67"/>
-      <c r="AJ4" s="115" t="s">
+      <c r="AJ4" s="117" t="s">
         <v>264</v>
       </c>
-      <c r="AK4" s="115"/>
+      <c r="AK4" s="117"/>
       <c r="AL4" s="9"/>
-      <c r="AM4" s="115" t="s">
+      <c r="AM4" s="117" t="s">
         <v>343</v>
       </c>
-      <c r="AN4" s="115"/>
-      <c r="AP4" s="116" t="s">
+      <c r="AN4" s="117"/>
+      <c r="AP4" s="118" t="s">
         <v>220</v>
       </c>
-      <c r="AQ4" s="115"/>
-      <c r="AR4" s="115"/>
-      <c r="AT4" s="112" t="s">
+      <c r="AQ4" s="117"/>
+      <c r="AR4" s="117"/>
+      <c r="AT4" s="114" t="s">
         <v>373</v>
       </c>
-      <c r="AU4" s="112"/>
+      <c r="AU4" s="114"/>
     </row>
     <row r="5" spans="2:47" s="84" customFormat="1" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="68" t="s">
@@ -10184,55 +10180,55 @@
     <mergeCell ref="AJ4:AK4"/>
   </mergeCells>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="21" priority="251"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="251"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H6:H102">
-    <cfRule type="duplicateValues" dxfId="20" priority="387"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="387"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H27 H21:H24 H16:H17 H1:H11 H35:H1048576">
-    <cfRule type="duplicateValues" dxfId="19" priority="293"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="293"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M1:M1048576">
-    <cfRule type="duplicateValues" dxfId="18" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q1:Q24 Q26:Q34 Q36:Q1048576">
-    <cfRule type="duplicateValues" dxfId="17" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q25">
-    <cfRule type="duplicateValues" dxfId="16" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q35">
-    <cfRule type="duplicateValues" dxfId="15" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="U34:U36">
-    <cfRule type="duplicateValues" dxfId="14" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="U41">
-    <cfRule type="duplicateValues" dxfId="13" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="U57:U1048576 U37:U40 U1:U33 U42:U55">
-    <cfRule type="duplicateValues" dxfId="12" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y1:Y15 Y17:Y1048576 AC16">
-    <cfRule type="duplicateValues" dxfId="11" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC17:AC1048576 AC1:AC15">
-    <cfRule type="duplicateValues" dxfId="10" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="15"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AG1:AH1048576">
+    <cfRule type="duplicateValues" dxfId="8" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AK1:AK1048576">
-    <cfRule type="duplicateValues" dxfId="8" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AN1:AN1048576">
-    <cfRule type="duplicateValues" dxfId="7" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AQ6:AQ102">
-    <cfRule type="duplicateValues" dxfId="6" priority="426"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="426"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AR1:AR1048576">
-    <cfRule type="duplicateValues" dxfId="5" priority="10"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AG1:AH1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="10"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -10262,3161 +10258,3333 @@
     <tabColor rgb="FF002060"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:AK169"/>
+  <dimension ref="B1:AL169"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.25" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="1.140625" style="1" customWidth="1"/>
     <col min="2" max="2" width="5.85546875" style="8" customWidth="1"/>
-    <col min="3" max="3" width="31.140625" style="9" customWidth="1"/>
-    <col min="4" max="4" width="57.42578125" style="9" customWidth="1"/>
-    <col min="5" max="5" width="31.85546875" style="9" customWidth="1"/>
-    <col min="6" max="6" width="8.5703125" style="9" customWidth="1"/>
-    <col min="7" max="7" width="13.28515625" style="10" customWidth="1"/>
-    <col min="8" max="8" width="21.42578125" style="10" customWidth="1"/>
-    <col min="9" max="9" width="15.42578125" style="9" customWidth="1"/>
-    <col min="10" max="10" width="11.7109375" style="9" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" style="9" customWidth="1"/>
-    <col min="12" max="12" width="2.42578125" style="1" customWidth="1"/>
-    <col min="13" max="13" width="3.85546875" style="1" customWidth="1"/>
-    <col min="14" max="14" width="11.140625" style="1" customWidth="1"/>
-    <col min="15" max="15" width="61.5703125" style="1" customWidth="1"/>
-    <col min="16" max="16" width="8.85546875" style="1"/>
-    <col min="17" max="17" width="2.42578125" style="1" customWidth="1"/>
-    <col min="18" max="18" width="3.85546875" style="1" customWidth="1"/>
-    <col min="19" max="19" width="8.85546875" style="1"/>
-    <col min="20" max="20" width="61.5703125" style="1" customWidth="1"/>
-    <col min="21" max="21" width="8.85546875" style="1"/>
-    <col min="22" max="22" width="2.42578125" style="1" customWidth="1"/>
-    <col min="23" max="23" width="4.140625" style="1" customWidth="1"/>
-    <col min="24" max="24" width="34.28515625" style="1" customWidth="1"/>
-    <col min="25" max="25" width="8.85546875" style="1" customWidth="1"/>
-    <col min="26" max="26" width="2.42578125" style="1" customWidth="1"/>
-    <col min="27" max="32" width="31.140625" style="1" customWidth="1"/>
-    <col min="33" max="33" width="2.42578125" style="1" customWidth="1"/>
-    <col min="34" max="34" width="12.140625" style="1" customWidth="1"/>
-    <col min="35" max="37" width="20" style="1" customWidth="1"/>
-    <col min="38" max="16384" width="8.85546875" style="1"/>
+    <col min="3" max="3" width="11.28515625" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="31.140625" style="9" customWidth="1"/>
+    <col min="5" max="5" width="57.42578125" style="9" customWidth="1"/>
+    <col min="6" max="6" width="31.85546875" style="9" customWidth="1"/>
+    <col min="7" max="7" width="8.5703125" style="9" customWidth="1"/>
+    <col min="8" max="8" width="13.28515625" style="10" customWidth="1"/>
+    <col min="9" max="9" width="21.42578125" style="10" customWidth="1"/>
+    <col min="10" max="10" width="15.42578125" style="9" customWidth="1"/>
+    <col min="11" max="11" width="11.7109375" style="9" customWidth="1"/>
+    <col min="12" max="12" width="14.28515625" style="9" customWidth="1"/>
+    <col min="13" max="13" width="2.42578125" style="1" customWidth="1"/>
+    <col min="14" max="14" width="3.85546875" style="1" customWidth="1"/>
+    <col min="15" max="15" width="11.140625" style="1" customWidth="1"/>
+    <col min="16" max="16" width="61.5703125" style="1" customWidth="1"/>
+    <col min="17" max="17" width="8.85546875" style="1"/>
+    <col min="18" max="18" width="2.42578125" style="1" customWidth="1"/>
+    <col min="19" max="19" width="3.85546875" style="1" customWidth="1"/>
+    <col min="20" max="20" width="8.85546875" style="1"/>
+    <col min="21" max="21" width="61.5703125" style="1" customWidth="1"/>
+    <col min="22" max="22" width="8.85546875" style="1"/>
+    <col min="23" max="23" width="2.42578125" style="1" customWidth="1"/>
+    <col min="24" max="24" width="4.140625" style="1" customWidth="1"/>
+    <col min="25" max="25" width="34.28515625" style="1" customWidth="1"/>
+    <col min="26" max="26" width="8.85546875" style="1" customWidth="1"/>
+    <col min="27" max="27" width="2.42578125" style="1" customWidth="1"/>
+    <col min="28" max="33" width="31.140625" style="1" customWidth="1"/>
+    <col min="34" max="34" width="2.42578125" style="1" customWidth="1"/>
+    <col min="35" max="35" width="12.140625" style="1" customWidth="1"/>
+    <col min="36" max="38" width="20" style="1" customWidth="1"/>
+    <col min="39" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:37" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:38" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1" s="6"/>
-      <c r="C1" s="2"/>
+      <c r="C1" s="6"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
-      <c r="G1" s="4"/>
+      <c r="G1" s="2"/>
       <c r="H1" s="4"/>
-      <c r="I1" s="2"/>
+      <c r="I1" s="4"/>
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
-    </row>
-    <row r="2" spans="2:37" ht="53.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L1" s="2"/>
+    </row>
+    <row r="2" spans="2:38" ht="53.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="6"/>
-      <c r="C2" s="110"/>
-      <c r="D2" s="110"/>
-      <c r="E2" s="110"/>
-      <c r="F2" s="110"/>
-      <c r="G2" s="111"/>
-      <c r="H2" s="111"/>
-      <c r="I2" s="110"/>
-      <c r="J2" s="65"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="112"/>
+      <c r="E2" s="112"/>
+      <c r="F2" s="112"/>
+      <c r="G2" s="112"/>
+      <c r="H2" s="113"/>
+      <c r="I2" s="113"/>
+      <c r="J2" s="112"/>
       <c r="K2" s="65"/>
-    </row>
-    <row r="3" spans="2:37" ht="9.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L2" s="65"/>
+    </row>
+    <row r="3" spans="2:38" ht="9.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="6"/>
-      <c r="C3" s="1"/>
+      <c r="C3" s="6"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
-      <c r="G3" s="5"/>
+      <c r="G3" s="1"/>
       <c r="H3" s="5"/>
-      <c r="I3" s="1"/>
+      <c r="I3" s="5"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
-    </row>
-    <row r="4" spans="2:37" ht="13.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="112" t="s">
+      <c r="L3" s="1"/>
+    </row>
+    <row r="4" spans="2:38" ht="13.7" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="114" t="s">
         <v>369</v>
       </c>
-      <c r="C4" s="112"/>
-      <c r="D4" s="112"/>
-      <c r="E4" s="112"/>
-      <c r="F4" s="112"/>
-      <c r="G4" s="112"/>
-      <c r="H4" s="112"/>
-      <c r="I4" s="112"/>
-      <c r="J4" s="112"/>
-      <c r="K4" s="112"/>
-      <c r="M4" s="113" t="s">
+      <c r="C4" s="114"/>
+      <c r="D4" s="114"/>
+      <c r="E4" s="114"/>
+      <c r="F4" s="114"/>
+      <c r="G4" s="114"/>
+      <c r="H4" s="114"/>
+      <c r="I4" s="114"/>
+      <c r="J4" s="114"/>
+      <c r="K4" s="114"/>
+      <c r="L4" s="114"/>
+      <c r="N4" s="115" t="s">
         <v>347</v>
       </c>
-      <c r="N4" s="113"/>
-      <c r="O4" s="113"/>
-      <c r="P4" s="113"/>
-      <c r="R4" s="113" t="s">
+      <c r="O4" s="115"/>
+      <c r="P4" s="115"/>
+      <c r="Q4" s="115"/>
+      <c r="S4" s="115" t="s">
         <v>265</v>
       </c>
-      <c r="S4" s="113"/>
-      <c r="T4" s="113"/>
-      <c r="U4" s="113"/>
-      <c r="W4" s="113" t="s">
+      <c r="T4" s="115"/>
+      <c r="U4" s="115"/>
+      <c r="V4" s="115"/>
+      <c r="X4" s="115" t="s">
         <v>375</v>
       </c>
-      <c r="X4" s="113"/>
-      <c r="Y4" s="113"/>
-      <c r="AA4" s="113" t="s">
+      <c r="Y4" s="115"/>
+      <c r="Z4" s="115"/>
+      <c r="AB4" s="115" t="s">
         <v>266</v>
       </c>
-      <c r="AB4" s="113"/>
-      <c r="AC4" s="113"/>
-      <c r="AD4" s="113"/>
-      <c r="AE4" s="113"/>
-      <c r="AF4" s="113"/>
-      <c r="AH4" s="113" t="s">
+      <c r="AC4" s="115"/>
+      <c r="AD4" s="115"/>
+      <c r="AE4" s="115"/>
+      <c r="AF4" s="115"/>
+      <c r="AG4" s="115"/>
+      <c r="AI4" s="115" t="s">
         <v>314</v>
       </c>
-      <c r="AI4" s="113"/>
-      <c r="AJ4" s="113"/>
-      <c r="AK4" s="113"/>
-    </row>
-    <row r="5" spans="2:37" ht="36" x14ac:dyDescent="0.25">
+      <c r="AJ4" s="115"/>
+      <c r="AK4" s="115"/>
+      <c r="AL4" s="115"/>
+    </row>
+    <row r="5" spans="2:38" ht="36" x14ac:dyDescent="0.25">
       <c r="B5" s="77" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="78" t="s">
+      <c r="C5" s="77" t="s">
+        <v>374</v>
+      </c>
+      <c r="D5" s="78" t="s">
         <v>348</v>
       </c>
-      <c r="D5" s="103" t="s">
+      <c r="E5" s="103" t="s">
         <v>367</v>
       </c>
-      <c r="E5" s="103" t="s">
+      <c r="F5" s="103" t="s">
         <v>357</v>
       </c>
-      <c r="F5" s="78" t="s">
+      <c r="G5" s="78" t="s">
         <v>25</v>
       </c>
-      <c r="G5" s="79" t="s">
+      <c r="H5" s="79" t="s">
         <v>30</v>
       </c>
-      <c r="H5" s="79" t="s">
+      <c r="I5" s="79" t="s">
         <v>31</v>
       </c>
-      <c r="I5" s="78" t="s">
+      <c r="J5" s="78" t="s">
         <v>32</v>
       </c>
-      <c r="J5" s="78" t="s">
+      <c r="K5" s="78" t="s">
         <v>38</v>
       </c>
-      <c r="K5" s="97" t="s">
+      <c r="L5" s="97" t="s">
         <v>346</v>
       </c>
-      <c r="M5" s="78" t="s">
+      <c r="N5" s="78" t="s">
         <v>9</v>
       </c>
-      <c r="N5" s="78" t="s">
+      <c r="O5" s="78" t="s">
         <v>13</v>
       </c>
-      <c r="O5" s="78" t="s">
+      <c r="P5" s="78" t="s">
         <v>1</v>
       </c>
-      <c r="P5" s="78" t="s">
+      <c r="Q5" s="78" t="s">
         <v>17</v>
       </c>
-      <c r="R5" s="78" t="s">
+      <c r="S5" s="78" t="s">
         <v>9</v>
       </c>
-      <c r="S5" s="78" t="s">
+      <c r="T5" s="78" t="s">
         <v>13</v>
       </c>
-      <c r="T5" s="78" t="s">
+      <c r="U5" s="78" t="s">
         <v>1</v>
       </c>
-      <c r="U5" s="78" t="s">
+      <c r="V5" s="78" t="s">
         <v>17</v>
       </c>
-      <c r="W5" s="78" t="s">
+      <c r="X5" s="78" t="s">
         <v>9</v>
       </c>
-      <c r="X5" s="78" t="s">
+      <c r="Y5" s="78" t="s">
         <v>5</v>
       </c>
-      <c r="Y5" s="78" t="s">
+      <c r="Z5" s="78" t="s">
         <v>17</v>
       </c>
-      <c r="AA5" s="78" t="s">
+      <c r="AB5" s="78" t="s">
         <v>267</v>
       </c>
-      <c r="AB5" s="78" t="s">
+      <c r="AC5" s="78" t="s">
         <v>341</v>
       </c>
-      <c r="AC5" s="78" t="s">
+      <c r="AD5" s="78" t="s">
         <v>340</v>
       </c>
-      <c r="AD5" s="78" t="s">
+      <c r="AE5" s="78" t="s">
         <v>339</v>
       </c>
-      <c r="AE5" s="78" t="s">
+      <c r="AF5" s="78" t="s">
         <v>79</v>
       </c>
-      <c r="AF5" s="78" t="s">
+      <c r="AG5" s="78" t="s">
         <v>342</v>
       </c>
-      <c r="AH5" s="78" t="s">
+      <c r="AI5" s="78" t="s">
         <v>315</v>
       </c>
-      <c r="AI5" s="78" t="s">
+      <c r="AJ5" s="78" t="s">
         <v>1</v>
       </c>
-      <c r="AJ5" s="78" t="s">
+      <c r="AK5" s="78" t="s">
         <v>316</v>
       </c>
-      <c r="AK5" s="78" t="s">
+      <c r="AL5" s="78" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="6" spans="2:37" ht="24" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:38" ht="24" x14ac:dyDescent="0.25">
       <c r="B6" s="86"/>
-      <c r="C6" s="81"/>
+      <c r="C6" s="86"/>
       <c r="D6" s="81"/>
       <c r="E6" s="81"/>
       <c r="F6" s="81"/>
-      <c r="G6" s="82"/>
+      <c r="G6" s="81"/>
       <c r="H6" s="82"/>
-      <c r="I6" s="81"/>
-      <c r="J6" s="108"/>
-      <c r="K6" s="81"/>
-      <c r="M6" s="83"/>
-      <c r="N6" s="81"/>
+      <c r="I6" s="82"/>
+      <c r="J6" s="81"/>
+      <c r="K6" s="108"/>
+      <c r="L6" s="81"/>
+      <c r="N6" s="83"/>
       <c r="O6" s="81"/>
       <c r="P6" s="81"/>
-      <c r="R6" s="83"/>
-      <c r="S6" s="81"/>
+      <c r="Q6" s="81"/>
+      <c r="S6" s="83"/>
       <c r="T6" s="81"/>
       <c r="U6" s="81"/>
-      <c r="W6" s="83"/>
-      <c r="X6" s="81"/>
+      <c r="V6" s="81"/>
+      <c r="X6" s="83"/>
       <c r="Y6" s="81"/>
-      <c r="AA6" s="87" t="s">
+      <c r="Z6" s="81"/>
+      <c r="AB6" s="87" t="s">
         <v>307</v>
       </c>
-      <c r="AB6" s="81" t="s">
+      <c r="AC6" s="81" t="s">
         <v>272</v>
       </c>
-      <c r="AC6" s="81" t="s">
+      <c r="AD6" s="81" t="s">
         <v>273</v>
       </c>
-      <c r="AD6" s="81" t="s">
+      <c r="AE6" s="81" t="s">
         <v>274</v>
       </c>
-      <c r="AE6" s="81" t="s">
+      <c r="AF6" s="81" t="s">
         <v>275</v>
       </c>
-      <c r="AF6" s="81" t="s">
+      <c r="AG6" s="81" t="s">
         <v>276</v>
       </c>
-      <c r="AH6" s="81" t="s">
+      <c r="AI6" s="81" t="s">
         <v>317</v>
       </c>
-      <c r="AI6" s="81" t="s">
+      <c r="AJ6" s="81" t="s">
         <v>322</v>
       </c>
-      <c r="AJ6" s="81" t="s">
+      <c r="AK6" s="81" t="s">
         <v>327</v>
       </c>
-      <c r="AK6" s="81" t="s">
+      <c r="AL6" s="81" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="7" spans="2:37" ht="60" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:38" ht="60" x14ac:dyDescent="0.25">
       <c r="B7" s="86"/>
-      <c r="C7" s="81"/>
+      <c r="C7" s="86"/>
       <c r="D7" s="81"/>
       <c r="E7" s="81"/>
       <c r="F7" s="81"/>
-      <c r="G7" s="82"/>
+      <c r="G7" s="81"/>
       <c r="H7" s="82"/>
-      <c r="I7" s="81"/>
-      <c r="J7" s="108"/>
-      <c r="K7" s="81"/>
-      <c r="M7" s="83"/>
-      <c r="N7" s="81"/>
+      <c r="I7" s="82"/>
+      <c r="J7" s="81"/>
+      <c r="K7" s="108"/>
+      <c r="L7" s="81"/>
+      <c r="N7" s="83"/>
       <c r="O7" s="81"/>
       <c r="P7" s="81"/>
-      <c r="R7" s="83"/>
-      <c r="S7" s="81"/>
+      <c r="Q7" s="81"/>
+      <c r="S7" s="83"/>
       <c r="T7" s="81"/>
       <c r="U7" s="81"/>
-      <c r="W7" s="83"/>
-      <c r="X7" s="81"/>
+      <c r="V7" s="81"/>
+      <c r="X7" s="83"/>
       <c r="Y7" s="81"/>
-      <c r="AA7" s="87" t="s">
+      <c r="Z7" s="81"/>
+      <c r="AB7" s="87" t="s">
         <v>308</v>
       </c>
-      <c r="AB7" s="81" t="s">
+      <c r="AC7" s="81" t="s">
         <v>277</v>
       </c>
-      <c r="AC7" s="81" t="s">
+      <c r="AD7" s="81" t="s">
         <v>278</v>
       </c>
-      <c r="AD7" s="81" t="s">
+      <c r="AE7" s="81" t="s">
         <v>279</v>
       </c>
-      <c r="AE7" s="81" t="s">
+      <c r="AF7" s="81" t="s">
         <v>280</v>
       </c>
-      <c r="AF7" s="81" t="s">
+      <c r="AG7" s="81" t="s">
         <v>281</v>
       </c>
-      <c r="AH7" s="81" t="s">
+      <c r="AI7" s="81" t="s">
         <v>318</v>
       </c>
-      <c r="AI7" s="81" t="s">
+      <c r="AJ7" s="81" t="s">
         <v>323</v>
       </c>
-      <c r="AJ7" s="81" t="s">
+      <c r="AK7" s="81" t="s">
         <v>327</v>
       </c>
-      <c r="AK7" s="81" t="s">
+      <c r="AL7" s="81" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="8" spans="2:37" ht="48" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:38" ht="48" x14ac:dyDescent="0.25">
       <c r="B8" s="86"/>
-      <c r="C8" s="108"/>
-      <c r="D8" s="81"/>
+      <c r="C8" s="86"/>
+      <c r="D8" s="108"/>
       <c r="E8" s="81"/>
       <c r="F8" s="81"/>
-      <c r="G8" s="82"/>
+      <c r="G8" s="81"/>
       <c r="H8" s="82"/>
-      <c r="I8" s="81"/>
-      <c r="J8" s="108"/>
-      <c r="K8" s="81"/>
-      <c r="M8" s="83"/>
-      <c r="N8" s="81"/>
+      <c r="I8" s="82"/>
+      <c r="J8" s="81"/>
+      <c r="K8" s="108"/>
+      <c r="L8" s="81"/>
+      <c r="N8" s="83"/>
       <c r="O8" s="81"/>
       <c r="P8" s="81"/>
-      <c r="R8" s="83"/>
-      <c r="S8" s="81"/>
+      <c r="Q8" s="81"/>
+      <c r="S8" s="83"/>
       <c r="T8" s="81"/>
       <c r="U8" s="81"/>
-      <c r="W8" s="83"/>
-      <c r="X8" s="81"/>
+      <c r="V8" s="81"/>
+      <c r="X8" s="83"/>
       <c r="Y8" s="81"/>
-      <c r="AA8" s="87" t="s">
+      <c r="Z8" s="81"/>
+      <c r="AB8" s="87" t="s">
         <v>309</v>
       </c>
-      <c r="AB8" s="81" t="s">
+      <c r="AC8" s="81" t="s">
         <v>282</v>
       </c>
-      <c r="AC8" s="81" t="s">
+      <c r="AD8" s="81" t="s">
         <v>283</v>
       </c>
-      <c r="AD8" s="81" t="s">
+      <c r="AE8" s="81" t="s">
         <v>284</v>
       </c>
-      <c r="AE8" s="81" t="s">
+      <c r="AF8" s="81" t="s">
         <v>285</v>
       </c>
-      <c r="AF8" s="81" t="s">
+      <c r="AG8" s="81" t="s">
         <v>286</v>
       </c>
-      <c r="AH8" s="81" t="s">
+      <c r="AI8" s="81" t="s">
         <v>319</v>
       </c>
-      <c r="AI8" s="81" t="s">
+      <c r="AJ8" s="81" t="s">
         <v>324</v>
       </c>
-      <c r="AJ8" s="81" t="s">
+      <c r="AK8" s="81" t="s">
         <v>327</v>
       </c>
-      <c r="AK8" s="81" t="s">
+      <c r="AL8" s="81" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="9" spans="2:37" ht="48" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:38" ht="48" x14ac:dyDescent="0.25">
       <c r="B9" s="86"/>
-      <c r="C9" s="81"/>
+      <c r="C9" s="86"/>
       <c r="D9" s="81"/>
       <c r="E9" s="81"/>
       <c r="F9" s="81"/>
-      <c r="G9" s="82"/>
+      <c r="G9" s="81"/>
       <c r="H9" s="82"/>
-      <c r="I9" s="81"/>
-      <c r="J9" s="108"/>
-      <c r="K9" s="81"/>
-      <c r="M9" s="83"/>
-      <c r="N9" s="81"/>
+      <c r="I9" s="82"/>
+      <c r="J9" s="81"/>
+      <c r="K9" s="108"/>
+      <c r="L9" s="81"/>
+      <c r="N9" s="83"/>
       <c r="O9" s="81"/>
       <c r="P9" s="81"/>
-      <c r="R9" s="83"/>
-      <c r="S9" s="81"/>
+      <c r="Q9" s="81"/>
+      <c r="S9" s="83"/>
       <c r="T9" s="81"/>
       <c r="U9" s="81"/>
-      <c r="W9" s="83"/>
-      <c r="X9" s="81"/>
+      <c r="V9" s="81"/>
+      <c r="X9" s="83"/>
       <c r="Y9" s="81"/>
-      <c r="AA9" s="87" t="s">
+      <c r="Z9" s="81"/>
+      <c r="AB9" s="87" t="s">
         <v>310</v>
       </c>
-      <c r="AB9" s="81" t="s">
+      <c r="AC9" s="81" t="s">
         <v>287</v>
       </c>
-      <c r="AC9" s="81" t="s">
+      <c r="AD9" s="81" t="s">
         <v>288</v>
       </c>
-      <c r="AD9" s="81" t="s">
+      <c r="AE9" s="81" t="s">
         <v>289</v>
       </c>
-      <c r="AE9" s="81" t="s">
+      <c r="AF9" s="81" t="s">
         <v>290</v>
       </c>
-      <c r="AF9" s="81" t="s">
+      <c r="AG9" s="81" t="s">
         <v>291</v>
       </c>
-      <c r="AH9" s="81" t="s">
+      <c r="AI9" s="81" t="s">
         <v>320</v>
       </c>
-      <c r="AI9" s="81" t="s">
+      <c r="AJ9" s="81" t="s">
         <v>325</v>
       </c>
-      <c r="AJ9" s="81" t="s">
+      <c r="AK9" s="81" t="s">
         <v>327</v>
       </c>
-      <c r="AK9" s="81" t="s">
+      <c r="AL9" s="81" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="2:37" ht="48" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:38" ht="48" x14ac:dyDescent="0.25">
       <c r="B10" s="86"/>
-      <c r="C10" s="81"/>
+      <c r="C10" s="86"/>
       <c r="D10" s="81"/>
       <c r="E10" s="81"/>
       <c r="F10" s="81"/>
-      <c r="G10" s="82"/>
+      <c r="G10" s="81"/>
       <c r="H10" s="82"/>
-      <c r="I10" s="81"/>
-      <c r="J10" s="108"/>
-      <c r="K10" s="81"/>
-      <c r="M10" s="83"/>
-      <c r="N10" s="81"/>
+      <c r="I10" s="82"/>
+      <c r="J10" s="81"/>
+      <c r="K10" s="108"/>
+      <c r="L10" s="81"/>
+      <c r="N10" s="83"/>
       <c r="O10" s="81"/>
       <c r="P10" s="81"/>
-      <c r="R10" s="83"/>
-      <c r="S10" s="81"/>
+      <c r="Q10" s="81"/>
+      <c r="S10" s="83"/>
       <c r="T10" s="81"/>
       <c r="U10" s="81"/>
-      <c r="W10" s="83"/>
-      <c r="X10" s="81"/>
+      <c r="V10" s="81"/>
+      <c r="X10" s="83"/>
       <c r="Y10" s="81"/>
-      <c r="AA10" s="87" t="s">
+      <c r="Z10" s="81"/>
+      <c r="AB10" s="87" t="s">
         <v>311</v>
       </c>
-      <c r="AB10" s="81" t="s">
+      <c r="AC10" s="81" t="s">
         <v>292</v>
       </c>
-      <c r="AC10" s="81" t="s">
+      <c r="AD10" s="81" t="s">
         <v>293</v>
       </c>
-      <c r="AD10" s="81" t="s">
+      <c r="AE10" s="81" t="s">
         <v>294</v>
       </c>
-      <c r="AE10" s="81" t="s">
+      <c r="AF10" s="81" t="s">
         <v>295</v>
       </c>
-      <c r="AF10" s="81" t="s">
+      <c r="AG10" s="81" t="s">
         <v>296</v>
       </c>
-      <c r="AH10" s="81" t="s">
+      <c r="AI10" s="81" t="s">
         <v>321</v>
       </c>
-      <c r="AI10" s="81" t="s">
+      <c r="AJ10" s="81" t="s">
         <v>326</v>
       </c>
-      <c r="AJ10" s="81" t="s">
+      <c r="AK10" s="81" t="s">
         <v>327</v>
       </c>
-      <c r="AK10" s="81" t="s">
+      <c r="AL10" s="81" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="11" spans="2:37" ht="24" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:38" ht="24" x14ac:dyDescent="0.25">
       <c r="B11" s="86"/>
-      <c r="C11" s="81"/>
+      <c r="C11" s="86"/>
       <c r="D11" s="81"/>
       <c r="E11" s="81"/>
       <c r="F11" s="81"/>
-      <c r="G11" s="82"/>
+      <c r="G11" s="81"/>
       <c r="H11" s="82"/>
-      <c r="I11" s="81"/>
-      <c r="J11" s="108"/>
-      <c r="K11" s="81"/>
-      <c r="M11" s="83"/>
-      <c r="N11" s="81"/>
+      <c r="I11" s="82"/>
+      <c r="J11" s="81"/>
+      <c r="K11" s="108"/>
+      <c r="L11" s="81"/>
+      <c r="N11" s="83"/>
       <c r="O11" s="81"/>
       <c r="P11" s="81"/>
-      <c r="W11" s="83"/>
-      <c r="X11" s="81"/>
+      <c r="Q11" s="81"/>
+      <c r="X11" s="83"/>
       <c r="Y11" s="81"/>
-      <c r="AA11" s="87" t="s">
+      <c r="Z11" s="81"/>
+      <c r="AB11" s="87" t="s">
         <v>312</v>
       </c>
-      <c r="AB11" s="81" t="s">
+      <c r="AC11" s="81" t="s">
         <v>297</v>
       </c>
-      <c r="AC11" s="81" t="s">
+      <c r="AD11" s="81" t="s">
         <v>298</v>
       </c>
-      <c r="AD11" s="81" t="s">
+      <c r="AE11" s="81" t="s">
         <v>299</v>
       </c>
-      <c r="AE11" s="81" t="s">
+      <c r="AF11" s="81" t="s">
         <v>300</v>
       </c>
-      <c r="AF11" s="81" t="s">
+      <c r="AG11" s="81" t="s">
         <v>301</v>
       </c>
-      <c r="AH11" s="81" t="s">
+      <c r="AI11" s="81" t="s">
         <v>328</v>
       </c>
-      <c r="AI11" s="81" t="s">
+      <c r="AJ11" s="81" t="s">
         <v>329</v>
       </c>
-      <c r="AJ11" s="81" t="s">
+      <c r="AK11" s="81" t="s">
         <v>338</v>
       </c>
-      <c r="AK11" s="81" t="s">
+      <c r="AL11" s="81" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="12" spans="2:37" ht="36" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:38" ht="36" x14ac:dyDescent="0.25">
       <c r="B12" s="86"/>
-      <c r="C12" s="81"/>
+      <c r="C12" s="86"/>
       <c r="D12" s="81"/>
       <c r="E12" s="81"/>
       <c r="F12" s="81"/>
-      <c r="G12" s="82"/>
+      <c r="G12" s="81"/>
       <c r="H12" s="82"/>
-      <c r="I12" s="81"/>
-      <c r="J12" s="108"/>
-      <c r="K12" s="81"/>
-      <c r="M12" s="83"/>
-      <c r="N12" s="81"/>
+      <c r="I12" s="82"/>
+      <c r="J12" s="81"/>
+      <c r="K12" s="108"/>
+      <c r="L12" s="81"/>
+      <c r="N12" s="83"/>
       <c r="O12" s="81"/>
       <c r="P12" s="81"/>
-      <c r="W12" s="83"/>
-      <c r="X12" s="81"/>
+      <c r="Q12" s="81"/>
+      <c r="X12" s="83"/>
       <c r="Y12" s="81"/>
-      <c r="AA12" s="87" t="s">
+      <c r="Z12" s="81"/>
+      <c r="AB12" s="87" t="s">
         <v>313</v>
       </c>
-      <c r="AB12" s="81" t="s">
+      <c r="AC12" s="81" t="s">
         <v>302</v>
       </c>
-      <c r="AC12" s="81" t="s">
+      <c r="AD12" s="81" t="s">
         <v>303</v>
       </c>
-      <c r="AD12" s="81" t="s">
+      <c r="AE12" s="81" t="s">
         <v>304</v>
       </c>
-      <c r="AE12" s="81" t="s">
+      <c r="AF12" s="81" t="s">
         <v>305</v>
       </c>
-      <c r="AF12" s="81" t="s">
+      <c r="AG12" s="81" t="s">
         <v>306</v>
       </c>
-      <c r="AH12" s="81" t="s">
+      <c r="AI12" s="81" t="s">
         <v>330</v>
       </c>
-      <c r="AI12" s="81" t="s">
+      <c r="AJ12" s="81" t="s">
         <v>331</v>
       </c>
-      <c r="AJ12" s="81" t="s">
+      <c r="AK12" s="81" t="s">
         <v>338</v>
       </c>
-      <c r="AK12" s="81" t="s">
+      <c r="AL12" s="81" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="13" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B13" s="86"/>
-      <c r="C13" s="81"/>
+      <c r="C13" s="86"/>
       <c r="D13" s="81"/>
       <c r="E13" s="81"/>
       <c r="F13" s="81"/>
-      <c r="G13" s="82"/>
+      <c r="G13" s="81"/>
       <c r="H13" s="82"/>
-      <c r="I13" s="81"/>
-      <c r="J13" s="108"/>
-      <c r="K13" s="81"/>
-      <c r="M13" s="83"/>
-      <c r="N13" s="81"/>
+      <c r="I13" s="82"/>
+      <c r="J13" s="81"/>
+      <c r="K13" s="108"/>
+      <c r="L13" s="81"/>
+      <c r="N13" s="83"/>
       <c r="O13" s="81"/>
       <c r="P13" s="81"/>
-      <c r="W13" s="83"/>
-      <c r="X13" s="81"/>
+      <c r="Q13" s="81"/>
+      <c r="X13" s="83"/>
       <c r="Y13" s="81"/>
-      <c r="AH13" s="81" t="s">
+      <c r="Z13" s="81"/>
+      <c r="AI13" s="81" t="s">
         <v>332</v>
       </c>
-      <c r="AI13" s="81" t="s">
+      <c r="AJ13" s="81" t="s">
         <v>333</v>
       </c>
-      <c r="AJ13" s="81" t="s">
+      <c r="AK13" s="81" t="s">
         <v>338</v>
       </c>
-      <c r="AK13" s="81" t="s">
+      <c r="AL13" s="81" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="14" spans="2:37" ht="41.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:38" ht="41.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="86"/>
-      <c r="C14" s="81"/>
+      <c r="C14" s="86"/>
       <c r="D14" s="81"/>
       <c r="E14" s="81"/>
       <c r="F14" s="81"/>
-      <c r="G14" s="82"/>
+      <c r="G14" s="81"/>
       <c r="H14" s="82"/>
-      <c r="I14" s="81"/>
-      <c r="J14" s="108"/>
-      <c r="K14" s="81"/>
-      <c r="M14" s="83"/>
-      <c r="N14" s="81"/>
+      <c r="I14" s="82"/>
+      <c r="J14" s="81"/>
+      <c r="K14" s="108"/>
+      <c r="L14" s="81"/>
+      <c r="N14" s="83"/>
       <c r="O14" s="81"/>
       <c r="P14" s="81"/>
-      <c r="W14" s="83"/>
-      <c r="X14" s="81"/>
+      <c r="Q14" s="81"/>
+      <c r="X14" s="83"/>
       <c r="Y14" s="81"/>
-      <c r="AH14" s="81" t="s">
+      <c r="Z14" s="81"/>
+      <c r="AI14" s="81" t="s">
         <v>334</v>
       </c>
-      <c r="AI14" s="81" t="s">
+      <c r="AJ14" s="81" t="s">
         <v>335</v>
       </c>
-      <c r="AJ14" s="81" t="s">
+      <c r="AK14" s="81" t="s">
         <v>338</v>
       </c>
-      <c r="AK14" s="81" t="s">
+      <c r="AL14" s="81" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="15" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B15" s="86"/>
-      <c r="C15" s="81"/>
+      <c r="C15" s="86"/>
       <c r="D15" s="81"/>
       <c r="E15" s="81"/>
       <c r="F15" s="81"/>
-      <c r="G15" s="82"/>
+      <c r="G15" s="81"/>
       <c r="H15" s="82"/>
-      <c r="I15" s="81"/>
-      <c r="J15" s="108"/>
-      <c r="K15" s="81"/>
-      <c r="M15" s="83"/>
-      <c r="N15" s="81"/>
+      <c r="I15" s="82"/>
+      <c r="J15" s="81"/>
+      <c r="K15" s="108"/>
+      <c r="L15" s="81"/>
+      <c r="N15" s="83"/>
       <c r="O15" s="81"/>
       <c r="P15" s="81"/>
-      <c r="W15" s="83"/>
-      <c r="X15" s="81"/>
+      <c r="Q15" s="81"/>
+      <c r="X15" s="83"/>
       <c r="Y15" s="81"/>
-      <c r="AH15" s="81" t="s">
+      <c r="Z15" s="81"/>
+      <c r="AI15" s="81" t="s">
         <v>336</v>
       </c>
-      <c r="AI15" s="81" t="s">
+      <c r="AJ15" s="81" t="s">
         <v>337</v>
       </c>
-      <c r="AJ15" s="81" t="s">
+      <c r="AK15" s="81" t="s">
         <v>338</v>
       </c>
-      <c r="AK15" s="81" t="s">
+      <c r="AL15" s="81" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="16" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B16" s="86"/>
-      <c r="C16" s="81"/>
+      <c r="C16" s="86"/>
       <c r="D16" s="81"/>
       <c r="E16" s="81"/>
       <c r="F16" s="81"/>
-      <c r="G16" s="82"/>
+      <c r="G16" s="81"/>
       <c r="H16" s="82"/>
-      <c r="I16" s="81"/>
-      <c r="J16" s="108"/>
-      <c r="K16" s="81"/>
-      <c r="M16" s="83"/>
-      <c r="N16" s="81"/>
+      <c r="I16" s="82"/>
+      <c r="J16" s="81"/>
+      <c r="K16" s="108"/>
+      <c r="L16" s="81"/>
+      <c r="N16" s="83"/>
       <c r="O16" s="81"/>
       <c r="P16" s="81"/>
-      <c r="W16" s="83"/>
-      <c r="X16" s="81"/>
+      <c r="Q16" s="81"/>
+      <c r="X16" s="83"/>
       <c r="Y16" s="81"/>
-    </row>
-    <row r="17" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="Z16" s="81"/>
+    </row>
+    <row r="17" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B17" s="86"/>
-      <c r="C17" s="81"/>
+      <c r="C17" s="86"/>
       <c r="D17" s="81"/>
       <c r="E17" s="81"/>
       <c r="F17" s="81"/>
-      <c r="G17" s="82"/>
+      <c r="G17" s="81"/>
       <c r="H17" s="82"/>
-      <c r="I17" s="81"/>
-      <c r="J17" s="108"/>
-      <c r="K17" s="81"/>
-      <c r="M17" s="83"/>
-      <c r="N17" s="81"/>
+      <c r="I17" s="82"/>
+      <c r="J17" s="81"/>
+      <c r="K17" s="108"/>
+      <c r="L17" s="81"/>
+      <c r="N17" s="83"/>
       <c r="O17" s="81"/>
       <c r="P17" s="81"/>
-      <c r="W17" s="83"/>
-      <c r="X17" s="81"/>
+      <c r="Q17" s="81"/>
+      <c r="X17" s="83"/>
       <c r="Y17" s="81"/>
-    </row>
-    <row r="18" spans="2:25" ht="41.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z17" s="81"/>
+    </row>
+    <row r="18" spans="2:26" ht="41.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="86"/>
-      <c r="C18" s="81"/>
+      <c r="C18" s="86"/>
       <c r="D18" s="81"/>
       <c r="E18" s="81"/>
       <c r="F18" s="81"/>
-      <c r="G18" s="82"/>
+      <c r="G18" s="81"/>
       <c r="H18" s="82"/>
-      <c r="I18" s="81"/>
-      <c r="J18" s="108"/>
-      <c r="K18" s="81"/>
-      <c r="M18" s="83"/>
-      <c r="N18" s="81"/>
+      <c r="I18" s="82"/>
+      <c r="J18" s="81"/>
+      <c r="K18" s="108"/>
+      <c r="L18" s="81"/>
+      <c r="N18" s="83"/>
       <c r="O18" s="81"/>
       <c r="P18" s="81"/>
-      <c r="W18" s="83"/>
-      <c r="X18" s="81"/>
+      <c r="Q18" s="81"/>
+      <c r="X18" s="83"/>
       <c r="Y18" s="81"/>
-    </row>
-    <row r="19" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="Z18" s="81"/>
+    </row>
+    <row r="19" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B19" s="86"/>
-      <c r="C19" s="81"/>
+      <c r="C19" s="86"/>
       <c r="D19" s="81"/>
       <c r="E19" s="81"/>
       <c r="F19" s="81"/>
-      <c r="G19" s="82"/>
+      <c r="G19" s="81"/>
       <c r="H19" s="82"/>
-      <c r="I19" s="81"/>
-      <c r="J19" s="108"/>
-      <c r="K19" s="81"/>
-      <c r="M19" s="83"/>
-      <c r="N19" s="81"/>
+      <c r="I19" s="82"/>
+      <c r="J19" s="81"/>
+      <c r="K19" s="108"/>
+      <c r="L19" s="81"/>
+      <c r="N19" s="83"/>
       <c r="O19" s="81"/>
       <c r="P19" s="81"/>
-      <c r="W19" s="83"/>
-      <c r="X19" s="81"/>
+      <c r="Q19" s="81"/>
+      <c r="X19" s="83"/>
       <c r="Y19" s="81"/>
-    </row>
-    <row r="20" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="Z19" s="81"/>
+    </row>
+    <row r="20" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B20" s="86"/>
-      <c r="C20" s="81"/>
+      <c r="C20" s="86"/>
       <c r="D20" s="81"/>
       <c r="E20" s="81"/>
       <c r="F20" s="81"/>
-      <c r="G20" s="82"/>
+      <c r="G20" s="81"/>
       <c r="H20" s="82"/>
-      <c r="I20" s="81"/>
-      <c r="J20" s="108"/>
-      <c r="K20" s="81"/>
-      <c r="M20" s="83"/>
-      <c r="N20" s="81"/>
+      <c r="I20" s="82"/>
+      <c r="J20" s="81"/>
+      <c r="K20" s="108"/>
+      <c r="L20" s="81"/>
+      <c r="N20" s="83"/>
       <c r="O20" s="81"/>
       <c r="P20" s="81"/>
-      <c r="W20" s="83"/>
-      <c r="X20" s="81"/>
+      <c r="Q20" s="81"/>
+      <c r="X20" s="83"/>
       <c r="Y20" s="81"/>
-    </row>
-    <row r="21" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="Z20" s="81"/>
+    </row>
+    <row r="21" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B21" s="86"/>
-      <c r="C21" s="81"/>
+      <c r="C21" s="86"/>
       <c r="D21" s="81"/>
       <c r="E21" s="81"/>
       <c r="F21" s="81"/>
-      <c r="G21" s="82"/>
+      <c r="G21" s="81"/>
       <c r="H21" s="82"/>
-      <c r="I21" s="81"/>
-      <c r="J21" s="108"/>
-      <c r="K21" s="81"/>
-      <c r="M21" s="83"/>
-      <c r="N21" s="81"/>
+      <c r="I21" s="82"/>
+      <c r="J21" s="81"/>
+      <c r="K21" s="108"/>
+      <c r="L21" s="81"/>
+      <c r="N21" s="83"/>
       <c r="O21" s="81"/>
       <c r="P21" s="81"/>
-      <c r="W21" s="83"/>
-      <c r="X21" s="81"/>
+      <c r="Q21" s="81"/>
+      <c r="X21" s="83"/>
       <c r="Y21" s="81"/>
-    </row>
-    <row r="22" spans="2:25" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z21" s="81"/>
+    </row>
+    <row r="22" spans="2:26" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="86"/>
-      <c r="C22" s="81"/>
+      <c r="C22" s="86"/>
       <c r="D22" s="81"/>
       <c r="E22" s="81"/>
       <c r="F22" s="81"/>
-      <c r="G22" s="82"/>
+      <c r="G22" s="81"/>
       <c r="H22" s="82"/>
-      <c r="I22" s="81"/>
-      <c r="J22" s="108"/>
-      <c r="K22" s="81"/>
-      <c r="M22" s="83"/>
-      <c r="N22" s="81"/>
+      <c r="I22" s="82"/>
+      <c r="J22" s="81"/>
+      <c r="K22" s="108"/>
+      <c r="L22" s="81"/>
+      <c r="N22" s="83"/>
       <c r="O22" s="81"/>
       <c r="P22" s="81"/>
-      <c r="W22" s="83"/>
-      <c r="X22" s="81"/>
+      <c r="Q22" s="81"/>
+      <c r="X22" s="83"/>
       <c r="Y22" s="81"/>
-    </row>
-    <row r="23" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="Z22" s="81"/>
+    </row>
+    <row r="23" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B23" s="86"/>
-      <c r="C23" s="81"/>
+      <c r="C23" s="86"/>
       <c r="D23" s="81"/>
       <c r="E23" s="81"/>
       <c r="F23" s="81"/>
-      <c r="G23" s="82"/>
+      <c r="G23" s="81"/>
       <c r="H23" s="82"/>
-      <c r="I23" s="81"/>
-      <c r="J23" s="108"/>
-      <c r="K23" s="81"/>
-      <c r="M23" s="83"/>
-      <c r="N23" s="81"/>
+      <c r="I23" s="82"/>
+      <c r="J23" s="81"/>
+      <c r="K23" s="108"/>
+      <c r="L23" s="81"/>
+      <c r="N23" s="83"/>
       <c r="O23" s="81"/>
       <c r="P23" s="81"/>
-      <c r="W23" s="83"/>
-      <c r="X23" s="81"/>
+      <c r="Q23" s="81"/>
+      <c r="X23" s="83"/>
       <c r="Y23" s="81"/>
-    </row>
-    <row r="24" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="Z23" s="81"/>
+    </row>
+    <row r="24" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B24" s="86"/>
-      <c r="C24" s="81"/>
+      <c r="C24" s="86"/>
       <c r="D24" s="81"/>
       <c r="E24" s="81"/>
       <c r="F24" s="81"/>
-      <c r="G24" s="82"/>
+      <c r="G24" s="81"/>
       <c r="H24" s="82"/>
-      <c r="I24" s="81"/>
-      <c r="J24" s="108"/>
-      <c r="K24" s="81"/>
-      <c r="M24" s="83"/>
-      <c r="N24" s="81"/>
+      <c r="I24" s="82"/>
+      <c r="J24" s="81"/>
+      <c r="K24" s="108"/>
+      <c r="L24" s="81"/>
+      <c r="N24" s="83"/>
       <c r="O24" s="81"/>
       <c r="P24" s="81"/>
-      <c r="W24" s="83"/>
-      <c r="X24" s="81"/>
+      <c r="Q24" s="81"/>
+      <c r="X24" s="83"/>
       <c r="Y24" s="81"/>
-    </row>
-    <row r="25" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="Z24" s="81"/>
+    </row>
+    <row r="25" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B25" s="86"/>
-      <c r="C25" s="81"/>
+      <c r="C25" s="86"/>
       <c r="D25" s="81"/>
       <c r="E25" s="81"/>
       <c r="F25" s="81"/>
-      <c r="G25" s="82"/>
+      <c r="G25" s="81"/>
       <c r="H25" s="82"/>
-      <c r="I25" s="81"/>
-      <c r="J25" s="108"/>
-      <c r="K25" s="81"/>
-      <c r="M25" s="83"/>
-      <c r="N25" s="81"/>
+      <c r="I25" s="82"/>
+      <c r="J25" s="81"/>
+      <c r="K25" s="108"/>
+      <c r="L25" s="81"/>
+      <c r="N25" s="83"/>
       <c r="O25" s="81"/>
       <c r="P25" s="81"/>
-      <c r="W25" s="83"/>
-      <c r="X25" s="81"/>
+      <c r="Q25" s="81"/>
+      <c r="X25" s="83"/>
       <c r="Y25" s="81"/>
-    </row>
-    <row r="26" spans="2:25" ht="36.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z25" s="81"/>
+    </row>
+    <row r="26" spans="2:26" ht="36.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="86"/>
-      <c r="C26" s="81"/>
+      <c r="C26" s="86"/>
       <c r="D26" s="81"/>
       <c r="E26" s="81"/>
       <c r="F26" s="81"/>
-      <c r="G26" s="82"/>
+      <c r="G26" s="81"/>
       <c r="H26" s="82"/>
-      <c r="I26" s="81"/>
-      <c r="J26" s="108"/>
-      <c r="K26" s="81"/>
-      <c r="M26" s="83"/>
-      <c r="N26" s="81"/>
+      <c r="I26" s="82"/>
+      <c r="J26" s="81"/>
+      <c r="K26" s="108"/>
+      <c r="L26" s="81"/>
+      <c r="N26" s="83"/>
       <c r="O26" s="81"/>
       <c r="P26" s="81"/>
-      <c r="W26" s="83"/>
-      <c r="X26" s="81"/>
+      <c r="Q26" s="81"/>
+      <c r="X26" s="83"/>
       <c r="Y26" s="81"/>
-    </row>
-    <row r="27" spans="2:25" ht="36.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z26" s="81"/>
+    </row>
+    <row r="27" spans="2:26" ht="36.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="86"/>
-      <c r="C27" s="81"/>
+      <c r="C27" s="86"/>
       <c r="D27" s="81"/>
       <c r="E27" s="81"/>
       <c r="F27" s="81"/>
-      <c r="G27" s="82"/>
+      <c r="G27" s="81"/>
       <c r="H27" s="82"/>
-      <c r="I27" s="81"/>
-      <c r="J27" s="108"/>
-      <c r="K27" s="81"/>
-      <c r="M27" s="83"/>
-      <c r="N27" s="81"/>
+      <c r="I27" s="82"/>
+      <c r="J27" s="81"/>
+      <c r="K27" s="108"/>
+      <c r="L27" s="81"/>
+      <c r="N27" s="83"/>
       <c r="O27" s="81"/>
       <c r="P27" s="81"/>
-      <c r="W27" s="83"/>
-      <c r="X27" s="81"/>
+      <c r="Q27" s="81"/>
+      <c r="X27" s="83"/>
       <c r="Y27" s="81"/>
-    </row>
-    <row r="28" spans="2:25" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z27" s="81"/>
+    </row>
+    <row r="28" spans="2:26" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="86"/>
-      <c r="C28" s="81"/>
+      <c r="C28" s="86"/>
       <c r="D28" s="81"/>
       <c r="E28" s="81"/>
       <c r="F28" s="81"/>
-      <c r="G28" s="82"/>
+      <c r="G28" s="81"/>
       <c r="H28" s="82"/>
-      <c r="I28" s="81"/>
-      <c r="J28" s="108"/>
-      <c r="K28" s="81"/>
-      <c r="M28" s="83"/>
-      <c r="N28" s="81"/>
+      <c r="I28" s="82"/>
+      <c r="J28" s="81"/>
+      <c r="K28" s="108"/>
+      <c r="L28" s="81"/>
+      <c r="N28" s="83"/>
       <c r="O28" s="81"/>
       <c r="P28" s="81"/>
-      <c r="W28" s="83"/>
-      <c r="X28" s="81"/>
+      <c r="Q28" s="81"/>
+      <c r="X28" s="83"/>
       <c r="Y28" s="81"/>
-    </row>
-    <row r="29" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="Z28" s="81"/>
+    </row>
+    <row r="29" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B29" s="86"/>
-      <c r="C29" s="81"/>
+      <c r="C29" s="86"/>
       <c r="D29" s="81"/>
       <c r="E29" s="81"/>
       <c r="F29" s="81"/>
-      <c r="G29" s="82"/>
+      <c r="G29" s="81"/>
       <c r="H29" s="82"/>
-      <c r="I29" s="81"/>
-      <c r="J29" s="108"/>
-      <c r="K29" s="81"/>
-      <c r="M29" s="83"/>
-      <c r="N29" s="81"/>
+      <c r="I29" s="82"/>
+      <c r="J29" s="81"/>
+      <c r="K29" s="108"/>
+      <c r="L29" s="81"/>
+      <c r="N29" s="83"/>
       <c r="O29" s="81"/>
       <c r="P29" s="81"/>
-      <c r="W29" s="83"/>
-      <c r="X29" s="81"/>
+      <c r="Q29" s="81"/>
+      <c r="X29" s="83"/>
       <c r="Y29" s="81"/>
-    </row>
-    <row r="30" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="Z29" s="81"/>
+    </row>
+    <row r="30" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B30" s="86"/>
-      <c r="C30" s="81"/>
+      <c r="C30" s="86"/>
       <c r="D30" s="81"/>
       <c r="E30" s="81"/>
       <c r="F30" s="81"/>
-      <c r="G30" s="82"/>
+      <c r="G30" s="81"/>
       <c r="H30" s="82"/>
-      <c r="I30" s="81"/>
-      <c r="J30" s="108"/>
-      <c r="K30" s="81"/>
-      <c r="M30" s="83"/>
-      <c r="N30" s="81"/>
+      <c r="I30" s="82"/>
+      <c r="J30" s="81"/>
+      <c r="K30" s="108"/>
+      <c r="L30" s="81"/>
+      <c r="N30" s="83"/>
       <c r="O30" s="81"/>
       <c r="P30" s="81"/>
-      <c r="W30" s="83"/>
-      <c r="X30" s="81"/>
+      <c r="Q30" s="81"/>
+      <c r="X30" s="83"/>
       <c r="Y30" s="81"/>
-    </row>
-    <row r="31" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="Z30" s="81"/>
+    </row>
+    <row r="31" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B31" s="86"/>
-      <c r="C31" s="81"/>
+      <c r="C31" s="86"/>
       <c r="D31" s="81"/>
       <c r="E31" s="81"/>
       <c r="F31" s="81"/>
-      <c r="G31" s="82"/>
+      <c r="G31" s="81"/>
       <c r="H31" s="82"/>
-      <c r="I31" s="81"/>
-      <c r="J31" s="108"/>
-      <c r="K31" s="81"/>
-      <c r="M31" s="83"/>
-      <c r="N31" s="81"/>
+      <c r="I31" s="82"/>
+      <c r="J31" s="81"/>
+      <c r="K31" s="108"/>
+      <c r="L31" s="81"/>
+      <c r="N31" s="83"/>
       <c r="O31" s="81"/>
       <c r="P31" s="81"/>
-      <c r="W31" s="83"/>
-      <c r="X31" s="81"/>
+      <c r="Q31" s="81"/>
+      <c r="X31" s="83"/>
       <c r="Y31" s="81"/>
-    </row>
-    <row r="32" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="Z31" s="81"/>
+    </row>
+    <row r="32" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B32" s="86"/>
-      <c r="C32" s="81"/>
+      <c r="C32" s="86"/>
       <c r="D32" s="81"/>
       <c r="E32" s="81"/>
       <c r="F32" s="81"/>
-      <c r="G32" s="82"/>
+      <c r="G32" s="81"/>
       <c r="H32" s="82"/>
-      <c r="I32" s="81"/>
-      <c r="J32" s="108"/>
-      <c r="K32" s="81"/>
-      <c r="M32" s="83"/>
-      <c r="N32" s="81"/>
+      <c r="I32" s="82"/>
+      <c r="J32" s="81"/>
+      <c r="K32" s="108"/>
+      <c r="L32" s="81"/>
+      <c r="N32" s="83"/>
       <c r="O32" s="81"/>
       <c r="P32" s="81"/>
-      <c r="W32" s="83"/>
-      <c r="X32" s="81"/>
+      <c r="Q32" s="81"/>
+      <c r="X32" s="83"/>
       <c r="Y32" s="81"/>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="Z32" s="81"/>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B33" s="86"/>
-      <c r="C33" s="81"/>
+      <c r="C33" s="86"/>
       <c r="D33" s="81"/>
       <c r="E33" s="81"/>
       <c r="F33" s="81"/>
-      <c r="G33" s="82"/>
+      <c r="G33" s="81"/>
       <c r="H33" s="82"/>
-      <c r="I33" s="81"/>
-      <c r="J33" s="108"/>
-      <c r="K33" s="81"/>
-      <c r="M33" s="83"/>
-      <c r="N33" s="81"/>
+      <c r="I33" s="82"/>
+      <c r="J33" s="81"/>
+      <c r="K33" s="108"/>
+      <c r="L33" s="81"/>
+      <c r="N33" s="83"/>
       <c r="O33" s="81"/>
       <c r="P33" s="81"/>
-      <c r="W33" s="83"/>
-      <c r="X33" s="81"/>
+      <c r="Q33" s="81"/>
+      <c r="X33" s="83"/>
       <c r="Y33" s="81"/>
-    </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="Z33" s="81"/>
+    </row>
+    <row r="34" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B34" s="86"/>
-      <c r="C34" s="81"/>
+      <c r="C34" s="86"/>
       <c r="D34" s="81"/>
       <c r="E34" s="81"/>
       <c r="F34" s="81"/>
-      <c r="G34" s="82"/>
+      <c r="G34" s="81"/>
       <c r="H34" s="82"/>
-      <c r="I34" s="81"/>
-      <c r="J34" s="108"/>
-      <c r="K34" s="81"/>
-      <c r="M34" s="83"/>
-      <c r="N34" s="81"/>
+      <c r="I34" s="82"/>
+      <c r="J34" s="81"/>
+      <c r="K34" s="108"/>
+      <c r="L34" s="81"/>
+      <c r="N34" s="83"/>
       <c r="O34" s="81"/>
       <c r="P34" s="81"/>
-      <c r="W34" s="83"/>
-      <c r="X34" s="81"/>
+      <c r="Q34" s="81"/>
+      <c r="X34" s="83"/>
       <c r="Y34" s="81"/>
-    </row>
-    <row r="35" spans="2:25" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z34" s="81"/>
+    </row>
+    <row r="35" spans="2:26" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="86"/>
-      <c r="C35" s="81"/>
+      <c r="C35" s="86"/>
       <c r="D35" s="81"/>
       <c r="E35" s="81"/>
       <c r="F35" s="81"/>
-      <c r="G35" s="82"/>
+      <c r="G35" s="81"/>
       <c r="H35" s="82"/>
-      <c r="I35" s="81"/>
-      <c r="J35" s="108"/>
-      <c r="K35" s="81"/>
-      <c r="M35" s="83"/>
-      <c r="N35" s="81"/>
+      <c r="I35" s="82"/>
+      <c r="J35" s="81"/>
+      <c r="K35" s="108"/>
+      <c r="L35" s="81"/>
+      <c r="N35" s="83"/>
       <c r="O35" s="81"/>
       <c r="P35" s="81"/>
-      <c r="W35" s="83"/>
-      <c r="X35" s="81"/>
+      <c r="Q35" s="81"/>
+      <c r="X35" s="83"/>
       <c r="Y35" s="81"/>
-    </row>
-    <row r="36" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="Z35" s="81"/>
+    </row>
+    <row r="36" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B36" s="86"/>
-      <c r="C36" s="81"/>
+      <c r="C36" s="86"/>
       <c r="D36" s="81"/>
       <c r="E36" s="81"/>
       <c r="F36" s="81"/>
-      <c r="G36" s="82"/>
+      <c r="G36" s="81"/>
       <c r="H36" s="82"/>
-      <c r="I36" s="81"/>
-      <c r="J36" s="108"/>
-      <c r="K36" s="81"/>
-      <c r="M36" s="83"/>
-      <c r="N36" s="81"/>
+      <c r="I36" s="82"/>
+      <c r="J36" s="81"/>
+      <c r="K36" s="108"/>
+      <c r="L36" s="81"/>
+      <c r="N36" s="83"/>
       <c r="O36" s="81"/>
       <c r="P36" s="81"/>
-      <c r="W36" s="83"/>
-      <c r="X36" s="81"/>
+      <c r="Q36" s="81"/>
+      <c r="X36" s="83"/>
       <c r="Y36" s="81"/>
-    </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="Z36" s="81"/>
+    </row>
+    <row r="37" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B37" s="86"/>
-      <c r="C37" s="81"/>
+      <c r="C37" s="86"/>
       <c r="D37" s="81"/>
       <c r="E37" s="81"/>
       <c r="F37" s="81"/>
-      <c r="G37" s="82"/>
+      <c r="G37" s="81"/>
       <c r="H37" s="82"/>
-      <c r="I37" s="81"/>
-      <c r="J37" s="108"/>
-      <c r="K37" s="81"/>
-      <c r="M37" s="83"/>
-      <c r="N37" s="81"/>
+      <c r="I37" s="82"/>
+      <c r="J37" s="81"/>
+      <c r="K37" s="108"/>
+      <c r="L37" s="81"/>
+      <c r="N37" s="83"/>
       <c r="O37" s="81"/>
       <c r="P37" s="81"/>
-      <c r="W37" s="83"/>
-      <c r="X37" s="81"/>
+      <c r="Q37" s="81"/>
+      <c r="X37" s="83"/>
       <c r="Y37" s="81"/>
-    </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="Z37" s="81"/>
+    </row>
+    <row r="38" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B38" s="86"/>
-      <c r="C38" s="81"/>
+      <c r="C38" s="86"/>
       <c r="D38" s="81"/>
       <c r="E38" s="81"/>
       <c r="F38" s="81"/>
-      <c r="G38" s="82"/>
+      <c r="G38" s="81"/>
       <c r="H38" s="82"/>
-      <c r="I38" s="81"/>
-      <c r="J38" s="108"/>
-      <c r="K38" s="81"/>
-      <c r="M38" s="83"/>
-      <c r="N38" s="81"/>
+      <c r="I38" s="82"/>
+      <c r="J38" s="81"/>
+      <c r="K38" s="108"/>
+      <c r="L38" s="81"/>
+      <c r="N38" s="83"/>
       <c r="O38" s="81"/>
       <c r="P38" s="81"/>
-      <c r="W38" s="83"/>
-      <c r="X38" s="81"/>
+      <c r="Q38" s="81"/>
+      <c r="X38" s="83"/>
       <c r="Y38" s="81"/>
-    </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="Z38" s="81"/>
+    </row>
+    <row r="39" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B39" s="86"/>
-      <c r="C39" s="81"/>
+      <c r="C39" s="86"/>
       <c r="D39" s="81"/>
       <c r="E39" s="81"/>
       <c r="F39" s="81"/>
-      <c r="G39" s="82"/>
+      <c r="G39" s="81"/>
       <c r="H39" s="82"/>
-      <c r="I39" s="81"/>
-      <c r="J39" s="108"/>
-      <c r="K39" s="81"/>
-      <c r="M39" s="83"/>
-      <c r="N39" s="81"/>
+      <c r="I39" s="82"/>
+      <c r="J39" s="81"/>
+      <c r="K39" s="108"/>
+      <c r="L39" s="81"/>
+      <c r="N39" s="83"/>
       <c r="O39" s="81"/>
       <c r="P39" s="81"/>
-      <c r="W39" s="83"/>
-      <c r="X39" s="81"/>
+      <c r="Q39" s="81"/>
+      <c r="X39" s="83"/>
       <c r="Y39" s="81"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="Z39" s="81"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B40" s="86"/>
-      <c r="C40" s="81"/>
+      <c r="C40" s="86"/>
       <c r="D40" s="81"/>
       <c r="E40" s="81"/>
       <c r="F40" s="81"/>
-      <c r="G40" s="82"/>
+      <c r="G40" s="81"/>
       <c r="H40" s="82"/>
-      <c r="I40" s="81"/>
-      <c r="J40" s="108"/>
-      <c r="K40" s="81"/>
-      <c r="M40" s="83"/>
-      <c r="N40" s="81"/>
+      <c r="I40" s="82"/>
+      <c r="J40" s="81"/>
+      <c r="K40" s="108"/>
+      <c r="L40" s="81"/>
+      <c r="N40" s="83"/>
       <c r="O40" s="81"/>
       <c r="P40" s="81"/>
-      <c r="W40" s="83"/>
-      <c r="X40" s="81"/>
+      <c r="Q40" s="81"/>
+      <c r="X40" s="83"/>
       <c r="Y40" s="81"/>
-    </row>
-    <row r="41" spans="2:25" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z40" s="81"/>
+    </row>
+    <row r="41" spans="2:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="86"/>
-      <c r="C41" s="81"/>
+      <c r="C41" s="86"/>
       <c r="D41" s="81"/>
       <c r="E41" s="81"/>
       <c r="F41" s="81"/>
-      <c r="G41" s="82"/>
+      <c r="G41" s="81"/>
       <c r="H41" s="82"/>
-      <c r="I41" s="81"/>
-      <c r="J41" s="108"/>
-      <c r="K41" s="81"/>
-      <c r="M41" s="83"/>
-      <c r="N41" s="81"/>
+      <c r="I41" s="82"/>
+      <c r="J41" s="81"/>
+      <c r="K41" s="108"/>
+      <c r="L41" s="81"/>
+      <c r="N41" s="83"/>
       <c r="O41" s="81"/>
       <c r="P41" s="81"/>
-      <c r="W41" s="83"/>
-      <c r="X41" s="81"/>
+      <c r="Q41" s="81"/>
+      <c r="X41" s="83"/>
       <c r="Y41" s="81"/>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="Z41" s="81"/>
+    </row>
+    <row r="42" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B42" s="86"/>
-      <c r="C42" s="81"/>
+      <c r="C42" s="86"/>
       <c r="D42" s="81"/>
       <c r="E42" s="81"/>
       <c r="F42" s="81"/>
-      <c r="G42" s="82"/>
+      <c r="G42" s="81"/>
       <c r="H42" s="82"/>
-      <c r="I42" s="81"/>
-      <c r="J42" s="108"/>
-      <c r="K42" s="81"/>
-      <c r="M42" s="83"/>
-      <c r="N42" s="81"/>
+      <c r="I42" s="82"/>
+      <c r="J42" s="81"/>
+      <c r="K42" s="108"/>
+      <c r="L42" s="81"/>
+      <c r="N42" s="83"/>
       <c r="O42" s="81"/>
       <c r="P42" s="81"/>
-      <c r="W42" s="83"/>
-      <c r="X42" s="81"/>
+      <c r="Q42" s="81"/>
+      <c r="X42" s="83"/>
       <c r="Y42" s="81"/>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="Z42" s="81"/>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B43" s="86"/>
-      <c r="C43" s="81"/>
+      <c r="C43" s="86"/>
       <c r="D43" s="81"/>
       <c r="E43" s="81"/>
       <c r="F43" s="81"/>
-      <c r="G43" s="82"/>
+      <c r="G43" s="81"/>
       <c r="H43" s="82"/>
-      <c r="I43" s="81"/>
-      <c r="J43" s="108"/>
-      <c r="K43" s="81"/>
-      <c r="M43" s="83"/>
-      <c r="N43" s="81"/>
+      <c r="I43" s="82"/>
+      <c r="J43" s="81"/>
+      <c r="K43" s="108"/>
+      <c r="L43" s="81"/>
+      <c r="N43" s="83"/>
       <c r="O43" s="81"/>
       <c r="P43" s="81"/>
-      <c r="W43" s="83"/>
-      <c r="X43" s="81"/>
+      <c r="Q43" s="81"/>
+      <c r="X43" s="83"/>
       <c r="Y43" s="81"/>
-    </row>
-    <row r="44" spans="2:25" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z43" s="81"/>
+    </row>
+    <row r="44" spans="2:26" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="86"/>
-      <c r="C44" s="81"/>
+      <c r="C44" s="86"/>
       <c r="D44" s="81"/>
       <c r="E44" s="81"/>
       <c r="F44" s="81"/>
-      <c r="G44" s="82"/>
+      <c r="G44" s="81"/>
       <c r="H44" s="82"/>
-      <c r="I44" s="81"/>
-      <c r="J44" s="108"/>
-      <c r="K44" s="81"/>
-      <c r="M44" s="83"/>
-      <c r="N44" s="81"/>
+      <c r="I44" s="82"/>
+      <c r="J44" s="81"/>
+      <c r="K44" s="108"/>
+      <c r="L44" s="81"/>
+      <c r="N44" s="83"/>
       <c r="O44" s="81"/>
       <c r="P44" s="81"/>
-      <c r="W44" s="83"/>
-      <c r="X44" s="81"/>
+      <c r="Q44" s="81"/>
+      <c r="X44" s="83"/>
       <c r="Y44" s="81"/>
-    </row>
-    <row r="45" spans="2:25" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z44" s="81"/>
+    </row>
+    <row r="45" spans="2:26" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="86"/>
-      <c r="C45" s="108"/>
-      <c r="D45" s="81"/>
+      <c r="C45" s="86"/>
+      <c r="D45" s="108"/>
       <c r="E45" s="81"/>
       <c r="F45" s="81"/>
-      <c r="G45" s="82"/>
+      <c r="G45" s="81"/>
       <c r="H45" s="82"/>
-      <c r="I45" s="81"/>
-      <c r="J45" s="108"/>
-      <c r="K45" s="81"/>
-      <c r="M45" s="83"/>
-      <c r="N45" s="81"/>
+      <c r="I45" s="82"/>
+      <c r="J45" s="81"/>
+      <c r="K45" s="108"/>
+      <c r="L45" s="81"/>
+      <c r="N45" s="83"/>
       <c r="O45" s="81"/>
       <c r="P45" s="81"/>
-      <c r="W45" s="83"/>
-      <c r="X45" s="81"/>
+      <c r="Q45" s="81"/>
+      <c r="X45" s="83"/>
       <c r="Y45" s="81"/>
-    </row>
-    <row r="46" spans="2:25" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z45" s="81"/>
+    </row>
+    <row r="46" spans="2:26" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B46" s="86"/>
-      <c r="C46" s="81"/>
+      <c r="C46" s="86"/>
       <c r="D46" s="81"/>
       <c r="E46" s="81"/>
       <c r="F46" s="81"/>
-      <c r="G46" s="82"/>
+      <c r="G46" s="81"/>
       <c r="H46" s="82"/>
-      <c r="I46" s="81"/>
-      <c r="J46" s="108"/>
-      <c r="K46" s="81"/>
-      <c r="M46" s="83"/>
-      <c r="N46" s="81"/>
+      <c r="I46" s="82"/>
+      <c r="J46" s="81"/>
+      <c r="K46" s="108"/>
+      <c r="L46" s="81"/>
+      <c r="N46" s="83"/>
       <c r="O46" s="81"/>
       <c r="P46" s="81"/>
-      <c r="W46" s="83"/>
-      <c r="X46" s="81"/>
+      <c r="Q46" s="81"/>
+      <c r="X46" s="83"/>
       <c r="Y46" s="81"/>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="Z46" s="81"/>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B47" s="86"/>
-      <c r="C47" s="81"/>
+      <c r="C47" s="86"/>
       <c r="D47" s="81"/>
       <c r="E47" s="81"/>
       <c r="F47" s="81"/>
-      <c r="G47" s="82"/>
+      <c r="G47" s="81"/>
       <c r="H47" s="82"/>
-      <c r="I47" s="81"/>
-      <c r="J47" s="108"/>
-      <c r="K47" s="81"/>
-      <c r="M47" s="83"/>
-      <c r="N47" s="81"/>
+      <c r="I47" s="82"/>
+      <c r="J47" s="81"/>
+      <c r="K47" s="108"/>
+      <c r="L47" s="81"/>
+      <c r="N47" s="83"/>
       <c r="O47" s="81"/>
       <c r="P47" s="81"/>
-      <c r="W47" s="83"/>
-      <c r="X47" s="81"/>
+      <c r="Q47" s="81"/>
+      <c r="X47" s="83"/>
       <c r="Y47" s="81"/>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="Z47" s="81"/>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B48" s="86"/>
-      <c r="C48" s="81"/>
+      <c r="C48" s="86"/>
       <c r="D48" s="81"/>
       <c r="E48" s="81"/>
       <c r="F48" s="81"/>
-      <c r="G48" s="82"/>
+      <c r="G48" s="81"/>
       <c r="H48" s="82"/>
-      <c r="I48" s="81"/>
-      <c r="J48" s="108"/>
-      <c r="K48" s="81"/>
-      <c r="M48" s="83"/>
-      <c r="N48" s="81"/>
+      <c r="I48" s="82"/>
+      <c r="J48" s="81"/>
+      <c r="K48" s="108"/>
+      <c r="L48" s="81"/>
+      <c r="N48" s="83"/>
       <c r="O48" s="81"/>
       <c r="P48" s="81"/>
-      <c r="W48" s="83"/>
-      <c r="X48" s="81"/>
+      <c r="Q48" s="81"/>
+      <c r="X48" s="83"/>
       <c r="Y48" s="81"/>
-    </row>
-    <row r="49" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="Z48" s="81"/>
+    </row>
+    <row r="49" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B49" s="86"/>
-      <c r="C49" s="81"/>
+      <c r="C49" s="86"/>
       <c r="D49" s="81"/>
       <c r="E49" s="81"/>
       <c r="F49" s="81"/>
-      <c r="G49" s="82"/>
+      <c r="G49" s="81"/>
       <c r="H49" s="82"/>
-      <c r="I49" s="81"/>
-      <c r="J49" s="108"/>
-      <c r="K49" s="81"/>
-      <c r="M49" s="83"/>
-      <c r="N49" s="81"/>
+      <c r="I49" s="82"/>
+      <c r="J49" s="81"/>
+      <c r="K49" s="108"/>
+      <c r="L49" s="81"/>
+      <c r="N49" s="83"/>
       <c r="O49" s="81"/>
       <c r="P49" s="81"/>
-      <c r="W49" s="83"/>
-      <c r="X49" s="81"/>
+      <c r="Q49" s="81"/>
+      <c r="X49" s="83"/>
       <c r="Y49" s="81"/>
-    </row>
-    <row r="50" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="Z49" s="81"/>
+    </row>
+    <row r="50" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B50" s="86"/>
-      <c r="C50" s="81"/>
+      <c r="C50" s="86"/>
       <c r="D50" s="81"/>
       <c r="E50" s="81"/>
       <c r="F50" s="81"/>
-      <c r="G50" s="82"/>
+      <c r="G50" s="81"/>
       <c r="H50" s="82"/>
-      <c r="I50" s="81"/>
-      <c r="J50" s="108"/>
-      <c r="K50" s="81"/>
-      <c r="M50" s="83"/>
-      <c r="N50" s="81"/>
+      <c r="I50" s="82"/>
+      <c r="J50" s="81"/>
+      <c r="K50" s="108"/>
+      <c r="L50" s="81"/>
+      <c r="N50" s="83"/>
       <c r="O50" s="81"/>
       <c r="P50" s="81"/>
-      <c r="W50" s="83"/>
-      <c r="X50" s="81"/>
+      <c r="Q50" s="81"/>
+      <c r="X50" s="83"/>
       <c r="Y50" s="81"/>
-    </row>
-    <row r="51" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="Z50" s="81"/>
+    </row>
+    <row r="51" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B51" s="86"/>
-      <c r="C51" s="81"/>
+      <c r="C51" s="86"/>
       <c r="D51" s="81"/>
       <c r="E51" s="81"/>
       <c r="F51" s="81"/>
-      <c r="G51" s="82"/>
+      <c r="G51" s="81"/>
       <c r="H51" s="82"/>
-      <c r="I51" s="81"/>
-      <c r="J51" s="108"/>
-      <c r="K51" s="81"/>
-      <c r="M51" s="83"/>
-      <c r="N51" s="81"/>
+      <c r="I51" s="82"/>
+      <c r="J51" s="81"/>
+      <c r="K51" s="108"/>
+      <c r="L51" s="81"/>
+      <c r="N51" s="83"/>
       <c r="O51" s="81"/>
       <c r="P51" s="81"/>
-      <c r="W51" s="83"/>
-      <c r="X51" s="81"/>
+      <c r="Q51" s="81"/>
+      <c r="X51" s="83"/>
       <c r="Y51" s="81"/>
-    </row>
-    <row r="52" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="Z51" s="81"/>
+    </row>
+    <row r="52" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B52" s="86"/>
-      <c r="C52" s="81"/>
+      <c r="C52" s="86"/>
       <c r="D52" s="81"/>
       <c r="E52" s="81"/>
       <c r="F52" s="81"/>
-      <c r="G52" s="82"/>
+      <c r="G52" s="81"/>
       <c r="H52" s="82"/>
-      <c r="I52" s="81"/>
-      <c r="J52" s="108"/>
-      <c r="K52" s="81"/>
-      <c r="M52" s="83"/>
-      <c r="N52" s="81"/>
+      <c r="I52" s="82"/>
+      <c r="J52" s="81"/>
+      <c r="K52" s="108"/>
+      <c r="L52" s="81"/>
+      <c r="N52" s="83"/>
       <c r="O52" s="81"/>
       <c r="P52" s="81"/>
-      <c r="W52" s="83"/>
-      <c r="X52" s="81"/>
+      <c r="Q52" s="81"/>
+      <c r="X52" s="83"/>
       <c r="Y52" s="81"/>
-    </row>
-    <row r="53" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="Z52" s="81"/>
+    </row>
+    <row r="53" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B53" s="86"/>
-      <c r="C53" s="81"/>
+      <c r="C53" s="86"/>
       <c r="D53" s="81"/>
       <c r="E53" s="81"/>
       <c r="F53" s="81"/>
-      <c r="G53" s="82"/>
+      <c r="G53" s="81"/>
       <c r="H53" s="82"/>
-      <c r="I53" s="81"/>
-      <c r="J53" s="108"/>
-      <c r="K53" s="81"/>
-      <c r="M53" s="83"/>
-      <c r="N53" s="81"/>
+      <c r="I53" s="82"/>
+      <c r="J53" s="81"/>
+      <c r="K53" s="108"/>
+      <c r="L53" s="81"/>
+      <c r="N53" s="83"/>
       <c r="O53" s="81"/>
       <c r="P53" s="81"/>
-      <c r="W53" s="83"/>
-      <c r="X53" s="81"/>
+      <c r="Q53" s="81"/>
+      <c r="X53" s="83"/>
       <c r="Y53" s="81"/>
-    </row>
-    <row r="54" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="Z53" s="81"/>
+    </row>
+    <row r="54" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B54" s="86"/>
-      <c r="C54" s="81"/>
+      <c r="C54" s="86"/>
       <c r="D54" s="81"/>
       <c r="E54" s="81"/>
       <c r="F54" s="81"/>
-      <c r="G54" s="82"/>
+      <c r="G54" s="81"/>
       <c r="H54" s="82"/>
-      <c r="I54" s="81"/>
-      <c r="J54" s="108"/>
-      <c r="K54" s="81"/>
-      <c r="M54" s="83"/>
-      <c r="N54" s="81"/>
+      <c r="I54" s="82"/>
+      <c r="J54" s="81"/>
+      <c r="K54" s="108"/>
+      <c r="L54" s="81"/>
+      <c r="N54" s="83"/>
       <c r="O54" s="81"/>
       <c r="P54" s="81"/>
-      <c r="W54" s="83"/>
-      <c r="X54" s="81"/>
+      <c r="Q54" s="81"/>
+      <c r="X54" s="83"/>
       <c r="Y54" s="81"/>
-    </row>
-    <row r="55" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="Z54" s="81"/>
+    </row>
+    <row r="55" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B55" s="86"/>
-      <c r="C55" s="81"/>
+      <c r="C55" s="86"/>
       <c r="D55" s="81"/>
       <c r="E55" s="81"/>
       <c r="F55" s="81"/>
-      <c r="G55" s="82"/>
+      <c r="G55" s="81"/>
       <c r="H55" s="82"/>
-      <c r="I55" s="81"/>
-      <c r="J55" s="108"/>
-      <c r="K55" s="81"/>
-      <c r="M55" s="83"/>
-      <c r="N55" s="81"/>
+      <c r="I55" s="82"/>
+      <c r="J55" s="81"/>
+      <c r="K55" s="108"/>
+      <c r="L55" s="81"/>
+      <c r="N55" s="83"/>
       <c r="O55" s="81"/>
       <c r="P55" s="81"/>
-      <c r="W55" s="83"/>
-      <c r="X55" s="81"/>
+      <c r="Q55" s="81"/>
+      <c r="X55" s="83"/>
       <c r="Y55" s="81"/>
-    </row>
-    <row r="56" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="Z55" s="81"/>
+    </row>
+    <row r="56" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B56" s="86"/>
-      <c r="C56" s="81"/>
+      <c r="C56" s="86"/>
       <c r="D56" s="81"/>
       <c r="E56" s="81"/>
       <c r="F56" s="81"/>
-      <c r="G56" s="82"/>
+      <c r="G56" s="81"/>
       <c r="H56" s="82"/>
-      <c r="I56" s="81"/>
-      <c r="J56" s="108"/>
-      <c r="K56" s="81"/>
-      <c r="M56" s="83"/>
-      <c r="N56" s="81"/>
+      <c r="I56" s="82"/>
+      <c r="J56" s="81"/>
+      <c r="K56" s="108"/>
+      <c r="L56" s="81"/>
+      <c r="N56" s="83"/>
       <c r="O56" s="81"/>
       <c r="P56" s="81"/>
-      <c r="W56" s="83"/>
-      <c r="X56" s="81"/>
+      <c r="Q56" s="81"/>
+      <c r="X56" s="83"/>
       <c r="Y56" s="81"/>
-    </row>
-    <row r="57" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="Z56" s="81"/>
+    </row>
+    <row r="57" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B57" s="86"/>
-      <c r="C57" s="81"/>
+      <c r="C57" s="86"/>
       <c r="D57" s="81"/>
       <c r="E57" s="81"/>
       <c r="F57" s="81"/>
-      <c r="G57" s="82"/>
+      <c r="G57" s="81"/>
       <c r="H57" s="82"/>
-      <c r="I57" s="81"/>
-      <c r="J57" s="108"/>
-      <c r="K57" s="81"/>
-      <c r="M57" s="83"/>
-      <c r="N57" s="81"/>
+      <c r="I57" s="82"/>
+      <c r="J57" s="81"/>
+      <c r="K57" s="108"/>
+      <c r="L57" s="81"/>
+      <c r="N57" s="83"/>
       <c r="O57" s="81"/>
       <c r="P57" s="81"/>
-      <c r="W57" s="83"/>
-      <c r="X57" s="81"/>
+      <c r="Q57" s="81"/>
+      <c r="X57" s="83"/>
       <c r="Y57" s="81"/>
-    </row>
-    <row r="58" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="Z57" s="81"/>
+    </row>
+    <row r="58" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B58" s="86"/>
-      <c r="C58" s="81"/>
+      <c r="C58" s="86"/>
       <c r="D58" s="81"/>
       <c r="E58" s="81"/>
       <c r="F58" s="81"/>
-      <c r="G58" s="82"/>
+      <c r="G58" s="81"/>
       <c r="H58" s="82"/>
-      <c r="I58" s="81"/>
-      <c r="J58" s="108"/>
-      <c r="K58" s="81"/>
-      <c r="M58" s="83"/>
-      <c r="N58" s="81"/>
+      <c r="I58" s="82"/>
+      <c r="J58" s="81"/>
+      <c r="K58" s="108"/>
+      <c r="L58" s="81"/>
+      <c r="N58" s="83"/>
       <c r="O58" s="81"/>
       <c r="P58" s="81"/>
-      <c r="W58" s="83"/>
-      <c r="X58" s="81"/>
+      <c r="Q58" s="81"/>
+      <c r="X58" s="83"/>
       <c r="Y58" s="81"/>
-    </row>
-    <row r="59" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="Z58" s="81"/>
+    </row>
+    <row r="59" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B59" s="86"/>
-      <c r="C59" s="81"/>
+      <c r="C59" s="86"/>
       <c r="D59" s="81"/>
       <c r="E59" s="81"/>
       <c r="F59" s="81"/>
-      <c r="G59" s="82"/>
+      <c r="G59" s="81"/>
       <c r="H59" s="82"/>
-      <c r="I59" s="81"/>
-      <c r="J59" s="108"/>
-      <c r="K59" s="81"/>
-      <c r="M59" s="83"/>
-      <c r="N59" s="81"/>
+      <c r="I59" s="82"/>
+      <c r="J59" s="81"/>
+      <c r="K59" s="108"/>
+      <c r="L59" s="81"/>
+      <c r="N59" s="83"/>
       <c r="O59" s="81"/>
       <c r="P59" s="81"/>
-      <c r="W59" s="83"/>
-      <c r="X59" s="81"/>
+      <c r="Q59" s="81"/>
+      <c r="X59" s="83"/>
       <c r="Y59" s="81"/>
-    </row>
-    <row r="60" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="Z59" s="81"/>
+    </row>
+    <row r="60" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B60" s="86"/>
-      <c r="C60" s="81"/>
+      <c r="C60" s="86"/>
       <c r="D60" s="81"/>
       <c r="E60" s="81"/>
       <c r="F60" s="81"/>
-      <c r="G60" s="82"/>
+      <c r="G60" s="81"/>
       <c r="H60" s="82"/>
-      <c r="I60" s="81"/>
-      <c r="J60" s="108"/>
-      <c r="K60" s="81"/>
-      <c r="M60" s="83"/>
-      <c r="N60" s="81"/>
+      <c r="I60" s="82"/>
+      <c r="J60" s="81"/>
+      <c r="K60" s="108"/>
+      <c r="L60" s="81"/>
+      <c r="N60" s="83"/>
       <c r="O60" s="81"/>
       <c r="P60" s="81"/>
-      <c r="W60" s="83"/>
-      <c r="X60" s="81"/>
+      <c r="Q60" s="81"/>
+      <c r="X60" s="83"/>
       <c r="Y60" s="81"/>
-    </row>
-    <row r="61" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="Z60" s="81"/>
+    </row>
+    <row r="61" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B61" s="86"/>
-      <c r="C61" s="81"/>
+      <c r="C61" s="86"/>
       <c r="D61" s="81"/>
       <c r="E61" s="81"/>
       <c r="F61" s="81"/>
-      <c r="G61" s="82"/>
+      <c r="G61" s="81"/>
       <c r="H61" s="82"/>
-      <c r="I61" s="81"/>
-      <c r="J61" s="108"/>
-      <c r="K61" s="81"/>
-      <c r="M61" s="83"/>
-      <c r="N61" s="81"/>
+      <c r="I61" s="82"/>
+      <c r="J61" s="81"/>
+      <c r="K61" s="108"/>
+      <c r="L61" s="81"/>
+      <c r="N61" s="83"/>
       <c r="O61" s="81"/>
       <c r="P61" s="81"/>
-      <c r="W61" s="83"/>
-      <c r="X61" s="81"/>
+      <c r="Q61" s="81"/>
+      <c r="X61" s="83"/>
       <c r="Y61" s="81"/>
-    </row>
-    <row r="62" spans="2:25" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z61" s="81"/>
+    </row>
+    <row r="62" spans="2:26" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B62" s="86"/>
-      <c r="C62" s="81"/>
+      <c r="C62" s="86"/>
       <c r="D62" s="81"/>
       <c r="E62" s="81"/>
       <c r="F62" s="81"/>
-      <c r="G62" s="82"/>
+      <c r="G62" s="81"/>
       <c r="H62" s="82"/>
-      <c r="I62" s="81"/>
-      <c r="J62" s="108"/>
-      <c r="K62" s="81"/>
-      <c r="M62" s="83"/>
-      <c r="N62" s="81"/>
+      <c r="I62" s="82"/>
+      <c r="J62" s="81"/>
+      <c r="K62" s="108"/>
+      <c r="L62" s="81"/>
+      <c r="N62" s="83"/>
       <c r="O62" s="81"/>
       <c r="P62" s="81"/>
-      <c r="W62" s="83"/>
-      <c r="X62" s="81"/>
+      <c r="Q62" s="81"/>
+      <c r="X62" s="83"/>
       <c r="Y62" s="81"/>
-    </row>
-    <row r="63" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="Z62" s="81"/>
+    </row>
+    <row r="63" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B63" s="86"/>
-      <c r="C63" s="81"/>
+      <c r="C63" s="86"/>
       <c r="D63" s="81"/>
       <c r="E63" s="81"/>
       <c r="F63" s="81"/>
-      <c r="G63" s="82"/>
+      <c r="G63" s="81"/>
       <c r="H63" s="82"/>
-      <c r="I63" s="81"/>
-      <c r="J63" s="108"/>
-      <c r="K63" s="81"/>
-      <c r="M63" s="83"/>
-      <c r="N63" s="81"/>
+      <c r="I63" s="82"/>
+      <c r="J63" s="81"/>
+      <c r="K63" s="108"/>
+      <c r="L63" s="81"/>
+      <c r="N63" s="83"/>
       <c r="O63" s="81"/>
       <c r="P63" s="81"/>
-      <c r="W63" s="83"/>
-      <c r="X63" s="81"/>
+      <c r="Q63" s="81"/>
+      <c r="X63" s="83"/>
       <c r="Y63" s="81"/>
-    </row>
-    <row r="64" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="Z63" s="81"/>
+    </row>
+    <row r="64" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B64" s="86"/>
-      <c r="C64" s="81"/>
+      <c r="C64" s="86"/>
       <c r="D64" s="81"/>
       <c r="E64" s="81"/>
       <c r="F64" s="81"/>
-      <c r="G64" s="82"/>
+      <c r="G64" s="81"/>
       <c r="H64" s="82"/>
-      <c r="I64" s="81"/>
-      <c r="J64" s="108"/>
-      <c r="K64" s="81"/>
-      <c r="M64" s="83"/>
-      <c r="N64" s="81"/>
+      <c r="I64" s="82"/>
+      <c r="J64" s="81"/>
+      <c r="K64" s="108"/>
+      <c r="L64" s="81"/>
+      <c r="N64" s="83"/>
       <c r="O64" s="81"/>
       <c r="P64" s="81"/>
-      <c r="W64" s="83"/>
-      <c r="X64" s="81"/>
+      <c r="Q64" s="81"/>
+      <c r="X64" s="83"/>
       <c r="Y64" s="81"/>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="Z64" s="81"/>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B65" s="86"/>
-      <c r="C65" s="81"/>
+      <c r="C65" s="86"/>
       <c r="D65" s="81"/>
       <c r="E65" s="81"/>
       <c r="F65" s="81"/>
-      <c r="G65" s="82"/>
+      <c r="G65" s="81"/>
       <c r="H65" s="82"/>
-      <c r="I65" s="81"/>
-      <c r="J65" s="108"/>
-      <c r="K65" s="81"/>
-      <c r="M65" s="83"/>
-      <c r="N65" s="81"/>
+      <c r="I65" s="82"/>
+      <c r="J65" s="81"/>
+      <c r="K65" s="108"/>
+      <c r="L65" s="81"/>
+      <c r="N65" s="83"/>
       <c r="O65" s="81"/>
       <c r="P65" s="81"/>
-      <c r="W65" s="83"/>
-      <c r="X65" s="81"/>
+      <c r="Q65" s="81"/>
+      <c r="X65" s="83"/>
       <c r="Y65" s="81"/>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="Z65" s="81"/>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B66" s="86"/>
-      <c r="C66" s="81"/>
+      <c r="C66" s="86"/>
       <c r="D66" s="81"/>
       <c r="E66" s="81"/>
       <c r="F66" s="81"/>
-      <c r="G66" s="82"/>
+      <c r="G66" s="81"/>
       <c r="H66" s="82"/>
-      <c r="I66" s="81"/>
-      <c r="J66" s="108"/>
-      <c r="K66" s="81"/>
-      <c r="M66" s="83"/>
-      <c r="N66" s="81"/>
+      <c r="I66" s="82"/>
+      <c r="J66" s="81"/>
+      <c r="K66" s="108"/>
+      <c r="L66" s="81"/>
+      <c r="N66" s="83"/>
       <c r="O66" s="81"/>
       <c r="P66" s="81"/>
-      <c r="W66" s="83"/>
-      <c r="X66" s="81"/>
+      <c r="Q66" s="81"/>
+      <c r="X66" s="83"/>
       <c r="Y66" s="81"/>
-    </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="Z66" s="81"/>
+    </row>
+    <row r="67" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B67" s="86"/>
-      <c r="C67" s="81"/>
+      <c r="C67" s="86"/>
       <c r="D67" s="81"/>
       <c r="E67" s="81"/>
       <c r="F67" s="81"/>
-      <c r="G67" s="82"/>
+      <c r="G67" s="81"/>
       <c r="H67" s="82"/>
-      <c r="I67" s="81"/>
-      <c r="J67" s="108"/>
-      <c r="K67" s="81"/>
-      <c r="M67" s="83"/>
-      <c r="N67" s="81"/>
+      <c r="I67" s="82"/>
+      <c r="J67" s="81"/>
+      <c r="K67" s="108"/>
+      <c r="L67" s="81"/>
+      <c r="N67" s="83"/>
       <c r="O67" s="81"/>
       <c r="P67" s="81"/>
-      <c r="W67" s="83"/>
-      <c r="X67" s="81"/>
+      <c r="Q67" s="81"/>
+      <c r="X67" s="83"/>
       <c r="Y67" s="81"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="Z67" s="81"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B68" s="86"/>
-      <c r="C68" s="81"/>
+      <c r="C68" s="86"/>
       <c r="D68" s="81"/>
       <c r="E68" s="81"/>
       <c r="F68" s="81"/>
-      <c r="G68" s="82"/>
+      <c r="G68" s="81"/>
       <c r="H68" s="82"/>
-      <c r="I68" s="81"/>
-      <c r="J68" s="108"/>
-      <c r="K68" s="81"/>
-      <c r="M68" s="83"/>
-      <c r="N68" s="81"/>
+      <c r="I68" s="82"/>
+      <c r="J68" s="81"/>
+      <c r="K68" s="108"/>
+      <c r="L68" s="81"/>
+      <c r="N68" s="83"/>
       <c r="O68" s="81"/>
       <c r="P68" s="81"/>
-      <c r="W68" s="83"/>
-      <c r="X68" s="81"/>
+      <c r="Q68" s="81"/>
+      <c r="X68" s="83"/>
       <c r="Y68" s="81"/>
-    </row>
-    <row r="69" spans="2:25" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z68" s="81"/>
+    </row>
+    <row r="69" spans="2:26" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B69" s="86"/>
-      <c r="C69" s="81"/>
+      <c r="C69" s="86"/>
       <c r="D69" s="81"/>
       <c r="E69" s="81"/>
       <c r="F69" s="81"/>
-      <c r="G69" s="82"/>
+      <c r="G69" s="81"/>
       <c r="H69" s="82"/>
-      <c r="I69" s="81"/>
-      <c r="J69" s="108"/>
-      <c r="K69" s="81"/>
-      <c r="M69" s="83"/>
-      <c r="N69" s="81"/>
+      <c r="I69" s="82"/>
+      <c r="J69" s="81"/>
+      <c r="K69" s="108"/>
+      <c r="L69" s="81"/>
+      <c r="N69" s="83"/>
       <c r="O69" s="81"/>
       <c r="P69" s="81"/>
-      <c r="W69" s="83"/>
-      <c r="X69" s="81"/>
+      <c r="Q69" s="81"/>
+      <c r="X69" s="83"/>
       <c r="Y69" s="81"/>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="Z69" s="81"/>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B70" s="86"/>
-      <c r="C70" s="81"/>
+      <c r="C70" s="86"/>
       <c r="D70" s="81"/>
       <c r="E70" s="81"/>
       <c r="F70" s="81"/>
-      <c r="G70" s="82"/>
+      <c r="G70" s="81"/>
       <c r="H70" s="82"/>
-      <c r="I70" s="81"/>
-      <c r="J70" s="108"/>
-      <c r="K70" s="81"/>
-      <c r="M70" s="83"/>
-      <c r="N70" s="81"/>
+      <c r="I70" s="82"/>
+      <c r="J70" s="81"/>
+      <c r="K70" s="108"/>
+      <c r="L70" s="81"/>
+      <c r="N70" s="83"/>
       <c r="O70" s="81"/>
       <c r="P70" s="81"/>
-      <c r="W70" s="83"/>
-      <c r="X70" s="81"/>
+      <c r="Q70" s="81"/>
+      <c r="X70" s="83"/>
       <c r="Y70" s="81"/>
-    </row>
-    <row r="71" spans="2:25" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z70" s="81"/>
+    </row>
+    <row r="71" spans="2:26" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B71" s="86"/>
-      <c r="C71" s="81"/>
+      <c r="C71" s="86"/>
       <c r="D71" s="81"/>
       <c r="E71" s="81"/>
       <c r="F71" s="81"/>
-      <c r="G71" s="82"/>
+      <c r="G71" s="81"/>
       <c r="H71" s="82"/>
-      <c r="I71" s="81"/>
-      <c r="J71" s="108"/>
-      <c r="K71" s="81"/>
-      <c r="M71" s="83"/>
-      <c r="N71" s="81"/>
+      <c r="I71" s="82"/>
+      <c r="J71" s="81"/>
+      <c r="K71" s="108"/>
+      <c r="L71" s="81"/>
+      <c r="N71" s="83"/>
       <c r="O71" s="81"/>
       <c r="P71" s="81"/>
-      <c r="W71" s="83"/>
-      <c r="X71" s="81"/>
+      <c r="Q71" s="81"/>
+      <c r="X71" s="83"/>
       <c r="Y71" s="81"/>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="Z71" s="81"/>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B72" s="86"/>
-      <c r="C72" s="81"/>
+      <c r="C72" s="86"/>
       <c r="D72" s="81"/>
       <c r="E72" s="81"/>
       <c r="F72" s="81"/>
-      <c r="G72" s="82"/>
+      <c r="G72" s="81"/>
       <c r="H72" s="82"/>
-      <c r="I72" s="81"/>
-      <c r="J72" s="108"/>
-      <c r="K72" s="81"/>
-      <c r="M72" s="83"/>
-      <c r="N72" s="81"/>
+      <c r="I72" s="82"/>
+      <c r="J72" s="81"/>
+      <c r="K72" s="108"/>
+      <c r="L72" s="81"/>
+      <c r="N72" s="83"/>
       <c r="O72" s="81"/>
       <c r="P72" s="81"/>
-      <c r="W72" s="83"/>
-      <c r="X72" s="81"/>
+      <c r="Q72" s="81"/>
+      <c r="X72" s="83"/>
       <c r="Y72" s="81"/>
-    </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="Z72" s="81"/>
+    </row>
+    <row r="73" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B73" s="86"/>
-      <c r="C73" s="81"/>
+      <c r="C73" s="86"/>
       <c r="D73" s="81"/>
       <c r="E73" s="81"/>
       <c r="F73" s="81"/>
-      <c r="G73" s="82"/>
+      <c r="G73" s="81"/>
       <c r="H73" s="82"/>
-      <c r="I73" s="81"/>
-      <c r="J73" s="108"/>
-      <c r="K73" s="81"/>
-      <c r="M73" s="83"/>
-      <c r="N73" s="81"/>
+      <c r="I73" s="82"/>
+      <c r="J73" s="81"/>
+      <c r="K73" s="108"/>
+      <c r="L73" s="81"/>
+      <c r="N73" s="83"/>
       <c r="O73" s="81"/>
       <c r="P73" s="81"/>
-      <c r="W73" s="83"/>
-      <c r="X73" s="81"/>
+      <c r="Q73" s="81"/>
+      <c r="X73" s="83"/>
       <c r="Y73" s="81"/>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="Z73" s="81"/>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B74" s="86"/>
-      <c r="C74" s="81"/>
+      <c r="C74" s="86"/>
       <c r="D74" s="81"/>
       <c r="E74" s="81"/>
       <c r="F74" s="81"/>
-      <c r="G74" s="82"/>
+      <c r="G74" s="81"/>
       <c r="H74" s="82"/>
-      <c r="I74" s="81"/>
-      <c r="J74" s="108"/>
-      <c r="K74" s="81"/>
-      <c r="M74" s="83"/>
-      <c r="N74" s="81"/>
+      <c r="I74" s="82"/>
+      <c r="J74" s="81"/>
+      <c r="K74" s="108"/>
+      <c r="L74" s="81"/>
+      <c r="N74" s="83"/>
       <c r="O74" s="81"/>
       <c r="P74" s="81"/>
-      <c r="W74" s="83"/>
-      <c r="X74" s="81"/>
+      <c r="Q74" s="81"/>
+      <c r="X74" s="83"/>
       <c r="Y74" s="81"/>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="Z74" s="81"/>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B75" s="86"/>
-      <c r="C75" s="81"/>
+      <c r="C75" s="86"/>
       <c r="D75" s="81"/>
       <c r="E75" s="81"/>
       <c r="F75" s="81"/>
-      <c r="G75" s="82"/>
+      <c r="G75" s="81"/>
       <c r="H75" s="82"/>
-      <c r="I75" s="81"/>
-      <c r="J75" s="108"/>
-      <c r="K75" s="81"/>
-      <c r="M75" s="83"/>
-      <c r="N75" s="81"/>
+      <c r="I75" s="82"/>
+      <c r="J75" s="81"/>
+      <c r="K75" s="108"/>
+      <c r="L75" s="81"/>
+      <c r="N75" s="83"/>
       <c r="O75" s="81"/>
       <c r="P75" s="81"/>
-      <c r="W75" s="83"/>
-      <c r="X75" s="81"/>
+      <c r="Q75" s="81"/>
+      <c r="X75" s="83"/>
       <c r="Y75" s="81"/>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="Z75" s="81"/>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B76" s="86"/>
-      <c r="C76" s="81"/>
+      <c r="C76" s="86"/>
       <c r="D76" s="81"/>
       <c r="E76" s="81"/>
       <c r="F76" s="81"/>
-      <c r="G76" s="82"/>
+      <c r="G76" s="81"/>
       <c r="H76" s="82"/>
-      <c r="I76" s="81"/>
-      <c r="J76" s="108"/>
-      <c r="K76" s="81"/>
-      <c r="M76" s="83"/>
-      <c r="N76" s="81"/>
+      <c r="I76" s="82"/>
+      <c r="J76" s="81"/>
+      <c r="K76" s="108"/>
+      <c r="L76" s="81"/>
+      <c r="N76" s="83"/>
       <c r="O76" s="81"/>
       <c r="P76" s="81"/>
-      <c r="W76" s="83"/>
-      <c r="X76" s="81"/>
+      <c r="Q76" s="81"/>
+      <c r="X76" s="83"/>
       <c r="Y76" s="81"/>
-    </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="Z76" s="81"/>
+    </row>
+    <row r="77" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B77" s="86"/>
-      <c r="C77" s="81"/>
+      <c r="C77" s="86"/>
       <c r="D77" s="81"/>
       <c r="E77" s="81"/>
       <c r="F77" s="81"/>
-      <c r="G77" s="82"/>
+      <c r="G77" s="81"/>
       <c r="H77" s="82"/>
-      <c r="I77" s="81"/>
-      <c r="J77" s="108"/>
-      <c r="K77" s="81"/>
-      <c r="M77" s="83"/>
-      <c r="N77" s="81"/>
+      <c r="I77" s="82"/>
+      <c r="J77" s="81"/>
+      <c r="K77" s="108"/>
+      <c r="L77" s="81"/>
+      <c r="N77" s="83"/>
       <c r="O77" s="81"/>
       <c r="P77" s="81"/>
-      <c r="W77" s="83"/>
-      <c r="X77" s="81"/>
+      <c r="Q77" s="81"/>
+      <c r="X77" s="83"/>
       <c r="Y77" s="81"/>
-    </row>
-    <row r="78" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="Z77" s="81"/>
+    </row>
+    <row r="78" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B78" s="86"/>
-      <c r="C78" s="81"/>
+      <c r="C78" s="86"/>
       <c r="D78" s="81"/>
       <c r="E78" s="81"/>
       <c r="F78" s="81"/>
-      <c r="G78" s="82"/>
+      <c r="G78" s="81"/>
       <c r="H78" s="82"/>
-      <c r="I78" s="81"/>
-      <c r="J78" s="108"/>
-      <c r="K78" s="81"/>
-      <c r="M78" s="83"/>
-      <c r="N78" s="81"/>
+      <c r="I78" s="82"/>
+      <c r="J78" s="81"/>
+      <c r="K78" s="108"/>
+      <c r="L78" s="81"/>
+      <c r="N78" s="83"/>
       <c r="O78" s="81"/>
       <c r="P78" s="81"/>
-      <c r="W78" s="83"/>
-      <c r="X78" s="81"/>
+      <c r="Q78" s="81"/>
+      <c r="X78" s="83"/>
       <c r="Y78" s="81"/>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="Z78" s="81"/>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B79" s="86"/>
-      <c r="C79" s="81"/>
+      <c r="C79" s="86"/>
       <c r="D79" s="81"/>
       <c r="E79" s="81"/>
       <c r="F79" s="81"/>
-      <c r="G79" s="82"/>
+      <c r="G79" s="81"/>
       <c r="H79" s="82"/>
-      <c r="I79" s="81"/>
-      <c r="J79" s="108"/>
-      <c r="K79" s="81"/>
-      <c r="M79" s="83"/>
-      <c r="N79" s="81"/>
+      <c r="I79" s="82"/>
+      <c r="J79" s="81"/>
+      <c r="K79" s="108"/>
+      <c r="L79" s="81"/>
+      <c r="N79" s="83"/>
       <c r="O79" s="81"/>
       <c r="P79" s="81"/>
-      <c r="W79" s="83"/>
-      <c r="X79" s="81"/>
+      <c r="Q79" s="81"/>
+      <c r="X79" s="83"/>
       <c r="Y79" s="81"/>
-    </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="Z79" s="81"/>
+    </row>
+    <row r="80" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B80" s="86"/>
-      <c r="C80" s="81"/>
+      <c r="C80" s="86"/>
       <c r="D80" s="81"/>
       <c r="E80" s="81"/>
       <c r="F80" s="81"/>
-      <c r="G80" s="82"/>
+      <c r="G80" s="81"/>
       <c r="H80" s="82"/>
-      <c r="I80" s="81"/>
-      <c r="J80" s="108"/>
-      <c r="K80" s="81"/>
-      <c r="M80" s="83"/>
-      <c r="N80" s="81"/>
+      <c r="I80" s="82"/>
+      <c r="J80" s="81"/>
+      <c r="K80" s="108"/>
+      <c r="L80" s="81"/>
+      <c r="N80" s="83"/>
       <c r="O80" s="81"/>
       <c r="P80" s="81"/>
-      <c r="W80" s="83"/>
-      <c r="X80" s="81"/>
+      <c r="Q80" s="81"/>
+      <c r="X80" s="83"/>
       <c r="Y80" s="81"/>
-    </row>
-    <row r="81" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="Z80" s="81"/>
+    </row>
+    <row r="81" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B81" s="86"/>
-      <c r="C81" s="81"/>
+      <c r="C81" s="86"/>
       <c r="D81" s="81"/>
       <c r="E81" s="81"/>
       <c r="F81" s="81"/>
-      <c r="G81" s="82"/>
+      <c r="G81" s="81"/>
       <c r="H81" s="82"/>
-      <c r="I81" s="81"/>
-      <c r="J81" s="108"/>
-      <c r="K81" s="81"/>
-      <c r="M81" s="83"/>
-      <c r="N81" s="81"/>
+      <c r="I81" s="82"/>
+      <c r="J81" s="81"/>
+      <c r="K81" s="108"/>
+      <c r="L81" s="81"/>
+      <c r="N81" s="83"/>
       <c r="O81" s="81"/>
       <c r="P81" s="81"/>
-      <c r="W81" s="83"/>
-      <c r="X81" s="81"/>
+      <c r="Q81" s="81"/>
+      <c r="X81" s="83"/>
       <c r="Y81" s="81"/>
-    </row>
-    <row r="82" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="Z81" s="81"/>
+    </row>
+    <row r="82" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B82" s="86"/>
-      <c r="C82" s="81"/>
+      <c r="C82" s="86"/>
       <c r="D82" s="81"/>
       <c r="E82" s="81"/>
       <c r="F82" s="81"/>
-      <c r="G82" s="82"/>
+      <c r="G82" s="81"/>
       <c r="H82" s="82"/>
-      <c r="I82" s="81"/>
-      <c r="J82" s="108"/>
-      <c r="K82" s="81"/>
-      <c r="M82" s="83"/>
-      <c r="N82" s="81"/>
+      <c r="I82" s="82"/>
+      <c r="J82" s="81"/>
+      <c r="K82" s="108"/>
+      <c r="L82" s="81"/>
+      <c r="N82" s="83"/>
       <c r="O82" s="81"/>
       <c r="P82" s="81"/>
-      <c r="W82" s="83"/>
-      <c r="X82" s="81"/>
+      <c r="Q82" s="81"/>
+      <c r="X82" s="83"/>
       <c r="Y82" s="81"/>
-    </row>
-    <row r="83" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="Z82" s="81"/>
+    </row>
+    <row r="83" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B83" s="86"/>
-      <c r="C83" s="81"/>
+      <c r="C83" s="86"/>
       <c r="D83" s="81"/>
       <c r="E83" s="81"/>
       <c r="F83" s="81"/>
-      <c r="G83" s="82"/>
+      <c r="G83" s="81"/>
       <c r="H83" s="82"/>
-      <c r="I83" s="81"/>
-      <c r="J83" s="108"/>
-      <c r="K83" s="81"/>
-      <c r="M83" s="83"/>
-      <c r="N83" s="81"/>
+      <c r="I83" s="82"/>
+      <c r="J83" s="81"/>
+      <c r="K83" s="108"/>
+      <c r="L83" s="81"/>
+      <c r="N83" s="83"/>
       <c r="O83" s="81"/>
       <c r="P83" s="81"/>
-      <c r="W83" s="83"/>
-      <c r="X83" s="81"/>
+      <c r="Q83" s="81"/>
+      <c r="X83" s="83"/>
       <c r="Y83" s="81"/>
-    </row>
-    <row r="84" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="Z83" s="81"/>
+    </row>
+    <row r="84" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B84" s="86"/>
-      <c r="C84" s="81"/>
+      <c r="C84" s="86"/>
       <c r="D84" s="81"/>
       <c r="E84" s="81"/>
       <c r="F84" s="81"/>
-      <c r="G84" s="82"/>
+      <c r="G84" s="81"/>
       <c r="H84" s="82"/>
-      <c r="I84" s="81"/>
-      <c r="J84" s="108"/>
-      <c r="K84" s="81"/>
-      <c r="M84" s="83"/>
-      <c r="N84" s="81"/>
+      <c r="I84" s="82"/>
+      <c r="J84" s="81"/>
+      <c r="K84" s="108"/>
+      <c r="L84" s="81"/>
+      <c r="N84" s="83"/>
       <c r="O84" s="81"/>
       <c r="P84" s="81"/>
-      <c r="W84" s="83"/>
-      <c r="X84" s="81"/>
+      <c r="Q84" s="81"/>
+      <c r="X84" s="83"/>
       <c r="Y84" s="81"/>
-    </row>
-    <row r="85" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="Z84" s="81"/>
+    </row>
+    <row r="85" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B85" s="86"/>
-      <c r="C85" s="81"/>
+      <c r="C85" s="86"/>
       <c r="D85" s="81"/>
       <c r="E85" s="81"/>
       <c r="F85" s="81"/>
-      <c r="G85" s="82"/>
+      <c r="G85" s="81"/>
       <c r="H85" s="82"/>
-      <c r="I85" s="81"/>
-      <c r="J85" s="108"/>
-      <c r="K85" s="81"/>
-      <c r="M85" s="83"/>
-      <c r="N85" s="81"/>
+      <c r="I85" s="82"/>
+      <c r="J85" s="81"/>
+      <c r="K85" s="108"/>
+      <c r="L85" s="81"/>
+      <c r="N85" s="83"/>
       <c r="O85" s="81"/>
       <c r="P85" s="81"/>
-      <c r="W85" s="83"/>
-      <c r="X85" s="81"/>
+      <c r="Q85" s="81"/>
+      <c r="X85" s="83"/>
       <c r="Y85" s="81"/>
-    </row>
-    <row r="86" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="Z85" s="81"/>
+    </row>
+    <row r="86" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B86" s="86"/>
-      <c r="C86" s="81"/>
+      <c r="C86" s="86"/>
       <c r="D86" s="81"/>
       <c r="E86" s="81"/>
       <c r="F86" s="81"/>
-      <c r="G86" s="82"/>
+      <c r="G86" s="81"/>
       <c r="H86" s="82"/>
-      <c r="I86" s="81"/>
-      <c r="J86" s="108"/>
-      <c r="K86" s="81"/>
-      <c r="M86" s="83"/>
-      <c r="N86" s="81"/>
+      <c r="I86" s="82"/>
+      <c r="J86" s="81"/>
+      <c r="K86" s="108"/>
+      <c r="L86" s="81"/>
+      <c r="N86" s="83"/>
       <c r="O86" s="81"/>
       <c r="P86" s="81"/>
-      <c r="W86" s="83"/>
-      <c r="X86" s="81"/>
+      <c r="Q86" s="81"/>
+      <c r="X86" s="83"/>
       <c r="Y86" s="81"/>
-    </row>
-    <row r="87" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="Z86" s="81"/>
+    </row>
+    <row r="87" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B87" s="86"/>
-      <c r="C87" s="81"/>
+      <c r="C87" s="86"/>
       <c r="D87" s="81"/>
       <c r="E87" s="81"/>
       <c r="F87" s="81"/>
-      <c r="G87" s="82"/>
+      <c r="G87" s="81"/>
       <c r="H87" s="82"/>
-      <c r="I87" s="81"/>
-      <c r="J87" s="108"/>
-      <c r="K87" s="81"/>
-      <c r="M87" s="83"/>
-      <c r="N87" s="81"/>
+      <c r="I87" s="82"/>
+      <c r="J87" s="81"/>
+      <c r="K87" s="108"/>
+      <c r="L87" s="81"/>
+      <c r="N87" s="83"/>
       <c r="O87" s="81"/>
       <c r="P87" s="81"/>
-      <c r="W87" s="83"/>
-      <c r="X87" s="81"/>
+      <c r="Q87" s="81"/>
+      <c r="X87" s="83"/>
       <c r="Y87" s="81"/>
-    </row>
-    <row r="88" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="Z87" s="81"/>
+    </row>
+    <row r="88" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B88" s="86"/>
-      <c r="C88" s="81"/>
+      <c r="C88" s="86"/>
       <c r="D88" s="81"/>
       <c r="E88" s="81"/>
       <c r="F88" s="81"/>
-      <c r="G88" s="82"/>
+      <c r="G88" s="81"/>
       <c r="H88" s="82"/>
-      <c r="I88" s="81"/>
-      <c r="J88" s="108"/>
-      <c r="K88" s="81"/>
-      <c r="M88" s="83"/>
-      <c r="N88" s="81"/>
+      <c r="I88" s="82"/>
+      <c r="J88" s="81"/>
+      <c r="K88" s="108"/>
+      <c r="L88" s="81"/>
+      <c r="N88" s="83"/>
       <c r="O88" s="81"/>
       <c r="P88" s="81"/>
-      <c r="W88" s="83"/>
-      <c r="X88" s="81"/>
+      <c r="Q88" s="81"/>
+      <c r="X88" s="83"/>
       <c r="Y88" s="81"/>
-    </row>
-    <row r="89" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="Z88" s="81"/>
+    </row>
+    <row r="89" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B89" s="86"/>
-      <c r="C89" s="81"/>
+      <c r="C89" s="86"/>
       <c r="D89" s="81"/>
       <c r="E89" s="81"/>
       <c r="F89" s="81"/>
-      <c r="G89" s="82"/>
+      <c r="G89" s="81"/>
       <c r="H89" s="82"/>
-      <c r="I89" s="81"/>
-      <c r="J89" s="108"/>
-      <c r="K89" s="81"/>
-      <c r="M89" s="83"/>
-      <c r="N89" s="81"/>
+      <c r="I89" s="82"/>
+      <c r="J89" s="81"/>
+      <c r="K89" s="108"/>
+      <c r="L89" s="81"/>
+      <c r="N89" s="83"/>
       <c r="O89" s="81"/>
       <c r="P89" s="81"/>
-      <c r="W89" s="83"/>
-      <c r="X89" s="81"/>
+      <c r="Q89" s="81"/>
+      <c r="X89" s="83"/>
       <c r="Y89" s="81"/>
-    </row>
-    <row r="90" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="Z89" s="81"/>
+    </row>
+    <row r="90" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B90" s="86"/>
-      <c r="C90" s="81"/>
+      <c r="C90" s="86"/>
       <c r="D90" s="81"/>
       <c r="E90" s="81"/>
       <c r="F90" s="81"/>
-      <c r="G90" s="82"/>
+      <c r="G90" s="81"/>
       <c r="H90" s="82"/>
-      <c r="I90" s="81"/>
-      <c r="J90" s="108"/>
-      <c r="K90" s="81"/>
-      <c r="M90" s="83"/>
-      <c r="N90" s="81"/>
+      <c r="I90" s="82"/>
+      <c r="J90" s="81"/>
+      <c r="K90" s="108"/>
+      <c r="L90" s="81"/>
+      <c r="N90" s="83"/>
       <c r="O90" s="81"/>
       <c r="P90" s="81"/>
-      <c r="W90" s="83"/>
-      <c r="X90" s="81"/>
+      <c r="Q90" s="81"/>
+      <c r="X90" s="83"/>
       <c r="Y90" s="81"/>
-    </row>
-    <row r="91" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="Z90" s="81"/>
+    </row>
+    <row r="91" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B91" s="86"/>
-      <c r="C91" s="81"/>
+      <c r="C91" s="86"/>
       <c r="D91" s="81"/>
       <c r="E91" s="81"/>
       <c r="F91" s="81"/>
-      <c r="G91" s="82"/>
+      <c r="G91" s="81"/>
       <c r="H91" s="82"/>
-      <c r="I91" s="81"/>
-      <c r="J91" s="108"/>
-      <c r="K91" s="81"/>
-      <c r="M91" s="83"/>
-      <c r="N91" s="81"/>
+      <c r="I91" s="82"/>
+      <c r="J91" s="81"/>
+      <c r="K91" s="108"/>
+      <c r="L91" s="81"/>
+      <c r="N91" s="83"/>
       <c r="O91" s="81"/>
       <c r="P91" s="81"/>
-      <c r="W91" s="83"/>
-      <c r="X91" s="81"/>
+      <c r="Q91" s="81"/>
+      <c r="X91" s="83"/>
       <c r="Y91" s="81"/>
-    </row>
-    <row r="92" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="Z91" s="81"/>
+    </row>
+    <row r="92" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B92" s="86"/>
-      <c r="C92" s="81"/>
+      <c r="C92" s="86"/>
       <c r="D92" s="81"/>
       <c r="E92" s="81"/>
       <c r="F92" s="81"/>
-      <c r="G92" s="82"/>
+      <c r="G92" s="81"/>
       <c r="H92" s="82"/>
-      <c r="I92" s="81"/>
-      <c r="J92" s="108"/>
-      <c r="K92" s="81"/>
-      <c r="M92" s="83"/>
-      <c r="N92" s="81"/>
+      <c r="I92" s="82"/>
+      <c r="J92" s="81"/>
+      <c r="K92" s="108"/>
+      <c r="L92" s="81"/>
+      <c r="N92" s="83"/>
       <c r="O92" s="81"/>
       <c r="P92" s="81"/>
-      <c r="W92" s="83"/>
-      <c r="X92" s="81"/>
+      <c r="Q92" s="81"/>
+      <c r="X92" s="83"/>
       <c r="Y92" s="81"/>
-    </row>
-    <row r="93" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="Z92" s="81"/>
+    </row>
+    <row r="93" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B93" s="86"/>
-      <c r="C93" s="81"/>
+      <c r="C93" s="86"/>
       <c r="D93" s="81"/>
       <c r="E93" s="81"/>
       <c r="F93" s="81"/>
-      <c r="G93" s="82"/>
+      <c r="G93" s="81"/>
       <c r="H93" s="82"/>
-      <c r="I93" s="81"/>
-      <c r="J93" s="108"/>
-      <c r="K93" s="81"/>
-      <c r="M93" s="83"/>
-      <c r="N93" s="81"/>
+      <c r="I93" s="82"/>
+      <c r="J93" s="81"/>
+      <c r="K93" s="108"/>
+      <c r="L93" s="81"/>
+      <c r="N93" s="83"/>
       <c r="O93" s="81"/>
       <c r="P93" s="81"/>
-      <c r="W93" s="83"/>
-      <c r="X93" s="81"/>
+      <c r="Q93" s="81"/>
+      <c r="X93" s="83"/>
       <c r="Y93" s="81"/>
-    </row>
-    <row r="94" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="Z93" s="81"/>
+    </row>
+    <row r="94" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B94" s="86"/>
-      <c r="C94" s="81"/>
+      <c r="C94" s="86"/>
       <c r="D94" s="81"/>
       <c r="E94" s="81"/>
       <c r="F94" s="81"/>
-      <c r="G94" s="82"/>
+      <c r="G94" s="81"/>
       <c r="H94" s="82"/>
-      <c r="I94" s="81"/>
-      <c r="J94" s="108"/>
-      <c r="K94" s="81"/>
-      <c r="M94" s="83"/>
-      <c r="N94" s="81"/>
+      <c r="I94" s="82"/>
+      <c r="J94" s="81"/>
+      <c r="K94" s="108"/>
+      <c r="L94" s="81"/>
+      <c r="N94" s="83"/>
       <c r="O94" s="81"/>
       <c r="P94" s="81"/>
-      <c r="W94" s="83"/>
-      <c r="X94" s="81"/>
+      <c r="Q94" s="81"/>
+      <c r="X94" s="83"/>
       <c r="Y94" s="81"/>
-    </row>
-    <row r="95" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="Z94" s="81"/>
+    </row>
+    <row r="95" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B95" s="86"/>
-      <c r="C95" s="81"/>
+      <c r="C95" s="86"/>
       <c r="D95" s="81"/>
       <c r="E95" s="81"/>
       <c r="F95" s="81"/>
-      <c r="G95" s="82"/>
+      <c r="G95" s="81"/>
       <c r="H95" s="82"/>
-      <c r="I95" s="81"/>
-      <c r="J95" s="108"/>
-      <c r="K95" s="81"/>
-      <c r="M95" s="83"/>
-      <c r="N95" s="81"/>
+      <c r="I95" s="82"/>
+      <c r="J95" s="81"/>
+      <c r="K95" s="108"/>
+      <c r="L95" s="81"/>
+      <c r="N95" s="83"/>
       <c r="O95" s="81"/>
       <c r="P95" s="81"/>
-      <c r="W95" s="83"/>
-      <c r="X95" s="81"/>
+      <c r="Q95" s="81"/>
+      <c r="X95" s="83"/>
       <c r="Y95" s="81"/>
-    </row>
-    <row r="96" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="Z95" s="81"/>
+    </row>
+    <row r="96" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B96" s="86"/>
-      <c r="C96" s="81"/>
+      <c r="C96" s="86"/>
       <c r="D96" s="81"/>
       <c r="E96" s="81"/>
       <c r="F96" s="81"/>
-      <c r="G96" s="82"/>
+      <c r="G96" s="81"/>
       <c r="H96" s="82"/>
-      <c r="I96" s="81"/>
-      <c r="J96" s="108"/>
-      <c r="K96" s="81"/>
-      <c r="M96" s="83"/>
-      <c r="N96" s="81"/>
+      <c r="I96" s="82"/>
+      <c r="J96" s="81"/>
+      <c r="K96" s="108"/>
+      <c r="L96" s="81"/>
+      <c r="N96" s="83"/>
       <c r="O96" s="81"/>
       <c r="P96" s="81"/>
-      <c r="W96" s="83"/>
-      <c r="X96" s="81"/>
+      <c r="Q96" s="81"/>
+      <c r="X96" s="83"/>
       <c r="Y96" s="81"/>
-    </row>
-    <row r="97" spans="2:25" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z96" s="81"/>
+    </row>
+    <row r="97" spans="2:26" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B97" s="86"/>
-      <c r="C97" s="81"/>
+      <c r="C97" s="86"/>
       <c r="D97" s="81"/>
       <c r="E97" s="81"/>
       <c r="F97" s="81"/>
-      <c r="G97" s="82"/>
+      <c r="G97" s="81"/>
       <c r="H97" s="82"/>
-      <c r="I97" s="81"/>
-      <c r="J97" s="108"/>
-      <c r="K97" s="81"/>
-      <c r="M97" s="83"/>
-      <c r="N97" s="81"/>
+      <c r="I97" s="82"/>
+      <c r="J97" s="81"/>
+      <c r="K97" s="108"/>
+      <c r="L97" s="81"/>
+      <c r="N97" s="83"/>
       <c r="O97" s="81"/>
       <c r="P97" s="81"/>
-      <c r="W97" s="83"/>
-      <c r="X97" s="81"/>
+      <c r="Q97" s="81"/>
+      <c r="X97" s="83"/>
       <c r="Y97" s="81"/>
-    </row>
-    <row r="98" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="Z97" s="81"/>
+    </row>
+    <row r="98" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B98" s="86"/>
-      <c r="C98" s="81"/>
+      <c r="C98" s="86"/>
       <c r="D98" s="81"/>
       <c r="E98" s="81"/>
       <c r="F98" s="81"/>
-      <c r="G98" s="82"/>
+      <c r="G98" s="81"/>
       <c r="H98" s="82"/>
-      <c r="I98" s="81"/>
-      <c r="J98" s="108"/>
-      <c r="K98" s="81"/>
-      <c r="M98" s="83"/>
-      <c r="N98" s="81"/>
+      <c r="I98" s="82"/>
+      <c r="J98" s="81"/>
+      <c r="K98" s="108"/>
+      <c r="L98" s="81"/>
+      <c r="N98" s="83"/>
       <c r="O98" s="81"/>
       <c r="P98" s="81"/>
-      <c r="W98" s="83"/>
-      <c r="X98" s="81"/>
+      <c r="Q98" s="81"/>
+      <c r="X98" s="83"/>
       <c r="Y98" s="81"/>
-    </row>
-    <row r="99" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="Z98" s="81"/>
+    </row>
+    <row r="99" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B99" s="86"/>
-      <c r="C99" s="81"/>
+      <c r="C99" s="86"/>
       <c r="D99" s="81"/>
       <c r="E99" s="81"/>
       <c r="F99" s="81"/>
-      <c r="G99" s="82"/>
+      <c r="G99" s="81"/>
       <c r="H99" s="82"/>
-      <c r="I99" s="81"/>
-      <c r="J99" s="108"/>
-      <c r="K99" s="81"/>
-      <c r="M99" s="83"/>
-      <c r="N99" s="81"/>
+      <c r="I99" s="82"/>
+      <c r="J99" s="81"/>
+      <c r="K99" s="108"/>
+      <c r="L99" s="81"/>
+      <c r="N99" s="83"/>
       <c r="O99" s="81"/>
       <c r="P99" s="81"/>
-      <c r="W99" s="83"/>
-      <c r="X99" s="81"/>
+      <c r="Q99" s="81"/>
+      <c r="X99" s="83"/>
       <c r="Y99" s="81"/>
-    </row>
-    <row r="100" spans="2:25" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z99" s="81"/>
+    </row>
+    <row r="100" spans="2:26" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B100" s="86"/>
-      <c r="C100" s="81"/>
+      <c r="C100" s="86"/>
       <c r="D100" s="81"/>
       <c r="E100" s="81"/>
       <c r="F100" s="81"/>
-      <c r="G100" s="82"/>
+      <c r="G100" s="81"/>
       <c r="H100" s="82"/>
-      <c r="I100" s="81"/>
-      <c r="J100" s="108"/>
-      <c r="K100" s="81"/>
-      <c r="M100" s="83"/>
-      <c r="N100" s="81"/>
+      <c r="I100" s="82"/>
+      <c r="J100" s="81"/>
+      <c r="K100" s="108"/>
+      <c r="L100" s="81"/>
+      <c r="N100" s="83"/>
       <c r="O100" s="81"/>
       <c r="P100" s="81"/>
-      <c r="W100" s="83"/>
-      <c r="X100" s="81"/>
+      <c r="Q100" s="81"/>
+      <c r="X100" s="83"/>
       <c r="Y100" s="81"/>
-    </row>
-    <row r="101" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="Z100" s="81"/>
+    </row>
+    <row r="101" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B101" s="86"/>
-      <c r="C101" s="81"/>
+      <c r="C101" s="86"/>
       <c r="D101" s="81"/>
       <c r="E101" s="81"/>
       <c r="F101" s="81"/>
-      <c r="G101" s="82"/>
+      <c r="G101" s="81"/>
       <c r="H101" s="82"/>
-      <c r="I101" s="81"/>
-      <c r="J101" s="108"/>
-      <c r="K101" s="81"/>
-      <c r="M101" s="83"/>
-      <c r="N101" s="81"/>
+      <c r="I101" s="82"/>
+      <c r="J101" s="81"/>
+      <c r="K101" s="108"/>
+      <c r="L101" s="81"/>
+      <c r="N101" s="83"/>
       <c r="O101" s="81"/>
       <c r="P101" s="81"/>
-      <c r="W101" s="83"/>
-      <c r="X101" s="81"/>
+      <c r="Q101" s="81"/>
+      <c r="X101" s="83"/>
       <c r="Y101" s="81"/>
-    </row>
-    <row r="102" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="Z101" s="81"/>
+    </row>
+    <row r="102" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B102" s="86"/>
-      <c r="C102" s="81"/>
+      <c r="C102" s="86"/>
       <c r="D102" s="81"/>
       <c r="E102" s="81"/>
       <c r="F102" s="81"/>
-      <c r="G102" s="82"/>
+      <c r="G102" s="81"/>
       <c r="H102" s="82"/>
-      <c r="I102" s="81"/>
-      <c r="J102" s="108"/>
-      <c r="K102" s="81"/>
-      <c r="M102" s="83"/>
-      <c r="N102" s="81"/>
+      <c r="I102" s="82"/>
+      <c r="J102" s="81"/>
+      <c r="K102" s="108"/>
+      <c r="L102" s="81"/>
+      <c r="N102" s="83"/>
       <c r="O102" s="81"/>
       <c r="P102" s="81"/>
-      <c r="W102" s="83"/>
-      <c r="X102" s="81"/>
+      <c r="Q102" s="81"/>
+      <c r="X102" s="83"/>
       <c r="Y102" s="81"/>
-    </row>
-    <row r="103" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="Z102" s="81"/>
+    </row>
+    <row r="103" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B103" s="86"/>
-      <c r="C103" s="81"/>
+      <c r="C103" s="86"/>
       <c r="D103" s="81"/>
       <c r="E103" s="81"/>
       <c r="F103" s="81"/>
-      <c r="G103" s="82"/>
+      <c r="G103" s="81"/>
       <c r="H103" s="82"/>
-      <c r="I103" s="81"/>
-      <c r="J103" s="108"/>
-      <c r="K103" s="81"/>
-      <c r="M103" s="83"/>
-      <c r="N103" s="81"/>
+      <c r="I103" s="82"/>
+      <c r="J103" s="81"/>
+      <c r="K103" s="108"/>
+      <c r="L103" s="81"/>
+      <c r="N103" s="83"/>
       <c r="O103" s="81"/>
       <c r="P103" s="81"/>
-      <c r="W103" s="83"/>
-      <c r="X103" s="81"/>
+      <c r="Q103" s="81"/>
+      <c r="X103" s="83"/>
       <c r="Y103" s="81"/>
-    </row>
-    <row r="104" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="Z103" s="81"/>
+    </row>
+    <row r="104" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B104" s="86"/>
-      <c r="C104" s="81"/>
+      <c r="C104" s="86"/>
       <c r="D104" s="81"/>
       <c r="E104" s="81"/>
       <c r="F104" s="81"/>
-      <c r="G104" s="82"/>
+      <c r="G104" s="81"/>
       <c r="H104" s="82"/>
-      <c r="I104" s="81"/>
-      <c r="J104" s="108"/>
-      <c r="K104" s="81"/>
-      <c r="M104" s="83"/>
-      <c r="N104" s="81"/>
+      <c r="I104" s="82"/>
+      <c r="J104" s="81"/>
+      <c r="K104" s="108"/>
+      <c r="L104" s="81"/>
+      <c r="N104" s="83"/>
       <c r="O104" s="81"/>
       <c r="P104" s="81"/>
-      <c r="W104" s="83"/>
-      <c r="X104" s="81"/>
+      <c r="Q104" s="81"/>
+      <c r="X104" s="83"/>
       <c r="Y104" s="81"/>
-    </row>
-    <row r="105" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="Z104" s="81"/>
+    </row>
+    <row r="105" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B105" s="86"/>
-      <c r="C105" s="81"/>
+      <c r="C105" s="86"/>
       <c r="D105" s="81"/>
       <c r="E105" s="81"/>
       <c r="F105" s="81"/>
-      <c r="G105" s="82"/>
+      <c r="G105" s="81"/>
       <c r="H105" s="82"/>
-      <c r="I105" s="81"/>
-      <c r="J105" s="108"/>
-      <c r="K105" s="81"/>
-    </row>
-    <row r="106" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="I105" s="82"/>
+      <c r="J105" s="81"/>
+      <c r="K105" s="108"/>
+      <c r="L105" s="81"/>
+    </row>
+    <row r="106" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B106" s="86"/>
-      <c r="C106" s="81"/>
+      <c r="C106" s="86"/>
       <c r="D106" s="81"/>
       <c r="E106" s="81"/>
       <c r="F106" s="81"/>
-      <c r="G106" s="82"/>
+      <c r="G106" s="81"/>
       <c r="H106" s="82"/>
-      <c r="I106" s="81"/>
-      <c r="J106" s="108"/>
-      <c r="K106" s="81"/>
-    </row>
-    <row r="107" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="I106" s="82"/>
+      <c r="J106" s="81"/>
+      <c r="K106" s="108"/>
+      <c r="L106" s="81"/>
+    </row>
+    <row r="107" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B107" s="86"/>
-      <c r="C107" s="81"/>
+      <c r="C107" s="86"/>
       <c r="D107" s="81"/>
       <c r="E107" s="81"/>
       <c r="F107" s="81"/>
-      <c r="G107" s="82"/>
+      <c r="G107" s="81"/>
       <c r="H107" s="82"/>
-      <c r="I107" s="81"/>
-      <c r="J107" s="108"/>
-      <c r="K107" s="81"/>
-    </row>
-    <row r="108" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="I107" s="82"/>
+      <c r="J107" s="81"/>
+      <c r="K107" s="108"/>
+      <c r="L107" s="81"/>
+    </row>
+    <row r="108" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B108" s="86"/>
-      <c r="C108" s="81"/>
+      <c r="C108" s="86"/>
       <c r="D108" s="81"/>
       <c r="E108" s="81"/>
       <c r="F108" s="81"/>
-      <c r="G108" s="82"/>
+      <c r="G108" s="81"/>
       <c r="H108" s="82"/>
-      <c r="I108" s="81"/>
-      <c r="J108" s="108"/>
-      <c r="K108" s="81"/>
-    </row>
-    <row r="109" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="I108" s="82"/>
+      <c r="J108" s="81"/>
+      <c r="K108" s="108"/>
+      <c r="L108" s="81"/>
+    </row>
+    <row r="109" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B109" s="86"/>
-      <c r="C109" s="81"/>
+      <c r="C109" s="86"/>
       <c r="D109" s="81"/>
       <c r="E109" s="81"/>
       <c r="F109" s="81"/>
-      <c r="G109" s="82"/>
+      <c r="G109" s="81"/>
       <c r="H109" s="82"/>
-      <c r="I109" s="81"/>
-      <c r="J109" s="108"/>
-      <c r="K109" s="81"/>
-    </row>
-    <row r="110" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="I109" s="82"/>
+      <c r="J109" s="81"/>
+      <c r="K109" s="108"/>
+      <c r="L109" s="81"/>
+    </row>
+    <row r="110" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B110" s="86"/>
-      <c r="C110" s="81"/>
+      <c r="C110" s="86"/>
       <c r="D110" s="81"/>
       <c r="E110" s="81"/>
       <c r="F110" s="81"/>
-      <c r="G110" s="82"/>
+      <c r="G110" s="81"/>
       <c r="H110" s="82"/>
-      <c r="I110" s="81"/>
-      <c r="J110" s="108"/>
-      <c r="K110" s="81"/>
-    </row>
-    <row r="111" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="I110" s="82"/>
+      <c r="J110" s="81"/>
+      <c r="K110" s="108"/>
+      <c r="L110" s="81"/>
+    </row>
+    <row r="111" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B111" s="86"/>
-      <c r="C111" s="81"/>
+      <c r="C111" s="86"/>
       <c r="D111" s="81"/>
       <c r="E111" s="81"/>
       <c r="F111" s="81"/>
-      <c r="G111" s="82"/>
+      <c r="G111" s="81"/>
       <c r="H111" s="82"/>
-      <c r="I111" s="81"/>
-      <c r="J111" s="108"/>
-      <c r="K111" s="81"/>
-    </row>
-    <row r="112" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="I111" s="82"/>
+      <c r="J111" s="81"/>
+      <c r="K111" s="108"/>
+      <c r="L111" s="81"/>
+    </row>
+    <row r="112" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B112" s="86"/>
-      <c r="C112" s="81"/>
+      <c r="C112" s="86"/>
       <c r="D112" s="81"/>
       <c r="E112" s="81"/>
       <c r="F112" s="81"/>
-      <c r="G112" s="82"/>
+      <c r="G112" s="81"/>
       <c r="H112" s="82"/>
-      <c r="I112" s="81"/>
-      <c r="J112" s="108"/>
-      <c r="K112" s="81"/>
-    </row>
-    <row r="113" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="I112" s="82"/>
+      <c r="J112" s="81"/>
+      <c r="K112" s="108"/>
+      <c r="L112" s="81"/>
+    </row>
+    <row r="113" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B113" s="86"/>
-      <c r="C113" s="81"/>
+      <c r="C113" s="86"/>
       <c r="D113" s="81"/>
       <c r="E113" s="81"/>
       <c r="F113" s="81"/>
-      <c r="G113" s="82"/>
+      <c r="G113" s="81"/>
       <c r="H113" s="82"/>
-      <c r="I113" s="81"/>
-      <c r="J113" s="108"/>
-      <c r="K113" s="81"/>
-    </row>
-    <row r="114" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="I113" s="82"/>
+      <c r="J113" s="81"/>
+      <c r="K113" s="108"/>
+      <c r="L113" s="81"/>
+    </row>
+    <row r="114" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B114" s="86"/>
-      <c r="C114" s="81"/>
+      <c r="C114" s="86"/>
       <c r="D114" s="81"/>
       <c r="E114" s="81"/>
       <c r="F114" s="81"/>
-      <c r="G114" s="82"/>
+      <c r="G114" s="81"/>
       <c r="H114" s="82"/>
-      <c r="I114" s="81"/>
-      <c r="J114" s="108"/>
-      <c r="K114" s="81"/>
-    </row>
-    <row r="115" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="I114" s="82"/>
+      <c r="J114" s="81"/>
+      <c r="K114" s="108"/>
+      <c r="L114" s="81"/>
+    </row>
+    <row r="115" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B115" s="86"/>
-      <c r="C115" s="81"/>
+      <c r="C115" s="86"/>
       <c r="D115" s="81"/>
       <c r="E115" s="81"/>
       <c r="F115" s="81"/>
-      <c r="G115" s="82"/>
+      <c r="G115" s="81"/>
       <c r="H115" s="82"/>
-      <c r="I115" s="81"/>
-      <c r="J115" s="108"/>
-      <c r="K115" s="81"/>
-    </row>
-    <row r="116" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="I115" s="82"/>
+      <c r="J115" s="81"/>
+      <c r="K115" s="108"/>
+      <c r="L115" s="81"/>
+    </row>
+    <row r="116" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B116" s="86"/>
-      <c r="C116" s="81"/>
+      <c r="C116" s="86"/>
       <c r="D116" s="81"/>
       <c r="E116" s="81"/>
       <c r="F116" s="81"/>
-      <c r="G116" s="82"/>
+      <c r="G116" s="81"/>
       <c r="H116" s="82"/>
-      <c r="I116" s="81"/>
-      <c r="J116" s="108"/>
-      <c r="K116" s="81"/>
-    </row>
-    <row r="117" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="I116" s="82"/>
+      <c r="J116" s="81"/>
+      <c r="K116" s="108"/>
+      <c r="L116" s="81"/>
+    </row>
+    <row r="117" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B117" s="86"/>
-      <c r="C117" s="81"/>
+      <c r="C117" s="86"/>
       <c r="D117" s="81"/>
       <c r="E117" s="81"/>
       <c r="F117" s="81"/>
-      <c r="G117" s="82"/>
+      <c r="G117" s="81"/>
       <c r="H117" s="82"/>
-      <c r="I117" s="81"/>
-      <c r="J117" s="108"/>
-      <c r="K117" s="81"/>
-    </row>
-    <row r="118" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="I117" s="82"/>
+      <c r="J117" s="81"/>
+      <c r="K117" s="108"/>
+      <c r="L117" s="81"/>
+    </row>
+    <row r="118" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B118" s="86"/>
-      <c r="C118" s="81"/>
+      <c r="C118" s="86"/>
       <c r="D118" s="81"/>
       <c r="E118" s="81"/>
       <c r="F118" s="81"/>
-      <c r="G118" s="82"/>
+      <c r="G118" s="81"/>
       <c r="H118" s="82"/>
-      <c r="I118" s="81"/>
-      <c r="J118" s="108"/>
-      <c r="K118" s="81"/>
-    </row>
-    <row r="119" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="I118" s="82"/>
+      <c r="J118" s="81"/>
+      <c r="K118" s="108"/>
+      <c r="L118" s="81"/>
+    </row>
+    <row r="119" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B119" s="86"/>
-      <c r="C119" s="81"/>
+      <c r="C119" s="86"/>
       <c r="D119" s="81"/>
       <c r="E119" s="81"/>
       <c r="F119" s="81"/>
-      <c r="G119" s="82"/>
+      <c r="G119" s="81"/>
       <c r="H119" s="82"/>
-      <c r="I119" s="81"/>
-      <c r="J119" s="108"/>
-      <c r="K119" s="81"/>
-    </row>
-    <row r="120" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="I119" s="82"/>
+      <c r="J119" s="81"/>
+      <c r="K119" s="108"/>
+      <c r="L119" s="81"/>
+    </row>
+    <row r="120" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B120" s="86"/>
-      <c r="C120" s="81"/>
+      <c r="C120" s="86"/>
       <c r="D120" s="81"/>
       <c r="E120" s="81"/>
       <c r="F120" s="81"/>
-      <c r="G120" s="82"/>
+      <c r="G120" s="81"/>
       <c r="H120" s="82"/>
-      <c r="I120" s="81"/>
-      <c r="J120" s="108"/>
-      <c r="K120" s="81"/>
-    </row>
-    <row r="121" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="I120" s="82"/>
+      <c r="J120" s="81"/>
+      <c r="K120" s="108"/>
+      <c r="L120" s="81"/>
+    </row>
+    <row r="121" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B121" s="86"/>
-      <c r="C121" s="81"/>
+      <c r="C121" s="86"/>
       <c r="D121" s="81"/>
       <c r="E121" s="81"/>
       <c r="F121" s="81"/>
-      <c r="G121" s="82"/>
+      <c r="G121" s="81"/>
       <c r="H121" s="82"/>
-      <c r="I121" s="81"/>
-      <c r="J121" s="108"/>
-      <c r="K121" s="81"/>
-    </row>
-    <row r="122" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="I121" s="82"/>
+      <c r="J121" s="81"/>
+      <c r="K121" s="108"/>
+      <c r="L121" s="81"/>
+    </row>
+    <row r="122" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B122" s="86"/>
-      <c r="C122" s="81"/>
+      <c r="C122" s="86"/>
       <c r="D122" s="81"/>
       <c r="E122" s="81"/>
       <c r="F122" s="81"/>
-      <c r="G122" s="82"/>
+      <c r="G122" s="81"/>
       <c r="H122" s="82"/>
-      <c r="I122" s="81"/>
-      <c r="J122" s="108"/>
-      <c r="K122" s="81"/>
-    </row>
-    <row r="123" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="I122" s="82"/>
+      <c r="J122" s="81"/>
+      <c r="K122" s="108"/>
+      <c r="L122" s="81"/>
+    </row>
+    <row r="123" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B123" s="86"/>
-      <c r="C123" s="81"/>
+      <c r="C123" s="86"/>
       <c r="D123" s="81"/>
       <c r="E123" s="81"/>
       <c r="F123" s="81"/>
-      <c r="G123" s="82"/>
+      <c r="G123" s="81"/>
       <c r="H123" s="82"/>
-      <c r="I123" s="81"/>
-      <c r="J123" s="108"/>
-      <c r="K123" s="81"/>
-    </row>
-    <row r="124" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="I123" s="82"/>
+      <c r="J123" s="81"/>
+      <c r="K123" s="108"/>
+      <c r="L123" s="81"/>
+    </row>
+    <row r="124" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B124" s="86"/>
-      <c r="C124" s="81"/>
+      <c r="C124" s="86"/>
       <c r="D124" s="81"/>
       <c r="E124" s="81"/>
       <c r="F124" s="81"/>
-      <c r="G124" s="82"/>
+      <c r="G124" s="81"/>
       <c r="H124" s="82"/>
-      <c r="I124" s="81"/>
-      <c r="J124" s="108"/>
-      <c r="K124" s="81"/>
-    </row>
-    <row r="125" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="I124" s="82"/>
+      <c r="J124" s="81"/>
+      <c r="K124" s="108"/>
+      <c r="L124" s="81"/>
+    </row>
+    <row r="125" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B125" s="86"/>
-      <c r="C125" s="81"/>
+      <c r="C125" s="86"/>
       <c r="D125" s="81"/>
       <c r="E125" s="81"/>
       <c r="F125" s="81"/>
-      <c r="G125" s="82"/>
+      <c r="G125" s="81"/>
       <c r="H125" s="82"/>
-      <c r="I125" s="81"/>
-      <c r="J125" s="108"/>
-      <c r="K125" s="81"/>
-    </row>
-    <row r="126" spans="2:11" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I125" s="82"/>
+      <c r="J125" s="81"/>
+      <c r="K125" s="108"/>
+      <c r="L125" s="81"/>
+    </row>
+    <row r="126" spans="2:12" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B126" s="86"/>
-      <c r="C126" s="81"/>
+      <c r="C126" s="86"/>
       <c r="D126" s="81"/>
       <c r="E126" s="81"/>
       <c r="F126" s="81"/>
-      <c r="G126" s="82"/>
+      <c r="G126" s="81"/>
       <c r="H126" s="82"/>
-      <c r="I126" s="81"/>
-      <c r="J126" s="108"/>
-      <c r="K126" s="81"/>
-    </row>
-    <row r="127" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="I126" s="82"/>
+      <c r="J126" s="81"/>
+      <c r="K126" s="108"/>
+      <c r="L126" s="81"/>
+    </row>
+    <row r="127" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B127" s="86"/>
-      <c r="C127" s="81"/>
+      <c r="C127" s="86"/>
       <c r="D127" s="81"/>
       <c r="E127" s="81"/>
       <c r="F127" s="81"/>
-      <c r="G127" s="82"/>
+      <c r="G127" s="81"/>
       <c r="H127" s="82"/>
-      <c r="I127" s="81"/>
-      <c r="J127" s="108"/>
-      <c r="K127" s="81"/>
-    </row>
-    <row r="128" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="I127" s="82"/>
+      <c r="J127" s="81"/>
+      <c r="K127" s="108"/>
+      <c r="L127" s="81"/>
+    </row>
+    <row r="128" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B128" s="86"/>
-      <c r="C128" s="81"/>
+      <c r="C128" s="86"/>
       <c r="D128" s="81"/>
       <c r="E128" s="81"/>
       <c r="F128" s="81"/>
-      <c r="G128" s="82"/>
+      <c r="G128" s="81"/>
       <c r="H128" s="82"/>
-      <c r="I128" s="81"/>
-      <c r="J128" s="108"/>
-      <c r="K128" s="81"/>
-    </row>
-    <row r="129" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="I128" s="82"/>
+      <c r="J128" s="81"/>
+      <c r="K128" s="108"/>
+      <c r="L128" s="81"/>
+    </row>
+    <row r="129" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B129" s="86"/>
-      <c r="C129" s="81"/>
+      <c r="C129" s="86"/>
       <c r="D129" s="81"/>
       <c r="E129" s="81"/>
       <c r="F129" s="81"/>
-      <c r="G129" s="82"/>
+      <c r="G129" s="81"/>
       <c r="H129" s="82"/>
-      <c r="I129" s="81"/>
-      <c r="J129" s="108"/>
-      <c r="K129" s="81"/>
-    </row>
-    <row r="130" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="I129" s="82"/>
+      <c r="J129" s="81"/>
+      <c r="K129" s="108"/>
+      <c r="L129" s="81"/>
+    </row>
+    <row r="130" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B130" s="86"/>
-      <c r="C130" s="81"/>
+      <c r="C130" s="86"/>
       <c r="D130" s="81"/>
       <c r="E130" s="81"/>
       <c r="F130" s="81"/>
-      <c r="G130" s="82"/>
+      <c r="G130" s="81"/>
       <c r="H130" s="82"/>
-      <c r="I130" s="81"/>
-      <c r="J130" s="108"/>
-      <c r="K130" s="81"/>
-    </row>
-    <row r="131" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="I130" s="82"/>
+      <c r="J130" s="81"/>
+      <c r="K130" s="108"/>
+      <c r="L130" s="81"/>
+    </row>
+    <row r="131" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B131" s="86"/>
-      <c r="C131" s="81"/>
+      <c r="C131" s="86"/>
       <c r="D131" s="81"/>
       <c r="E131" s="81"/>
       <c r="F131" s="81"/>
-      <c r="G131" s="82"/>
+      <c r="G131" s="81"/>
       <c r="H131" s="82"/>
-      <c r="I131" s="81"/>
-      <c r="J131" s="108"/>
-      <c r="K131" s="81"/>
-    </row>
-    <row r="132" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="I131" s="82"/>
+      <c r="J131" s="81"/>
+      <c r="K131" s="108"/>
+      <c r="L131" s="81"/>
+    </row>
+    <row r="132" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B132" s="86"/>
-      <c r="C132" s="81"/>
+      <c r="C132" s="86"/>
       <c r="D132" s="81"/>
       <c r="E132" s="81"/>
       <c r="F132" s="81"/>
-      <c r="G132" s="82"/>
+      <c r="G132" s="81"/>
       <c r="H132" s="82"/>
-      <c r="I132" s="81"/>
-      <c r="J132" s="108"/>
-      <c r="K132" s="81"/>
-    </row>
-    <row r="133" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="I132" s="82"/>
+      <c r="J132" s="81"/>
+      <c r="K132" s="108"/>
+      <c r="L132" s="81"/>
+    </row>
+    <row r="133" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B133" s="86"/>
-      <c r="C133" s="81"/>
+      <c r="C133" s="86"/>
       <c r="D133" s="81"/>
       <c r="E133" s="81"/>
       <c r="F133" s="81"/>
-      <c r="G133" s="82"/>
+      <c r="G133" s="81"/>
       <c r="H133" s="82"/>
-      <c r="I133" s="81"/>
-      <c r="J133" s="108"/>
-      <c r="K133" s="81"/>
-    </row>
-    <row r="134" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="I133" s="82"/>
+      <c r="J133" s="81"/>
+      <c r="K133" s="108"/>
+      <c r="L133" s="81"/>
+    </row>
+    <row r="134" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B134" s="86"/>
-      <c r="C134" s="81"/>
+      <c r="C134" s="86"/>
       <c r="D134" s="81"/>
       <c r="E134" s="81"/>
       <c r="F134" s="81"/>
-      <c r="G134" s="82"/>
+      <c r="G134" s="81"/>
       <c r="H134" s="82"/>
-      <c r="I134" s="81"/>
-      <c r="J134" s="108"/>
-      <c r="K134" s="81"/>
-    </row>
-    <row r="135" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="I134" s="82"/>
+      <c r="J134" s="81"/>
+      <c r="K134" s="108"/>
+      <c r="L134" s="81"/>
+    </row>
+    <row r="135" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B135" s="86"/>
-      <c r="C135" s="81"/>
+      <c r="C135" s="86"/>
       <c r="D135" s="81"/>
       <c r="E135" s="81"/>
       <c r="F135" s="81"/>
-      <c r="G135" s="82"/>
+      <c r="G135" s="81"/>
       <c r="H135" s="82"/>
-      <c r="I135" s="81"/>
-      <c r="J135" s="108"/>
-      <c r="K135" s="81"/>
-    </row>
-    <row r="136" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="I135" s="82"/>
+      <c r="J135" s="81"/>
+      <c r="K135" s="108"/>
+      <c r="L135" s="81"/>
+    </row>
+    <row r="136" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B136" s="86"/>
-      <c r="C136" s="81"/>
+      <c r="C136" s="86"/>
       <c r="D136" s="81"/>
       <c r="E136" s="81"/>
       <c r="F136" s="81"/>
-      <c r="G136" s="82"/>
+      <c r="G136" s="81"/>
       <c r="H136" s="82"/>
-      <c r="I136" s="81"/>
-      <c r="J136" s="108"/>
-      <c r="K136" s="81"/>
-    </row>
-    <row r="137" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="I136" s="82"/>
+      <c r="J136" s="81"/>
+      <c r="K136" s="108"/>
+      <c r="L136" s="81"/>
+    </row>
+    <row r="137" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B137" s="86"/>
-      <c r="C137" s="81"/>
+      <c r="C137" s="86"/>
       <c r="D137" s="81"/>
       <c r="E137" s="81"/>
       <c r="F137" s="81"/>
-      <c r="G137" s="82"/>
+      <c r="G137" s="81"/>
       <c r="H137" s="82"/>
-      <c r="I137" s="81"/>
-      <c r="J137" s="108"/>
-      <c r="K137" s="81"/>
-    </row>
-    <row r="138" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="I137" s="82"/>
+      <c r="J137" s="81"/>
+      <c r="K137" s="108"/>
+      <c r="L137" s="81"/>
+    </row>
+    <row r="138" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B138" s="86"/>
-      <c r="C138" s="81"/>
+      <c r="C138" s="86"/>
       <c r="D138" s="81"/>
       <c r="E138" s="81"/>
       <c r="F138" s="81"/>
-      <c r="G138" s="82"/>
+      <c r="G138" s="81"/>
       <c r="H138" s="82"/>
-      <c r="I138" s="81"/>
-      <c r="J138" s="108"/>
-      <c r="K138" s="81"/>
-    </row>
-    <row r="139" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="I138" s="82"/>
+      <c r="J138" s="81"/>
+      <c r="K138" s="108"/>
+      <c r="L138" s="81"/>
+    </row>
+    <row r="139" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B139" s="86"/>
-      <c r="C139" s="81"/>
+      <c r="C139" s="86"/>
       <c r="D139" s="81"/>
       <c r="E139" s="81"/>
       <c r="F139" s="81"/>
-      <c r="G139" s="82"/>
+      <c r="G139" s="81"/>
       <c r="H139" s="82"/>
-      <c r="I139" s="81"/>
-      <c r="J139" s="108"/>
-      <c r="K139" s="81"/>
-    </row>
-    <row r="140" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="I139" s="82"/>
+      <c r="J139" s="81"/>
+      <c r="K139" s="108"/>
+      <c r="L139" s="81"/>
+    </row>
+    <row r="140" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B140" s="86"/>
-      <c r="C140" s="81"/>
+      <c r="C140" s="86"/>
       <c r="D140" s="81"/>
       <c r="E140" s="81"/>
       <c r="F140" s="81"/>
-      <c r="G140" s="82"/>
+      <c r="G140" s="81"/>
       <c r="H140" s="82"/>
-      <c r="I140" s="81"/>
-      <c r="J140" s="108"/>
-      <c r="K140" s="81"/>
-    </row>
-    <row r="141" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="I140" s="82"/>
+      <c r="J140" s="81"/>
+      <c r="K140" s="108"/>
+      <c r="L140" s="81"/>
+    </row>
+    <row r="141" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B141" s="86"/>
-      <c r="C141" s="81"/>
+      <c r="C141" s="86"/>
       <c r="D141" s="81"/>
       <c r="E141" s="81"/>
       <c r="F141" s="81"/>
-      <c r="G141" s="82"/>
+      <c r="G141" s="81"/>
       <c r="H141" s="82"/>
-      <c r="I141" s="81"/>
-      <c r="J141" s="108"/>
-      <c r="K141" s="81"/>
-    </row>
-    <row r="142" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="I141" s="82"/>
+      <c r="J141" s="81"/>
+      <c r="K141" s="108"/>
+      <c r="L141" s="81"/>
+    </row>
+    <row r="142" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B142" s="86"/>
-      <c r="C142" s="81"/>
+      <c r="C142" s="86"/>
       <c r="D142" s="81"/>
       <c r="E142" s="81"/>
       <c r="F142" s="81"/>
-      <c r="G142" s="82"/>
+      <c r="G142" s="81"/>
       <c r="H142" s="82"/>
-      <c r="I142" s="81"/>
-      <c r="J142" s="108"/>
-      <c r="K142" s="81"/>
-    </row>
-    <row r="143" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="I142" s="82"/>
+      <c r="J142" s="81"/>
+      <c r="K142" s="108"/>
+      <c r="L142" s="81"/>
+    </row>
+    <row r="143" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B143" s="86"/>
-      <c r="C143" s="81"/>
+      <c r="C143" s="86"/>
       <c r="D143" s="81"/>
       <c r="E143" s="81"/>
       <c r="F143" s="81"/>
-      <c r="G143" s="82"/>
+      <c r="G143" s="81"/>
       <c r="H143" s="82"/>
-      <c r="I143" s="81"/>
-      <c r="J143" s="108"/>
-      <c r="K143" s="81"/>
-    </row>
-    <row r="144" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="I143" s="82"/>
+      <c r="J143" s="81"/>
+      <c r="K143" s="108"/>
+      <c r="L143" s="81"/>
+    </row>
+    <row r="144" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B144" s="86"/>
-      <c r="C144" s="81"/>
+      <c r="C144" s="86"/>
       <c r="D144" s="81"/>
       <c r="E144" s="81"/>
       <c r="F144" s="81"/>
-      <c r="G144" s="82"/>
+      <c r="G144" s="81"/>
       <c r="H144" s="82"/>
-      <c r="I144" s="81"/>
-      <c r="J144" s="108"/>
-      <c r="K144" s="81"/>
-    </row>
-    <row r="145" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="I144" s="82"/>
+      <c r="J144" s="81"/>
+      <c r="K144" s="108"/>
+      <c r="L144" s="81"/>
+    </row>
+    <row r="145" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B145" s="86"/>
-      <c r="C145" s="81"/>
+      <c r="C145" s="86"/>
       <c r="D145" s="81"/>
       <c r="E145" s="81"/>
       <c r="F145" s="81"/>
-      <c r="G145" s="82"/>
+      <c r="G145" s="81"/>
       <c r="H145" s="82"/>
-      <c r="I145" s="81"/>
-      <c r="J145" s="108"/>
-      <c r="K145" s="81"/>
-    </row>
-    <row r="146" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="I145" s="82"/>
+      <c r="J145" s="81"/>
+      <c r="K145" s="108"/>
+      <c r="L145" s="81"/>
+    </row>
+    <row r="146" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B146" s="86"/>
-      <c r="C146" s="81"/>
+      <c r="C146" s="86"/>
       <c r="D146" s="81"/>
       <c r="E146" s="81"/>
       <c r="F146" s="81"/>
-      <c r="G146" s="82"/>
+      <c r="G146" s="81"/>
       <c r="H146" s="82"/>
-      <c r="I146" s="81"/>
-      <c r="J146" s="108"/>
-      <c r="K146" s="81"/>
-    </row>
-    <row r="147" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="I146" s="82"/>
+      <c r="J146" s="81"/>
+      <c r="K146" s="108"/>
+      <c r="L146" s="81"/>
+    </row>
+    <row r="147" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B147" s="86"/>
-      <c r="C147" s="81"/>
+      <c r="C147" s="86"/>
       <c r="D147" s="81"/>
       <c r="E147" s="81"/>
       <c r="F147" s="81"/>
-      <c r="G147" s="82"/>
+      <c r="G147" s="81"/>
       <c r="H147" s="82"/>
-      <c r="I147" s="81"/>
-      <c r="J147" s="108"/>
-      <c r="K147" s="81"/>
-    </row>
-    <row r="148" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="I147" s="82"/>
+      <c r="J147" s="81"/>
+      <c r="K147" s="108"/>
+      <c r="L147" s="81"/>
+    </row>
+    <row r="148" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B148" s="86"/>
-      <c r="C148" s="81"/>
+      <c r="C148" s="86"/>
       <c r="D148" s="81"/>
       <c r="E148" s="81"/>
       <c r="F148" s="81"/>
-      <c r="G148" s="82"/>
+      <c r="G148" s="81"/>
       <c r="H148" s="82"/>
-      <c r="I148" s="81"/>
-      <c r="J148" s="108"/>
-      <c r="K148" s="81"/>
-    </row>
-    <row r="149" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="I148" s="82"/>
+      <c r="J148" s="81"/>
+      <c r="K148" s="108"/>
+      <c r="L148" s="81"/>
+    </row>
+    <row r="149" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B149" s="86"/>
-      <c r="C149" s="81"/>
+      <c r="C149" s="86"/>
       <c r="D149" s="81"/>
       <c r="E149" s="81"/>
       <c r="F149" s="81"/>
-      <c r="G149" s="82"/>
+      <c r="G149" s="81"/>
       <c r="H149" s="82"/>
-      <c r="I149" s="81"/>
-      <c r="J149" s="108"/>
-      <c r="K149" s="81"/>
-    </row>
-    <row r="150" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="I149" s="82"/>
+      <c r="J149" s="81"/>
+      <c r="K149" s="108"/>
+      <c r="L149" s="81"/>
+    </row>
+    <row r="150" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B150" s="86"/>
-      <c r="C150" s="81"/>
+      <c r="C150" s="86"/>
       <c r="D150" s="81"/>
       <c r="E150" s="81"/>
       <c r="F150" s="81"/>
-      <c r="G150" s="82"/>
+      <c r="G150" s="81"/>
       <c r="H150" s="82"/>
-      <c r="I150" s="81"/>
-      <c r="J150" s="108"/>
-      <c r="K150" s="81"/>
-    </row>
-    <row r="151" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="I150" s="82"/>
+      <c r="J150" s="81"/>
+      <c r="K150" s="108"/>
+      <c r="L150" s="81"/>
+    </row>
+    <row r="151" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B151" s="86"/>
-      <c r="C151" s="81"/>
+      <c r="C151" s="86"/>
       <c r="D151" s="81"/>
       <c r="E151" s="81"/>
       <c r="F151" s="81"/>
-      <c r="G151" s="82"/>
+      <c r="G151" s="81"/>
       <c r="H151" s="82"/>
-      <c r="I151" s="81"/>
-      <c r="J151" s="108"/>
-      <c r="K151" s="81"/>
-    </row>
-    <row r="152" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="I151" s="82"/>
+      <c r="J151" s="81"/>
+      <c r="K151" s="108"/>
+      <c r="L151" s="81"/>
+    </row>
+    <row r="152" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B152" s="86"/>
-      <c r="C152" s="81"/>
+      <c r="C152" s="86"/>
       <c r="D152" s="81"/>
       <c r="E152" s="81"/>
       <c r="F152" s="81"/>
-      <c r="G152" s="82"/>
+      <c r="G152" s="81"/>
       <c r="H152" s="82"/>
-      <c r="I152" s="81"/>
-      <c r="J152" s="108"/>
-      <c r="K152" s="81"/>
-    </row>
-    <row r="153" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="I152" s="82"/>
+      <c r="J152" s="81"/>
+      <c r="K152" s="108"/>
+      <c r="L152" s="81"/>
+    </row>
+    <row r="153" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B153" s="86"/>
-      <c r="C153" s="81"/>
+      <c r="C153" s="86"/>
       <c r="D153" s="81"/>
       <c r="E153" s="81"/>
       <c r="F153" s="81"/>
-      <c r="G153" s="82"/>
+      <c r="G153" s="81"/>
       <c r="H153" s="82"/>
-      <c r="I153" s="81"/>
-      <c r="J153" s="108"/>
-      <c r="K153" s="81"/>
-    </row>
-    <row r="154" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="I153" s="82"/>
+      <c r="J153" s="81"/>
+      <c r="K153" s="108"/>
+      <c r="L153" s="81"/>
+    </row>
+    <row r="154" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B154" s="86"/>
-      <c r="C154" s="81"/>
+      <c r="C154" s="86"/>
       <c r="D154" s="81"/>
       <c r="E154" s="81"/>
       <c r="F154" s="81"/>
-      <c r="G154" s="82"/>
+      <c r="G154" s="81"/>
       <c r="H154" s="82"/>
-      <c r="I154" s="81"/>
-      <c r="J154" s="108"/>
-      <c r="K154" s="81"/>
-    </row>
-    <row r="155" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="I154" s="82"/>
+      <c r="J154" s="81"/>
+      <c r="K154" s="108"/>
+      <c r="L154" s="81"/>
+    </row>
+    <row r="155" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B155" s="86"/>
-      <c r="C155" s="81"/>
+      <c r="C155" s="86"/>
       <c r="D155" s="81"/>
       <c r="E155" s="81"/>
       <c r="F155" s="81"/>
-      <c r="G155" s="82"/>
+      <c r="G155" s="81"/>
       <c r="H155" s="82"/>
-      <c r="I155" s="81"/>
-      <c r="J155" s="108"/>
-      <c r="K155" s="81"/>
-    </row>
-    <row r="156" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="I155" s="82"/>
+      <c r="J155" s="81"/>
+      <c r="K155" s="108"/>
+      <c r="L155" s="81"/>
+    </row>
+    <row r="156" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B156" s="86"/>
-      <c r="C156" s="81"/>
+      <c r="C156" s="86"/>
       <c r="D156" s="81"/>
       <c r="E156" s="81"/>
       <c r="F156" s="81"/>
-      <c r="G156" s="82"/>
+      <c r="G156" s="81"/>
       <c r="H156" s="82"/>
-      <c r="I156" s="81"/>
-      <c r="J156" s="108"/>
-      <c r="K156" s="81"/>
-    </row>
-    <row r="157" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="I156" s="82"/>
+      <c r="J156" s="81"/>
+      <c r="K156" s="108"/>
+      <c r="L156" s="81"/>
+    </row>
+    <row r="157" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B157" s="86"/>
-      <c r="C157" s="81"/>
+      <c r="C157" s="86"/>
       <c r="D157" s="81"/>
       <c r="E157" s="81"/>
       <c r="F157" s="81"/>
-      <c r="G157" s="82"/>
+      <c r="G157" s="81"/>
       <c r="H157" s="82"/>
-      <c r="I157" s="81"/>
-      <c r="J157" s="108"/>
-      <c r="K157" s="81"/>
-    </row>
-    <row r="158" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="I157" s="82"/>
+      <c r="J157" s="81"/>
+      <c r="K157" s="108"/>
+      <c r="L157" s="81"/>
+    </row>
+    <row r="158" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B158" s="86"/>
-      <c r="C158" s="81"/>
+      <c r="C158" s="86"/>
       <c r="D158" s="81"/>
       <c r="E158" s="81"/>
       <c r="F158" s="81"/>
-      <c r="G158" s="82"/>
+      <c r="G158" s="81"/>
       <c r="H158" s="82"/>
-      <c r="I158" s="81"/>
-      <c r="J158" s="108"/>
-      <c r="K158" s="81"/>
-    </row>
-    <row r="159" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="I158" s="82"/>
+      <c r="J158" s="81"/>
+      <c r="K158" s="108"/>
+      <c r="L158" s="81"/>
+    </row>
+    <row r="159" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B159" s="86"/>
-      <c r="C159" s="81"/>
+      <c r="C159" s="86"/>
       <c r="D159" s="81"/>
       <c r="E159" s="81"/>
       <c r="F159" s="81"/>
-      <c r="G159" s="82"/>
+      <c r="G159" s="81"/>
       <c r="H159" s="82"/>
-      <c r="I159" s="81"/>
-      <c r="J159" s="108"/>
-      <c r="K159" s="81"/>
-    </row>
-    <row r="160" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="I159" s="82"/>
+      <c r="J159" s="81"/>
+      <c r="K159" s="108"/>
+      <c r="L159" s="81"/>
+    </row>
+    <row r="160" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B160" s="86"/>
-      <c r="C160" s="81"/>
+      <c r="C160" s="86"/>
       <c r="D160" s="81"/>
       <c r="E160" s="81"/>
       <c r="F160" s="81"/>
-      <c r="G160" s="82"/>
+      <c r="G160" s="81"/>
       <c r="H160" s="82"/>
-      <c r="I160" s="81"/>
-      <c r="J160" s="108"/>
-      <c r="K160" s="81"/>
-    </row>
-    <row r="161" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="I160" s="82"/>
+      <c r="J160" s="81"/>
+      <c r="K160" s="108"/>
+      <c r="L160" s="81"/>
+    </row>
+    <row r="161" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B161" s="86"/>
-      <c r="C161" s="81"/>
+      <c r="C161" s="86"/>
       <c r="D161" s="81"/>
       <c r="E161" s="81"/>
       <c r="F161" s="81"/>
-      <c r="G161" s="82"/>
+      <c r="G161" s="81"/>
       <c r="H161" s="82"/>
-      <c r="I161" s="81"/>
-      <c r="J161" s="108"/>
-      <c r="K161" s="81"/>
-    </row>
-    <row r="162" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="I161" s="82"/>
+      <c r="J161" s="81"/>
+      <c r="K161" s="108"/>
+      <c r="L161" s="81"/>
+    </row>
+    <row r="162" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B162" s="86"/>
-      <c r="C162" s="81"/>
+      <c r="C162" s="86"/>
       <c r="D162" s="81"/>
       <c r="E162" s="81"/>
       <c r="F162" s="81"/>
-      <c r="G162" s="82"/>
+      <c r="G162" s="81"/>
       <c r="H162" s="82"/>
-      <c r="I162" s="81"/>
-      <c r="J162" s="108"/>
-      <c r="K162" s="81"/>
-    </row>
-    <row r="163" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="I162" s="82"/>
+      <c r="J162" s="81"/>
+      <c r="K162" s="108"/>
+      <c r="L162" s="81"/>
+    </row>
+    <row r="163" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B163" s="86"/>
-      <c r="C163" s="81"/>
+      <c r="C163" s="86"/>
       <c r="D163" s="81"/>
       <c r="E163" s="81"/>
       <c r="F163" s="81"/>
-      <c r="G163" s="82"/>
+      <c r="G163" s="81"/>
       <c r="H163" s="82"/>
-      <c r="I163" s="81"/>
-      <c r="J163" s="108"/>
-      <c r="K163" s="81"/>
-    </row>
-    <row r="164" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="I163" s="82"/>
+      <c r="J163" s="81"/>
+      <c r="K163" s="108"/>
+      <c r="L163" s="81"/>
+    </row>
+    <row r="164" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B164" s="86"/>
-      <c r="C164" s="81"/>
+      <c r="C164" s="86"/>
       <c r="D164" s="81"/>
       <c r="E164" s="81"/>
       <c r="F164" s="81"/>
-      <c r="G164" s="82"/>
+      <c r="G164" s="81"/>
       <c r="H164" s="82"/>
-      <c r="I164" s="81"/>
-      <c r="J164" s="108"/>
-      <c r="K164" s="81"/>
-    </row>
-    <row r="165" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="I164" s="82"/>
+      <c r="J164" s="81"/>
+      <c r="K164" s="108"/>
+      <c r="L164" s="81"/>
+    </row>
+    <row r="165" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B165" s="86"/>
-      <c r="C165" s="81"/>
+      <c r="C165" s="86"/>
       <c r="D165" s="81"/>
       <c r="E165" s="81"/>
       <c r="F165" s="81"/>
-      <c r="G165" s="82"/>
+      <c r="G165" s="81"/>
       <c r="H165" s="82"/>
-      <c r="I165" s="81"/>
-      <c r="J165" s="108"/>
-      <c r="K165" s="81"/>
-    </row>
-    <row r="166" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="I165" s="82"/>
+      <c r="J165" s="81"/>
+      <c r="K165" s="108"/>
+      <c r="L165" s="81"/>
+    </row>
+    <row r="166" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B166" s="86"/>
-      <c r="C166" s="81"/>
+      <c r="C166" s="86"/>
       <c r="D166" s="81"/>
       <c r="E166" s="81"/>
       <c r="F166" s="81"/>
-      <c r="G166" s="82"/>
+      <c r="G166" s="81"/>
       <c r="H166" s="82"/>
-      <c r="I166" s="81"/>
-      <c r="J166" s="108"/>
-      <c r="K166" s="81"/>
-    </row>
-    <row r="167" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="I166" s="82"/>
+      <c r="J166" s="81"/>
+      <c r="K166" s="108"/>
+      <c r="L166" s="81"/>
+    </row>
+    <row r="167" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B167" s="86"/>
-      <c r="C167" s="81"/>
+      <c r="C167" s="86"/>
       <c r="D167" s="81"/>
       <c r="E167" s="81"/>
       <c r="F167" s="81"/>
-      <c r="G167" s="82"/>
+      <c r="G167" s="81"/>
       <c r="H167" s="82"/>
-      <c r="I167" s="81"/>
-      <c r="J167" s="108"/>
-      <c r="K167" s="81"/>
-    </row>
-    <row r="168" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="I167" s="82"/>
+      <c r="J167" s="81"/>
+      <c r="K167" s="108"/>
+      <c r="L167" s="81"/>
+    </row>
+    <row r="168" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B168" s="86"/>
-      <c r="C168" s="81"/>
+      <c r="C168" s="86"/>
       <c r="D168" s="81"/>
       <c r="E168" s="81"/>
       <c r="F168" s="81"/>
-      <c r="G168" s="82"/>
+      <c r="G168" s="81"/>
       <c r="H168" s="82"/>
-      <c r="I168" s="81"/>
-      <c r="J168" s="108"/>
-      <c r="K168" s="81"/>
-    </row>
-    <row r="169" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="I168" s="82"/>
+      <c r="J168" s="81"/>
+      <c r="K168" s="108"/>
+      <c r="L168" s="81"/>
+    </row>
+    <row r="169" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B169" s="86"/>
-      <c r="C169" s="81"/>
+      <c r="C169" s="86"/>
       <c r="D169" s="81"/>
       <c r="E169" s="81"/>
       <c r="F169" s="81"/>
-      <c r="G169" s="82"/>
+      <c r="G169" s="81"/>
       <c r="H169" s="82"/>
-      <c r="I169" s="81"/>
-      <c r="J169" s="108"/>
-      <c r="K169" s="81"/>
+      <c r="I169" s="82"/>
+      <c r="J169" s="81"/>
+      <c r="K169" s="108"/>
+      <c r="L169" s="81"/>
     </row>
   </sheetData>
-  <autoFilter ref="B5:K169" xr:uid="{CEC92FA4-70EE-4762-B420-00770F4D0B4A}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C6:K47">
-    <sortCondition ref="C6:C47"/>
+  <autoFilter ref="B5:L169" xr:uid="{CEC92FA4-70EE-4762-B420-00770F4D0B4A}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="D6:L47">
+    <sortCondition ref="D6:D47"/>
   </sortState>
   <mergeCells count="7">
-    <mergeCell ref="R4:U4"/>
-    <mergeCell ref="AA4:AF4"/>
-    <mergeCell ref="AH4:AK4"/>
-    <mergeCell ref="C2:I2"/>
-    <mergeCell ref="M4:P4"/>
-    <mergeCell ref="B4:K4"/>
-    <mergeCell ref="W4:Y4"/>
+    <mergeCell ref="S4:V4"/>
+    <mergeCell ref="AB4:AG4"/>
+    <mergeCell ref="AI4:AL4"/>
+    <mergeCell ref="D2:J2"/>
+    <mergeCell ref="N4:Q4"/>
+    <mergeCell ref="B4:L4"/>
+    <mergeCell ref="X4:Z4"/>
   </mergeCells>
-  <conditionalFormatting sqref="C6:C169">
-    <cfRule type="duplicateValues" dxfId="4" priority="105"/>
+  <conditionalFormatting sqref="D6:D169">
+    <cfRule type="duplicateValues" dxfId="3" priority="105"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -13434,37 +13602,37 @@
           <x14:formula1>
             <xm:f>'#Ref'!$C$2:$C$3</xm:f>
           </x14:formula1>
-          <xm:sqref>F6:F169</xm:sqref>
+          <xm:sqref>G6:G169</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{E9903B30-889D-482F-9CC6-9D4973CDCCF7}">
           <x14:formula1>
             <xm:f>'#Ref'!$C$21:$C$23</xm:f>
           </x14:formula1>
-          <xm:sqref>G6:G169</xm:sqref>
+          <xm:sqref>H6:H169</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{F2CAF2BB-EA43-444B-8510-05713DAD9EBD}">
           <x14:formula1>
             <xm:f>'#Ref'!$A$32:$A$34</xm:f>
           </x14:formula1>
-          <xm:sqref>H6:H169</xm:sqref>
+          <xm:sqref>I6:I169</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{C9F6E568-A673-4BCE-A2B5-BA5224306C15}">
           <x14:formula1>
             <xm:f>'#Ref'!$H$25:$H$30</xm:f>
           </x14:formula1>
-          <xm:sqref>I6:I169</xm:sqref>
+          <xm:sqref>J6:J169</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{2EB2728E-F0A3-4A21-9FC1-5128AE82D710}">
           <x14:formula1>
             <xm:f>'#Ref'!$A$2:$A$8</xm:f>
           </x14:formula1>
-          <xm:sqref>K6:K169</xm:sqref>
+          <xm:sqref>L6:L169</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{760233FE-8C48-4FE7-8F75-4A14ADA43E4A}">
           <x14:formula1>
             <xm:f>'#Ref'!$K$2:$K$5</xm:f>
           </x14:formula1>
-          <xm:sqref>J6:J169</xm:sqref>
+          <xm:sqref>K6:K169</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -13502,11 +13670,11 @@
     </row>
     <row r="2" spans="2:7" ht="53.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="6"/>
-      <c r="C2" s="110"/>
-      <c r="D2" s="110"/>
-      <c r="E2" s="111"/>
-      <c r="F2" s="111"/>
-      <c r="G2" s="110"/>
+      <c r="C2" s="112"/>
+      <c r="D2" s="112"/>
+      <c r="E2" s="113"/>
+      <c r="F2" s="113"/>
+      <c r="G2" s="112"/>
     </row>
     <row r="3" spans="2:7" ht="9.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="6"/>
@@ -13517,14 +13685,14 @@
       <c r="G3" s="1"/>
     </row>
     <row r="4" spans="2:7" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="112" t="s">
+      <c r="B4" s="114" t="s">
         <v>223</v>
       </c>
-      <c r="C4" s="113"/>
-      <c r="D4" s="113"/>
-      <c r="E4" s="114"/>
-      <c r="F4" s="114"/>
-      <c r="G4" s="113"/>
+      <c r="C4" s="115"/>
+      <c r="D4" s="115"/>
+      <c r="E4" s="116"/>
+      <c r="F4" s="116"/>
+      <c r="G4" s="115"/>
     </row>
     <row r="5" spans="2:7" ht="24" x14ac:dyDescent="0.25">
       <c r="B5" s="77" t="s">
@@ -14385,7 +14553,7 @@
   <cols>
     <col min="1" max="1" width="1.140625" style="1" customWidth="1"/>
     <col min="2" max="2" width="7.42578125" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.85546875" style="8" customWidth="1"/>
+    <col min="3" max="3" width="28.85546875" style="111" customWidth="1"/>
     <col min="4" max="4" width="29.5703125" style="9" customWidth="1"/>
     <col min="5" max="5" width="34.85546875" style="9" customWidth="1"/>
     <col min="6" max="6" width="61" style="10" customWidth="1"/>
@@ -14403,9 +14571,9 @@
     <row r="2" spans="2:6" ht="53.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
-      <c r="D2" s="110"/>
-      <c r="E2" s="110"/>
-      <c r="F2" s="111"/>
+      <c r="D2" s="112"/>
+      <c r="E2" s="112"/>
+      <c r="F2" s="113"/>
     </row>
     <row r="3" spans="2:6" ht="9.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="6"/>
@@ -14415,13 +14583,13 @@
       <c r="F3" s="5"/>
     </row>
     <row r="4" spans="2:6" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="112" t="s">
+      <c r="B4" s="114" t="s">
         <v>263</v>
       </c>
-      <c r="C4" s="112"/>
-      <c r="D4" s="113"/>
-      <c r="E4" s="113"/>
-      <c r="F4" s="114"/>
+      <c r="C4" s="114"/>
+      <c r="D4" s="115"/>
+      <c r="E4" s="115"/>
+      <c r="F4" s="116"/>
     </row>
     <row r="5" spans="2:6" ht="19.350000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="77" t="s">
@@ -14442,1197 +14610,1197 @@
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B6" s="86"/>
-      <c r="C6" s="86"/>
+      <c r="C6" s="110"/>
       <c r="D6" s="81"/>
       <c r="E6" s="81"/>
       <c r="F6" s="82"/>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B7" s="86"/>
-      <c r="C7" s="86"/>
+      <c r="C7" s="110"/>
       <c r="D7" s="81"/>
       <c r="E7" s="81"/>
       <c r="F7" s="82"/>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B8" s="86"/>
-      <c r="C8" s="86"/>
+      <c r="C8" s="110"/>
       <c r="D8" s="81"/>
       <c r="E8" s="81"/>
       <c r="F8" s="82"/>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B9" s="86"/>
-      <c r="C9" s="86"/>
+      <c r="C9" s="110"/>
       <c r="D9" s="81"/>
       <c r="E9" s="81"/>
       <c r="F9" s="82"/>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B10" s="86"/>
-      <c r="C10" s="86"/>
+      <c r="C10" s="110"/>
       <c r="D10" s="81"/>
       <c r="E10" s="81"/>
       <c r="F10" s="82"/>
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B11" s="86"/>
-      <c r="C11" s="86"/>
+      <c r="C11" s="110"/>
       <c r="D11" s="81"/>
       <c r="E11" s="81"/>
       <c r="F11" s="82"/>
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B12" s="86"/>
-      <c r="C12" s="86"/>
+      <c r="C12" s="110"/>
       <c r="D12" s="81"/>
       <c r="E12" s="81"/>
       <c r="F12" s="82"/>
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B13" s="86"/>
-      <c r="C13" s="86"/>
+      <c r="C13" s="110"/>
       <c r="D13" s="81"/>
       <c r="E13" s="81"/>
       <c r="F13" s="82"/>
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B14" s="86"/>
-      <c r="C14" s="86"/>
+      <c r="C14" s="110"/>
       <c r="D14" s="81"/>
       <c r="E14" s="81"/>
       <c r="F14" s="82"/>
     </row>
     <row r="15" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B15" s="86"/>
-      <c r="C15" s="86"/>
+      <c r="C15" s="110"/>
       <c r="D15" s="81"/>
       <c r="E15" s="81"/>
       <c r="F15" s="82"/>
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B16" s="86"/>
-      <c r="C16" s="86"/>
+      <c r="C16" s="110"/>
       <c r="D16" s="81"/>
       <c r="E16" s="81"/>
       <c r="F16" s="82"/>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B17" s="86"/>
-      <c r="C17" s="86"/>
+      <c r="C17" s="110"/>
       <c r="D17" s="81"/>
       <c r="E17" s="81"/>
       <c r="F17" s="82"/>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B18" s="86"/>
-      <c r="C18" s="86"/>
+      <c r="C18" s="110"/>
       <c r="D18" s="81"/>
       <c r="E18" s="81"/>
       <c r="F18" s="82"/>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B19" s="86"/>
-      <c r="C19" s="86"/>
+      <c r="C19" s="110"/>
       <c r="D19" s="81"/>
       <c r="E19" s="81"/>
       <c r="F19" s="82"/>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B20" s="86"/>
-      <c r="C20" s="86"/>
+      <c r="C20" s="110"/>
       <c r="D20" s="81"/>
       <c r="E20" s="81"/>
       <c r="F20" s="82"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B21" s="86"/>
-      <c r="C21" s="86"/>
+      <c r="C21" s="110"/>
       <c r="D21" s="81"/>
       <c r="E21" s="81"/>
       <c r="F21" s="82"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B22" s="86"/>
-      <c r="C22" s="86"/>
+      <c r="C22" s="110"/>
       <c r="D22" s="81"/>
       <c r="E22" s="81"/>
       <c r="F22" s="82"/>
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B23" s="86"/>
-      <c r="C23" s="86"/>
+      <c r="C23" s="110"/>
       <c r="D23" s="81"/>
       <c r="E23" s="81"/>
       <c r="F23" s="82"/>
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B24" s="86"/>
-      <c r="C24" s="86"/>
+      <c r="C24" s="110"/>
       <c r="D24" s="81"/>
       <c r="E24" s="81"/>
       <c r="F24" s="82"/>
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B25" s="86"/>
-      <c r="C25" s="86"/>
+      <c r="C25" s="110"/>
       <c r="D25" s="81"/>
       <c r="E25" s="81"/>
       <c r="F25" s="82"/>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B26" s="86"/>
-      <c r="C26" s="86"/>
+      <c r="C26" s="110"/>
       <c r="D26" s="81"/>
       <c r="E26" s="81"/>
       <c r="F26" s="82"/>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B27" s="86"/>
-      <c r="C27" s="86"/>
+      <c r="C27" s="110"/>
       <c r="D27" s="81"/>
       <c r="E27" s="81"/>
       <c r="F27" s="82"/>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B28" s="86"/>
-      <c r="C28" s="86"/>
+      <c r="C28" s="110"/>
       <c r="D28" s="81"/>
       <c r="E28" s="81"/>
       <c r="F28" s="82"/>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B29" s="86"/>
-      <c r="C29" s="86"/>
+      <c r="C29" s="110"/>
       <c r="D29" s="81"/>
       <c r="E29" s="81"/>
       <c r="F29" s="81"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B30" s="86"/>
-      <c r="C30" s="86"/>
+      <c r="C30" s="110"/>
       <c r="D30" s="81"/>
       <c r="E30" s="81"/>
       <c r="F30" s="81"/>
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B31" s="86"/>
-      <c r="C31" s="86"/>
+      <c r="C31" s="110"/>
       <c r="D31" s="81"/>
       <c r="E31" s="81"/>
       <c r="F31" s="81"/>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B32" s="86"/>
-      <c r="C32" s="86"/>
+      <c r="C32" s="110"/>
       <c r="D32" s="81"/>
       <c r="E32" s="81"/>
       <c r="F32" s="81"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B33" s="86"/>
-      <c r="C33" s="86"/>
+      <c r="C33" s="110"/>
       <c r="D33" s="81"/>
       <c r="E33" s="81"/>
       <c r="F33" s="81"/>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B34" s="86"/>
-      <c r="C34" s="86"/>
+      <c r="C34" s="110"/>
       <c r="D34" s="81"/>
       <c r="E34" s="81"/>
       <c r="F34" s="81"/>
     </row>
     <row r="35" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B35" s="86"/>
-      <c r="C35" s="86"/>
+      <c r="C35" s="110"/>
       <c r="D35" s="81"/>
       <c r="E35" s="81"/>
       <c r="F35" s="81"/>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B36" s="86"/>
-      <c r="C36" s="86"/>
+      <c r="C36" s="110"/>
       <c r="D36" s="81"/>
       <c r="E36" s="81"/>
       <c r="F36" s="81"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B37" s="86"/>
-      <c r="C37" s="86"/>
+      <c r="C37" s="110"/>
       <c r="D37" s="81"/>
       <c r="E37" s="81"/>
       <c r="F37" s="81"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B38" s="86"/>
-      <c r="C38" s="86"/>
+      <c r="C38" s="110"/>
       <c r="D38" s="81"/>
       <c r="E38" s="81"/>
       <c r="F38" s="81"/>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B39" s="86"/>
-      <c r="C39" s="86"/>
+      <c r="C39" s="110"/>
       <c r="D39" s="81"/>
       <c r="E39" s="81"/>
       <c r="F39" s="81"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B40" s="86"/>
-      <c r="C40" s="86"/>
+      <c r="C40" s="110"/>
       <c r="D40" s="81"/>
       <c r="E40" s="81"/>
       <c r="F40" s="81"/>
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B41" s="86"/>
-      <c r="C41" s="86"/>
+      <c r="C41" s="110"/>
       <c r="D41" s="81"/>
       <c r="E41" s="81"/>
       <c r="F41" s="81"/>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B42" s="86"/>
-      <c r="C42" s="86"/>
+      <c r="C42" s="110"/>
       <c r="D42" s="81"/>
       <c r="E42" s="81"/>
       <c r="F42" s="81"/>
     </row>
     <row r="43" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B43" s="86"/>
-      <c r="C43" s="86"/>
+      <c r="C43" s="110"/>
       <c r="D43" s="81"/>
       <c r="E43" s="81"/>
       <c r="F43" s="81"/>
     </row>
     <row r="44" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B44" s="86"/>
-      <c r="C44" s="86"/>
+      <c r="C44" s="110"/>
       <c r="D44" s="81"/>
       <c r="E44" s="81"/>
       <c r="F44" s="81"/>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B45" s="86"/>
-      <c r="C45" s="86"/>
+      <c r="C45" s="110"/>
       <c r="D45" s="81"/>
       <c r="E45" s="81"/>
       <c r="F45" s="81"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B46" s="86"/>
-      <c r="C46" s="86"/>
+      <c r="C46" s="110"/>
       <c r="D46" s="81"/>
       <c r="E46" s="81"/>
       <c r="F46" s="81"/>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B47" s="86"/>
-      <c r="C47" s="86"/>
+      <c r="C47" s="110"/>
       <c r="D47" s="81"/>
       <c r="E47" s="81"/>
       <c r="F47" s="81"/>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B48" s="86"/>
-      <c r="C48" s="86"/>
+      <c r="C48" s="110"/>
       <c r="D48" s="81"/>
       <c r="E48" s="81"/>
       <c r="F48" s="81"/>
     </row>
     <row r="49" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B49" s="86"/>
-      <c r="C49" s="86"/>
+      <c r="C49" s="110"/>
       <c r="D49" s="81"/>
       <c r="E49" s="81"/>
       <c r="F49" s="81"/>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B50" s="86"/>
-      <c r="C50" s="86"/>
+      <c r="C50" s="110"/>
       <c r="D50" s="81"/>
       <c r="E50" s="81"/>
       <c r="F50" s="81"/>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B51" s="86"/>
-      <c r="C51" s="86"/>
+      <c r="C51" s="110"/>
       <c r="D51" s="81"/>
       <c r="E51" s="81"/>
       <c r="F51" s="81"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B52" s="86"/>
-      <c r="C52" s="86"/>
+      <c r="C52" s="110"/>
       <c r="D52" s="81"/>
       <c r="E52" s="81"/>
       <c r="F52" s="81"/>
     </row>
     <row r="53" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B53" s="86"/>
-      <c r="C53" s="86"/>
+      <c r="C53" s="110"/>
       <c r="D53" s="81"/>
       <c r="E53" s="81"/>
       <c r="F53" s="81"/>
     </row>
     <row r="54" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B54" s="86"/>
-      <c r="C54" s="86"/>
+      <c r="C54" s="110"/>
       <c r="D54" s="81"/>
       <c r="E54" s="81"/>
       <c r="F54" s="81"/>
     </row>
     <row r="55" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B55" s="86"/>
-      <c r="C55" s="86"/>
+      <c r="C55" s="110"/>
       <c r="D55" s="81"/>
       <c r="E55" s="81"/>
       <c r="F55" s="81"/>
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B56" s="86"/>
-      <c r="C56" s="86"/>
+      <c r="C56" s="110"/>
       <c r="D56" s="81"/>
       <c r="E56" s="81"/>
       <c r="F56" s="81"/>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B57" s="86"/>
-      <c r="C57" s="86"/>
+      <c r="C57" s="110"/>
       <c r="D57" s="81"/>
       <c r="E57" s="81"/>
       <c r="F57" s="81"/>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B58" s="86"/>
-      <c r="C58" s="86"/>
+      <c r="C58" s="110"/>
       <c r="D58" s="81"/>
       <c r="E58" s="81"/>
       <c r="F58" s="81"/>
     </row>
     <row r="59" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B59" s="86"/>
-      <c r="C59" s="86"/>
+      <c r="C59" s="110"/>
       <c r="D59" s="81"/>
       <c r="E59" s="81"/>
       <c r="F59" s="81"/>
     </row>
     <row r="60" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B60" s="86"/>
-      <c r="C60" s="86"/>
+      <c r="C60" s="110"/>
       <c r="D60" s="81"/>
       <c r="E60" s="81"/>
       <c r="F60" s="81"/>
     </row>
     <row r="61" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B61" s="86"/>
-      <c r="C61" s="86"/>
+      <c r="C61" s="110"/>
       <c r="D61" s="81"/>
       <c r="E61" s="81"/>
       <c r="F61" s="81"/>
     </row>
     <row r="62" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B62" s="86"/>
-      <c r="C62" s="86"/>
+      <c r="C62" s="110"/>
       <c r="D62" s="81"/>
       <c r="E62" s="81"/>
       <c r="F62" s="81"/>
     </row>
     <row r="63" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B63" s="86"/>
-      <c r="C63" s="86"/>
+      <c r="C63" s="110"/>
       <c r="D63" s="81"/>
       <c r="E63" s="81"/>
       <c r="F63" s="81"/>
     </row>
     <row r="64" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B64" s="86"/>
-      <c r="C64" s="86"/>
+      <c r="C64" s="110"/>
       <c r="D64" s="81"/>
       <c r="E64" s="81"/>
       <c r="F64" s="81"/>
     </row>
     <row r="65" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B65" s="86"/>
-      <c r="C65" s="86"/>
+      <c r="C65" s="110"/>
       <c r="D65" s="81"/>
       <c r="E65" s="81"/>
       <c r="F65" s="81"/>
     </row>
     <row r="66" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B66" s="86"/>
-      <c r="C66" s="86"/>
+      <c r="C66" s="110"/>
       <c r="D66" s="81"/>
       <c r="E66" s="81"/>
       <c r="F66" s="81"/>
     </row>
     <row r="67" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B67" s="86"/>
-      <c r="C67" s="86"/>
+      <c r="C67" s="110"/>
       <c r="D67" s="81"/>
       <c r="E67" s="81"/>
       <c r="F67" s="81"/>
     </row>
     <row r="68" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B68" s="86"/>
-      <c r="C68" s="86"/>
+      <c r="C68" s="110"/>
       <c r="D68" s="81"/>
       <c r="E68" s="81"/>
       <c r="F68" s="81"/>
     </row>
     <row r="69" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B69" s="86"/>
-      <c r="C69" s="86"/>
+      <c r="C69" s="110"/>
       <c r="D69" s="81"/>
       <c r="E69" s="81"/>
       <c r="F69" s="81"/>
     </row>
     <row r="70" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B70" s="86"/>
-      <c r="C70" s="86"/>
+      <c r="C70" s="110"/>
       <c r="D70" s="81"/>
       <c r="E70" s="81"/>
       <c r="F70" s="81"/>
     </row>
     <row r="71" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B71" s="86"/>
-      <c r="C71" s="86"/>
+      <c r="C71" s="110"/>
       <c r="D71" s="81"/>
       <c r="E71" s="81"/>
       <c r="F71" s="81"/>
     </row>
     <row r="72" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B72" s="86"/>
-      <c r="C72" s="86"/>
+      <c r="C72" s="110"/>
       <c r="D72" s="81"/>
       <c r="E72" s="81"/>
       <c r="F72" s="81"/>
     </row>
     <row r="73" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B73" s="86"/>
-      <c r="C73" s="86"/>
+      <c r="C73" s="110"/>
       <c r="D73" s="81"/>
       <c r="E73" s="81"/>
       <c r="F73" s="81"/>
     </row>
     <row r="74" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B74" s="86"/>
-      <c r="C74" s="86"/>
+      <c r="C74" s="110"/>
       <c r="D74" s="81"/>
       <c r="E74" s="81"/>
       <c r="F74" s="81"/>
     </row>
     <row r="75" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B75" s="86"/>
-      <c r="C75" s="86"/>
+      <c r="C75" s="110"/>
       <c r="D75" s="81"/>
       <c r="E75" s="81"/>
       <c r="F75" s="81"/>
     </row>
     <row r="76" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B76" s="86"/>
-      <c r="C76" s="86"/>
+      <c r="C76" s="110"/>
       <c r="D76" s="81"/>
       <c r="E76" s="81"/>
       <c r="F76" s="81"/>
     </row>
     <row r="77" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B77" s="86"/>
-      <c r="C77" s="86"/>
+      <c r="C77" s="110"/>
       <c r="D77" s="81"/>
       <c r="E77" s="81"/>
       <c r="F77" s="81"/>
     </row>
     <row r="78" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B78" s="86"/>
-      <c r="C78" s="86"/>
+      <c r="C78" s="110"/>
       <c r="D78" s="81"/>
       <c r="E78" s="81"/>
       <c r="F78" s="81"/>
     </row>
     <row r="79" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B79" s="86"/>
-      <c r="C79" s="86"/>
+      <c r="C79" s="110"/>
       <c r="D79" s="81"/>
       <c r="E79" s="81"/>
       <c r="F79" s="81"/>
     </row>
     <row r="80" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B80" s="86"/>
-      <c r="C80" s="86"/>
+      <c r="C80" s="110"/>
       <c r="D80" s="81"/>
       <c r="E80" s="81"/>
       <c r="F80" s="81"/>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B81" s="86"/>
-      <c r="C81" s="86"/>
+      <c r="C81" s="110"/>
       <c r="D81" s="81"/>
       <c r="E81" s="81"/>
       <c r="F81" s="81"/>
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B82" s="86"/>
-      <c r="C82" s="86"/>
+      <c r="C82" s="110"/>
       <c r="D82" s="81"/>
       <c r="E82" s="81"/>
       <c r="F82" s="81"/>
     </row>
     <row r="83" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B83" s="86"/>
-      <c r="C83" s="86"/>
+      <c r="C83" s="110"/>
       <c r="D83" s="81"/>
       <c r="E83" s="81"/>
       <c r="F83" s="81"/>
     </row>
     <row r="84" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B84" s="86"/>
-      <c r="C84" s="86"/>
+      <c r="C84" s="110"/>
       <c r="D84" s="81"/>
       <c r="E84" s="81"/>
       <c r="F84" s="81"/>
     </row>
     <row r="85" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B85" s="86"/>
-      <c r="C85" s="86"/>
+      <c r="C85" s="110"/>
       <c r="D85" s="81"/>
       <c r="E85" s="81"/>
       <c r="F85" s="81"/>
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B86" s="86"/>
-      <c r="C86" s="86"/>
+      <c r="C86" s="110"/>
       <c r="D86" s="81"/>
       <c r="E86" s="81"/>
       <c r="F86" s="81"/>
     </row>
     <row r="87" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B87" s="86"/>
-      <c r="C87" s="86"/>
+      <c r="C87" s="110"/>
       <c r="D87" s="81"/>
       <c r="E87" s="81"/>
       <c r="F87" s="81"/>
     </row>
     <row r="88" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B88" s="86"/>
-      <c r="C88" s="86"/>
+      <c r="C88" s="110"/>
       <c r="D88" s="81"/>
       <c r="E88" s="81"/>
       <c r="F88" s="81"/>
     </row>
     <row r="89" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B89" s="86"/>
-      <c r="C89" s="86"/>
+      <c r="C89" s="110"/>
       <c r="D89" s="81"/>
       <c r="E89" s="81"/>
       <c r="F89" s="81"/>
     </row>
     <row r="90" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B90" s="86"/>
-      <c r="C90" s="86"/>
+      <c r="C90" s="110"/>
       <c r="D90" s="81"/>
       <c r="E90" s="81"/>
       <c r="F90" s="81"/>
     </row>
     <row r="91" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B91" s="86"/>
-      <c r="C91" s="86"/>
+      <c r="C91" s="110"/>
       <c r="D91" s="81"/>
       <c r="E91" s="81"/>
       <c r="F91" s="81"/>
     </row>
     <row r="92" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B92" s="86"/>
-      <c r="C92" s="86"/>
+      <c r="C92" s="110"/>
       <c r="D92" s="81"/>
       <c r="E92" s="81"/>
       <c r="F92" s="81"/>
     </row>
     <row r="93" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B93" s="86"/>
-      <c r="C93" s="86"/>
+      <c r="C93" s="110"/>
       <c r="D93" s="81"/>
       <c r="E93" s="81"/>
       <c r="F93" s="81"/>
     </row>
     <row r="94" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B94" s="86"/>
-      <c r="C94" s="86"/>
+      <c r="C94" s="110"/>
       <c r="D94" s="81"/>
       <c r="E94" s="81"/>
       <c r="F94" s="81"/>
     </row>
     <row r="95" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B95" s="86"/>
-      <c r="C95" s="86"/>
+      <c r="C95" s="110"/>
       <c r="D95" s="81"/>
       <c r="E95" s="81"/>
       <c r="F95" s="81"/>
     </row>
     <row r="96" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B96" s="86"/>
-      <c r="C96" s="86"/>
+      <c r="C96" s="110"/>
       <c r="D96" s="81"/>
       <c r="E96" s="81"/>
       <c r="F96" s="81"/>
     </row>
     <row r="97" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B97" s="86"/>
-      <c r="C97" s="86"/>
+      <c r="C97" s="110"/>
       <c r="D97" s="81"/>
       <c r="E97" s="81"/>
       <c r="F97" s="81"/>
     </row>
     <row r="98" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B98" s="86"/>
-      <c r="C98" s="86"/>
+      <c r="C98" s="110"/>
       <c r="D98" s="81"/>
       <c r="E98" s="81"/>
       <c r="F98" s="81"/>
     </row>
     <row r="99" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B99" s="86"/>
-      <c r="C99" s="86"/>
+      <c r="C99" s="110"/>
       <c r="D99" s="81"/>
       <c r="E99" s="81"/>
       <c r="F99" s="81"/>
     </row>
     <row r="100" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B100" s="86"/>
-      <c r="C100" s="86"/>
+      <c r="C100" s="110"/>
       <c r="D100" s="81"/>
       <c r="E100" s="81"/>
       <c r="F100" s="81"/>
     </row>
     <row r="101" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B101" s="86"/>
-      <c r="C101" s="86"/>
+      <c r="C101" s="110"/>
       <c r="D101" s="81"/>
       <c r="E101" s="81"/>
       <c r="F101" s="81"/>
     </row>
     <row r="102" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B102" s="86"/>
-      <c r="C102" s="86"/>
+      <c r="C102" s="110"/>
       <c r="D102" s="81"/>
       <c r="E102" s="81"/>
       <c r="F102" s="81"/>
     </row>
     <row r="103" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B103" s="86"/>
-      <c r="C103" s="86"/>
+      <c r="C103" s="110"/>
       <c r="D103" s="81"/>
       <c r="E103" s="81"/>
       <c r="F103" s="81"/>
     </row>
     <row r="104" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B104" s="86"/>
-      <c r="C104" s="86"/>
+      <c r="C104" s="110"/>
       <c r="D104" s="81"/>
       <c r="E104" s="81"/>
       <c r="F104" s="81"/>
     </row>
     <row r="105" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B105" s="86"/>
-      <c r="C105" s="86"/>
+      <c r="C105" s="110"/>
       <c r="D105" s="81"/>
       <c r="E105" s="81"/>
       <c r="F105" s="81"/>
     </row>
     <row r="106" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B106" s="86"/>
-      <c r="C106" s="86"/>
+      <c r="C106" s="110"/>
       <c r="D106" s="81"/>
       <c r="E106" s="81"/>
       <c r="F106" s="81"/>
     </row>
     <row r="107" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B107" s="86"/>
-      <c r="C107" s="86"/>
+      <c r="C107" s="110"/>
       <c r="D107" s="81"/>
       <c r="E107" s="81"/>
       <c r="F107" s="81"/>
     </row>
     <row r="108" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B108" s="86"/>
-      <c r="C108" s="86"/>
+      <c r="C108" s="110"/>
       <c r="D108" s="81"/>
       <c r="E108" s="81"/>
       <c r="F108" s="81"/>
     </row>
     <row r="109" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B109" s="86"/>
-      <c r="C109" s="86"/>
+      <c r="C109" s="110"/>
       <c r="D109" s="81"/>
       <c r="E109" s="81"/>
       <c r="F109" s="81"/>
     </row>
     <row r="110" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B110" s="86"/>
-      <c r="C110" s="86"/>
+      <c r="C110" s="110"/>
       <c r="D110" s="81"/>
       <c r="E110" s="81"/>
       <c r="F110" s="81"/>
     </row>
     <row r="111" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B111" s="86"/>
-      <c r="C111" s="86"/>
+      <c r="C111" s="110"/>
       <c r="D111" s="81"/>
       <c r="E111" s="81"/>
       <c r="F111" s="81"/>
     </row>
     <row r="112" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B112" s="86"/>
-      <c r="C112" s="86"/>
+      <c r="C112" s="110"/>
       <c r="D112" s="81"/>
       <c r="E112" s="81"/>
       <c r="F112" s="81"/>
     </row>
     <row r="113" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B113" s="86"/>
-      <c r="C113" s="86"/>
+      <c r="C113" s="110"/>
       <c r="D113" s="81"/>
       <c r="E113" s="81"/>
       <c r="F113" s="81"/>
     </row>
     <row r="114" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B114" s="86"/>
-      <c r="C114" s="86"/>
+      <c r="C114" s="110"/>
       <c r="D114" s="81"/>
       <c r="E114" s="81"/>
       <c r="F114" s="81"/>
     </row>
     <row r="115" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B115" s="86"/>
-      <c r="C115" s="86"/>
+      <c r="C115" s="110"/>
       <c r="D115" s="81"/>
       <c r="E115" s="81"/>
       <c r="F115" s="81"/>
     </row>
     <row r="116" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B116" s="86"/>
-      <c r="C116" s="86"/>
+      <c r="C116" s="110"/>
       <c r="D116" s="81"/>
       <c r="E116" s="81"/>
       <c r="F116" s="81"/>
     </row>
     <row r="117" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B117" s="86"/>
-      <c r="C117" s="86"/>
+      <c r="C117" s="110"/>
       <c r="D117" s="81"/>
       <c r="E117" s="81"/>
       <c r="F117" s="81"/>
     </row>
     <row r="118" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B118" s="86"/>
-      <c r="C118" s="86"/>
+      <c r="C118" s="110"/>
       <c r="D118" s="81"/>
       <c r="E118" s="81"/>
       <c r="F118" s="81"/>
     </row>
     <row r="119" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B119" s="86"/>
-      <c r="C119" s="86"/>
+      <c r="C119" s="110"/>
       <c r="D119" s="81"/>
       <c r="E119" s="81"/>
       <c r="F119" s="81"/>
     </row>
     <row r="120" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B120" s="86"/>
-      <c r="C120" s="86"/>
+      <c r="C120" s="110"/>
       <c r="D120" s="81"/>
       <c r="E120" s="81"/>
       <c r="F120" s="81"/>
     </row>
     <row r="121" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B121" s="86"/>
-      <c r="C121" s="86"/>
+      <c r="C121" s="110"/>
       <c r="D121" s="81"/>
       <c r="E121" s="81"/>
       <c r="F121" s="81"/>
     </row>
     <row r="122" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B122" s="86"/>
-      <c r="C122" s="86"/>
+      <c r="C122" s="110"/>
       <c r="D122" s="81"/>
       <c r="E122" s="81"/>
       <c r="F122" s="81"/>
     </row>
     <row r="123" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B123" s="86"/>
-      <c r="C123" s="86"/>
+      <c r="C123" s="110"/>
       <c r="D123" s="81"/>
       <c r="E123" s="81"/>
       <c r="F123" s="81"/>
     </row>
     <row r="124" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B124" s="86"/>
-      <c r="C124" s="86"/>
+      <c r="C124" s="110"/>
       <c r="D124" s="81"/>
       <c r="E124" s="81"/>
       <c r="F124" s="81"/>
     </row>
     <row r="125" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B125" s="86"/>
-      <c r="C125" s="86"/>
+      <c r="C125" s="110"/>
       <c r="D125" s="81"/>
       <c r="E125" s="81"/>
       <c r="F125" s="81"/>
     </row>
     <row r="126" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B126" s="86"/>
-      <c r="C126" s="86"/>
+      <c r="C126" s="110"/>
       <c r="D126" s="81"/>
       <c r="E126" s="81"/>
       <c r="F126" s="81"/>
     </row>
     <row r="127" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B127" s="86"/>
-      <c r="C127" s="86"/>
+      <c r="C127" s="110"/>
       <c r="D127" s="81"/>
       <c r="E127" s="81"/>
       <c r="F127" s="81"/>
     </row>
     <row r="128" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B128" s="86"/>
-      <c r="C128" s="86"/>
+      <c r="C128" s="110"/>
       <c r="D128" s="81"/>
       <c r="E128" s="81"/>
       <c r="F128" s="81"/>
     </row>
     <row r="129" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B129" s="86"/>
-      <c r="C129" s="86"/>
+      <c r="C129" s="110"/>
       <c r="D129" s="81"/>
       <c r="E129" s="81"/>
       <c r="F129" s="81"/>
     </row>
     <row r="130" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B130" s="86"/>
-      <c r="C130" s="86"/>
+      <c r="C130" s="110"/>
       <c r="D130" s="81"/>
       <c r="E130" s="81"/>
       <c r="F130" s="81"/>
     </row>
     <row r="131" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B131" s="86"/>
-      <c r="C131" s="86"/>
+      <c r="C131" s="110"/>
       <c r="D131" s="81"/>
       <c r="E131" s="81"/>
       <c r="F131" s="81"/>
     </row>
     <row r="132" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B132" s="86"/>
-      <c r="C132" s="86"/>
+      <c r="C132" s="110"/>
       <c r="D132" s="81"/>
       <c r="E132" s="81"/>
       <c r="F132" s="81"/>
     </row>
     <row r="133" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B133" s="86"/>
-      <c r="C133" s="86"/>
+      <c r="C133" s="110"/>
       <c r="D133" s="81"/>
       <c r="E133" s="81"/>
       <c r="F133" s="81"/>
     </row>
     <row r="134" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B134" s="86"/>
-      <c r="C134" s="86"/>
+      <c r="C134" s="110"/>
       <c r="D134" s="81"/>
       <c r="E134" s="81"/>
       <c r="F134" s="81"/>
     </row>
     <row r="135" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B135" s="86"/>
-      <c r="C135" s="86"/>
+      <c r="C135" s="110"/>
       <c r="D135" s="81"/>
       <c r="E135" s="81"/>
       <c r="F135" s="81"/>
     </row>
     <row r="136" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B136" s="86"/>
-      <c r="C136" s="86"/>
+      <c r="C136" s="110"/>
       <c r="D136" s="81"/>
       <c r="E136" s="81"/>
       <c r="F136" s="81"/>
     </row>
     <row r="137" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B137" s="86"/>
-      <c r="C137" s="86"/>
+      <c r="C137" s="110"/>
       <c r="D137" s="81"/>
       <c r="E137" s="81"/>
       <c r="F137" s="81"/>
     </row>
     <row r="138" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B138" s="86"/>
-      <c r="C138" s="86"/>
+      <c r="C138" s="110"/>
       <c r="D138" s="81"/>
       <c r="E138" s="81"/>
       <c r="F138" s="81"/>
     </row>
     <row r="139" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B139" s="86"/>
-      <c r="C139" s="86"/>
+      <c r="C139" s="110"/>
       <c r="D139" s="81"/>
       <c r="E139" s="81"/>
       <c r="F139" s="81"/>
     </row>
     <row r="140" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B140" s="86"/>
-      <c r="C140" s="86"/>
+      <c r="C140" s="110"/>
       <c r="D140" s="81"/>
       <c r="E140" s="81"/>
       <c r="F140" s="81"/>
     </row>
     <row r="141" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B141" s="86"/>
-      <c r="C141" s="86"/>
+      <c r="C141" s="110"/>
       <c r="D141" s="81"/>
       <c r="E141" s="81"/>
       <c r="F141" s="81"/>
     </row>
     <row r="142" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B142" s="86"/>
-      <c r="C142" s="86"/>
+      <c r="C142" s="110"/>
       <c r="D142" s="81"/>
       <c r="E142" s="81"/>
       <c r="F142" s="81"/>
     </row>
     <row r="143" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B143" s="86"/>
-      <c r="C143" s="86"/>
+      <c r="C143" s="110"/>
       <c r="D143" s="81"/>
       <c r="E143" s="81"/>
       <c r="F143" s="81"/>
     </row>
     <row r="144" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B144" s="86"/>
-      <c r="C144" s="86"/>
+      <c r="C144" s="110"/>
       <c r="D144" s="81"/>
       <c r="E144" s="81"/>
       <c r="F144" s="81"/>
     </row>
     <row r="145" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B145" s="86"/>
-      <c r="C145" s="86"/>
+      <c r="C145" s="110"/>
       <c r="D145" s="81"/>
       <c r="E145" s="81"/>
       <c r="F145" s="81"/>
     </row>
     <row r="146" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B146" s="86"/>
-      <c r="C146" s="86"/>
+      <c r="C146" s="110"/>
       <c r="D146" s="81"/>
       <c r="E146" s="81"/>
       <c r="F146" s="81"/>
     </row>
     <row r="147" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B147" s="86"/>
-      <c r="C147" s="86"/>
+      <c r="C147" s="110"/>
       <c r="D147" s="81"/>
       <c r="E147" s="81"/>
       <c r="F147" s="81"/>
     </row>
     <row r="148" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B148" s="86"/>
-      <c r="C148" s="86"/>
+      <c r="C148" s="110"/>
       <c r="D148" s="81"/>
       <c r="E148" s="81"/>
       <c r="F148" s="81"/>
     </row>
     <row r="149" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B149" s="86"/>
-      <c r="C149" s="86"/>
+      <c r="C149" s="110"/>
       <c r="D149" s="81"/>
       <c r="E149" s="81"/>
       <c r="F149" s="81"/>
     </row>
     <row r="150" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B150" s="86"/>
-      <c r="C150" s="86"/>
+      <c r="C150" s="110"/>
       <c r="D150" s="81"/>
       <c r="E150" s="81"/>
       <c r="F150" s="81"/>
     </row>
     <row r="151" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B151" s="86"/>
-      <c r="C151" s="86"/>
+      <c r="C151" s="110"/>
       <c r="D151" s="81"/>
       <c r="E151" s="81"/>
       <c r="F151" s="81"/>
     </row>
     <row r="152" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B152" s="86"/>
-      <c r="C152" s="86"/>
+      <c r="C152" s="110"/>
       <c r="D152" s="81"/>
       <c r="E152" s="81"/>
       <c r="F152" s="81"/>
     </row>
     <row r="153" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B153" s="86"/>
-      <c r="C153" s="86"/>
+      <c r="C153" s="110"/>
       <c r="D153" s="81"/>
       <c r="E153" s="81"/>
       <c r="F153" s="81"/>
     </row>
     <row r="154" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B154" s="86"/>
-      <c r="C154" s="86"/>
+      <c r="C154" s="110"/>
       <c r="D154" s="81"/>
       <c r="E154" s="81"/>
       <c r="F154" s="81"/>
     </row>
     <row r="155" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B155" s="86"/>
-      <c r="C155" s="86"/>
+      <c r="C155" s="110"/>
       <c r="D155" s="81"/>
       <c r="E155" s="81"/>
       <c r="F155" s="81"/>
     </row>
     <row r="156" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B156" s="86"/>
-      <c r="C156" s="86"/>
+      <c r="C156" s="110"/>
       <c r="D156" s="81"/>
       <c r="E156" s="81"/>
       <c r="F156" s="81"/>
     </row>
     <row r="157" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B157" s="86"/>
-      <c r="C157" s="86"/>
+      <c r="C157" s="110"/>
       <c r="D157" s="81"/>
       <c r="E157" s="81"/>
       <c r="F157" s="81"/>
     </row>
     <row r="158" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B158" s="86"/>
-      <c r="C158" s="86"/>
+      <c r="C158" s="110"/>
       <c r="D158" s="81"/>
       <c r="E158" s="81"/>
       <c r="F158" s="81"/>
     </row>
     <row r="159" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B159" s="86"/>
-      <c r="C159" s="86"/>
+      <c r="C159" s="110"/>
       <c r="D159" s="81"/>
       <c r="E159" s="81"/>
       <c r="F159" s="81"/>
     </row>
     <row r="160" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B160" s="86"/>
-      <c r="C160" s="86"/>
+      <c r="C160" s="110"/>
       <c r="D160" s="81"/>
       <c r="E160" s="81"/>
       <c r="F160" s="81"/>
     </row>
     <row r="161" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B161" s="86"/>
-      <c r="C161" s="86"/>
+      <c r="C161" s="110"/>
       <c r="D161" s="81"/>
       <c r="E161" s="81"/>
       <c r="F161" s="81"/>
     </row>
     <row r="162" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B162" s="86"/>
-      <c r="C162" s="86"/>
+      <c r="C162" s="110"/>
       <c r="D162" s="81"/>
       <c r="E162" s="81"/>
       <c r="F162" s="81"/>
     </row>
     <row r="163" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B163" s="86"/>
-      <c r="C163" s="86"/>
+      <c r="C163" s="110"/>
       <c r="D163" s="81"/>
       <c r="E163" s="81"/>
       <c r="F163" s="81"/>
     </row>
     <row r="164" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B164" s="86"/>
-      <c r="C164" s="86"/>
+      <c r="C164" s="110"/>
       <c r="D164" s="81"/>
       <c r="E164" s="81"/>
       <c r="F164" s="81"/>
     </row>
     <row r="165" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B165" s="86"/>
-      <c r="C165" s="86"/>
+      <c r="C165" s="110"/>
       <c r="D165" s="81"/>
       <c r="E165" s="81"/>
       <c r="F165" s="81"/>
     </row>
     <row r="166" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B166" s="86"/>
-      <c r="C166" s="86"/>
+      <c r="C166" s="110"/>
       <c r="D166" s="81"/>
       <c r="E166" s="81"/>
       <c r="F166" s="81"/>
     </row>
     <row r="167" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B167" s="86"/>
-      <c r="C167" s="86"/>
+      <c r="C167" s="110"/>
       <c r="D167" s="81"/>
       <c r="E167" s="81"/>
       <c r="F167" s="81"/>
     </row>
     <row r="168" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B168" s="86"/>
-      <c r="C168" s="86"/>
+      <c r="C168" s="110"/>
       <c r="D168" s="81"/>
       <c r="E168" s="81"/>
       <c r="F168" s="81"/>
     </row>
     <row r="169" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B169" s="86"/>
-      <c r="C169" s="86"/>
+      <c r="C169" s="110"/>
       <c r="D169" s="81"/>
       <c r="E169" s="81"/>
       <c r="F169" s="81"/>
     </row>
     <row r="170" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B170" s="86"/>
-      <c r="C170" s="86"/>
+      <c r="C170" s="110"/>
       <c r="D170" s="81"/>
       <c r="E170" s="81"/>
       <c r="F170" s="81"/>
     </row>
     <row r="171" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B171" s="86"/>
-      <c r="C171" s="86"/>
+      <c r="C171" s="110"/>
       <c r="D171" s="81"/>
       <c r="E171" s="81"/>
       <c r="F171" s="81"/>
     </row>
     <row r="172" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B172" s="86"/>
-      <c r="C172" s="86"/>
+      <c r="C172" s="110"/>
       <c r="D172" s="81"/>
       <c r="E172" s="81"/>
       <c r="F172" s="81"/>
     </row>
     <row r="173" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B173" s="86"/>
-      <c r="C173" s="86"/>
+      <c r="C173" s="110"/>
       <c r="D173" s="81"/>
       <c r="E173" s="81"/>
       <c r="F173" s="81"/>
     </row>
     <row r="174" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B174" s="86"/>
-      <c r="C174" s="86"/>
+      <c r="C174" s="110"/>
       <c r="D174" s="81"/>
       <c r="E174" s="81"/>
       <c r="F174" s="81"/>
     </row>
     <row r="175" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B175" s="86"/>
-      <c r="C175" s="86"/>
+      <c r="C175" s="110"/>
       <c r="D175" s="81"/>
       <c r="E175" s="81"/>
       <c r="F175" s="81"/>
     </row>
     <row r="176" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B176" s="86"/>
-      <c r="C176" s="86"/>
+      <c r="C176" s="110"/>
       <c r="D176" s="81"/>
       <c r="E176" s="81"/>
       <c r="F176" s="81"/>
@@ -15694,10 +15862,10 @@
     </row>
     <row r="2" spans="2:8" ht="53.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="6"/>
-      <c r="C2" s="110"/>
-      <c r="D2" s="110"/>
-      <c r="E2" s="111"/>
-      <c r="F2" s="110"/>
+      <c r="C2" s="112"/>
+      <c r="D2" s="112"/>
+      <c r="E2" s="113"/>
+      <c r="F2" s="112"/>
     </row>
     <row r="3" spans="2:8" ht="9.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="6"/>
@@ -15718,23 +15886,23 @@
       <c r="H4" s="90"/>
     </row>
     <row r="5" spans="2:8" ht="28.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="117" t="s">
+      <c r="B5" s="119" t="s">
         <v>232</v>
       </c>
-      <c r="C5" s="118" t="s">
+      <c r="C5" s="120" t="s">
         <v>35</v>
       </c>
-      <c r="D5" s="118" t="s">
+      <c r="D5" s="120" t="s">
         <v>36</v>
       </c>
-      <c r="E5" s="118"/>
-      <c r="F5" s="118"/>
-      <c r="G5" s="118"/>
-      <c r="H5" s="118"/>
+      <c r="E5" s="120"/>
+      <c r="F5" s="120"/>
+      <c r="G5" s="120"/>
+      <c r="H5" s="120"/>
     </row>
     <row r="6" spans="2:8" ht="28.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="117"/>
-      <c r="C6" s="118"/>
+      <c r="B6" s="119"/>
+      <c r="C6" s="120"/>
       <c r="D6" s="91" t="s">
         <v>227</v>
       </c>
@@ -16644,16 +16812,16 @@
       </c>
     </row>
     <row r="9" spans="1:27" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="119"/>
-      <c r="C9" s="119"/>
-      <c r="H9" s="120" t="s">
+      <c r="B9" s="121"/>
+      <c r="C9" s="121"/>
+      <c r="H9" s="122" t="s">
         <v>110</v>
       </c>
-      <c r="I9" s="120"/>
-      <c r="J9" s="120"/>
-      <c r="K9" s="120"/>
-      <c r="L9" s="120"/>
-      <c r="M9" s="120"/>
+      <c r="I9" s="122"/>
+      <c r="J9" s="122"/>
+      <c r="K9" s="122"/>
+      <c r="L9" s="122"/>
+      <c r="M9" s="122"/>
       <c r="P9" s="19" t="s">
         <v>111</v>
       </c>
@@ -16675,14 +16843,14 @@
       </c>
     </row>
     <row r="10" spans="1:27" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="121" t="s">
+      <c r="A10" s="123" t="s">
         <v>116</v>
       </c>
-      <c r="B10" s="121"/>
-      <c r="C10" s="121"/>
-      <c r="D10" s="121"/>
-      <c r="E10" s="121"/>
-      <c r="F10" s="121"/>
+      <c r="B10" s="123"/>
+      <c r="C10" s="123"/>
+      <c r="D10" s="123"/>
+      <c r="E10" s="123"/>
+      <c r="F10" s="123"/>
       <c r="I10" s="27"/>
       <c r="J10" s="28" t="s">
         <v>117</v>
@@ -17010,11 +17178,11 @@
       <c r="AA16" s="24"/>
     </row>
     <row r="17" spans="1:27" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="119"/>
-      <c r="C17" s="119"/>
-      <c r="D17" s="119"/>
-      <c r="E17" s="119"/>
-      <c r="F17" s="119"/>
+      <c r="B17" s="121"/>
+      <c r="C17" s="121"/>
+      <c r="D17" s="121"/>
+      <c r="E17" s="121"/>
+      <c r="F17" s="121"/>
       <c r="P17" s="19" t="s">
         <v>170</v>
       </c>
@@ -17083,15 +17251,15 @@
       <c r="E21" s="44" t="s">
         <v>182</v>
       </c>
-      <c r="H21" s="122" t="s">
+      <c r="H21" s="124" t="s">
         <v>32</v>
       </c>
-      <c r="I21" s="122" t="s">
+      <c r="I21" s="124" t="s">
         <v>183</v>
       </c>
-      <c r="J21" s="122"/>
-      <c r="K21" s="122"/>
-      <c r="L21" s="122"/>
+      <c r="J21" s="124"/>
+      <c r="K21" s="124"/>
+      <c r="L21" s="124"/>
       <c r="P21" s="19" t="s">
         <v>184</v>
       </c>
@@ -17111,11 +17279,11 @@
       <c r="E22" s="45" t="s">
         <v>188</v>
       </c>
-      <c r="H22" s="122"/>
-      <c r="I22" s="122"/>
-      <c r="J22" s="122"/>
-      <c r="K22" s="122"/>
-      <c r="L22" s="122"/>
+      <c r="H22" s="124"/>
+      <c r="I22" s="124"/>
+      <c r="J22" s="124"/>
+      <c r="K22" s="124"/>
+      <c r="L22" s="124"/>
       <c r="P22" s="19" t="s">
         <v>189</v>
       </c>
@@ -17132,7 +17300,7 @@
       <c r="E23" s="44" t="s">
         <v>192</v>
       </c>
-      <c r="H23" s="122"/>
+      <c r="H23" s="124"/>
       <c r="I23" s="46">
         <v>1</v>
       </c>
@@ -17158,7 +17326,7 @@
       <c r="E24" s="45" t="s">
         <v>195</v>
       </c>
-      <c r="H24" s="122"/>
+      <c r="H24" s="124"/>
       <c r="I24" s="46">
         <v>0.9</v>
       </c>
@@ -17806,13 +17974,13 @@
     <mergeCell ref="I21:L22"/>
   </mergeCells>
   <conditionalFormatting sqref="I25:L30">
-    <cfRule type="cellIs" dxfId="3" priority="1" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="1" stopIfTrue="1" operator="equal">
       <formula>"NE"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="2" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="2" stopIfTrue="1" operator="equal">
       <formula>"VE"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="3" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="3" stopIfTrue="1" operator="equal">
       <formula>"CI"</formula>
     </cfRule>
   </conditionalFormatting>
